--- a/models/kimi-k3/kimi-k3-analysis.xlsx
+++ b/models/kimi-k3/kimi-k3-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rcbc1f4d3bf7d4ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R635e7593f08f4288"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R89bce39f71bf4098"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R7eb98dc02dcc493d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,13 +14,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="8">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.####"/>
     <x:numFmt numFmtId="203" formatCode="0.000000"/>
+    <x:numFmt numFmtId="204" formatCode="0.0%"/>
+    <x:numFmt numFmtId="205" formatCode="0.000"/>
+    <x:numFmt numFmtId="206" formatCode="0.00%"/>
+    <x:numFmt numFmtId="207" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -41,8 +45,14 @@
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="14"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -62,6 +72,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8EEF5"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -99,7 +124,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="42">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -172,10 +197,71 @@
     <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="2">
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:color rgb="FFA32020"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE9E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -4591,7 +4677,1493 @@
       <x:c r="O92" s="30"/>
       <x:c r="P92" s="30"/>
     </x:row>
+    <x:row r="95" ht="23" customHeight="1">
+      <x:c r="A95" s="42" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B95" s="30"/>
+      <x:c r="C95" s="30"/>
+      <x:c r="D95" s="30"/>
+      <x:c r="E95" s="30"/>
+      <x:c r="F95" s="30"/>
+      <x:c r="G95" s="30"/>
+      <x:c r="H95" s="30"/>
+      <x:c r="I95" s="30"/>
+      <x:c r="J95" s="30"/>
+      <x:c r="K95" s="30"/>
+      <x:c r="L95" s="30"/>
+    </x:row>
+    <x:row r="96" ht="23" customHeight="1">
+      <x:c r="A96" s="30" t="str">
+        <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B96" s="30"/>
+      <x:c r="C96" s="30"/>
+      <x:c r="D96" s="30"/>
+      <x:c r="E96" s="30"/>
+      <x:c r="F96" s="30"/>
+      <x:c r="G96" s="30"/>
+      <x:c r="H96" s="30"/>
+      <x:c r="I96" s="30"/>
+      <x:c r="J96" s="30"/>
+      <x:c r="K96" s="30"/>
+      <x:c r="L96" s="30"/>
+    </x:row>
+    <x:row r="97" ht="38" customHeight="1">
+      <x:c r="A97" s="45" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B97" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C97" s="45" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D97" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E97" s="45" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F97" s="45" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G97" s="45" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H97" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I97" s="30"/>
+      <x:c r="J97" s="30"/>
+      <x:c r="K97" s="30"/>
+      <x:c r="L97" s="30"/>
+    </x:row>
+    <x:row r="98" ht="23" customHeight="1">
+      <x:c r="A98" s="30"/>
+      <x:c r="B98" s="47" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C98" s="30"/>
+      <x:c r="D98" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E98" s="30"/>
+      <x:c r="F98" s="48"/>
+      <x:c r="G98" s="30"/>
+      <x:c r="H98" s="48" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I98" s="30"/>
+      <x:c r="J98" s="30"/>
+      <x:c r="K98" s="30"/>
+      <x:c r="L98" s="30"/>
+    </x:row>
+    <x:row r="99" ht="38" customHeight="1">
+      <x:c r="A99" s="45" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B99" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C99" s="45" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D99" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E99" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F99" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G99" s="45" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H99" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I99" s="45" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J99" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K99" s="45" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L99" s="45" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="23" customHeight="1">
+      <x:c r="A100" s="49"/>
+      <x:c r="B100" s="49" t="n">
+        <x:f>SUM(G104:G131)</x:f>
+        <x:v>761.74866432</x:v>
+      </x:c>
+      <x:c r="C100" s="49"/>
+      <x:c r="D100" s="49" t="n">
+        <x:f>SUM(H104:H131)</x:f>
+        <x:v>846.3874048</x:v>
+      </x:c>
+      <x:c r="E100" s="49"/>
+      <x:c r="F100" s="49" t="n">
+        <x:f>SUM(K104:K131)</x:f>
+        <x:v>84.63874048000001</x:v>
+      </x:c>
+      <x:c r="G100" s="49"/>
+      <x:c r="H100" s="49" t="str">
+        <x:f>IF(AND(ISNUMBER($F$98),$F$98&gt;0,$F$98&gt;=SUMPRODUCT(G104:G131,J104:J131)),$F$98+F100,"")</x:f>
+      </x:c>
+      <x:c r="I100" s="49"/>
+      <x:c r="J100" s="50" t="str">
+        <x:f>IF(AND(ISNUMBER($F$98),$F$98&gt;0,$F$98&gt;=SUMPRODUCT(G104:G131,J104:J131)),F100/$F$98,"")</x:f>
+      </x:c>
+      <x:c r="K100" s="49"/>
+      <x:c r="L100" s="49" t="str">
+        <x:f>IF($F$98="","待填基线",IF(AND(ISNUMBER($F$98),$F$98&gt;0,$F$98&gt;=SUMPRODUCT(G104:G131,J104:J131)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="23" customHeight="1">
+      <x:c r="A101" s="30" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B101" s="30"/>
+      <x:c r="C101" s="30"/>
+      <x:c r="D101" s="30"/>
+      <x:c r="E101" s="30"/>
+      <x:c r="F101" s="30"/>
+      <x:c r="G101" s="30"/>
+      <x:c r="H101" s="30"/>
+      <x:c r="I101" s="30"/>
+      <x:c r="J101" s="30"/>
+      <x:c r="K101" s="30"/>
+      <x:c r="L101" s="30"/>
+    </x:row>
+    <x:row r="102" ht="23" customHeight="1">
+      <x:c r="A102" s="30" t="str">
+        <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
+      </x:c>
+      <x:c r="B102" s="30"/>
+      <x:c r="C102" s="30"/>
+      <x:c r="D102" s="30"/>
+      <x:c r="E102" s="30"/>
+      <x:c r="F102" s="30"/>
+      <x:c r="G102" s="30"/>
+      <x:c r="H102" s="30"/>
+      <x:c r="I102" s="30"/>
+      <x:c r="J102" s="30"/>
+      <x:c r="K102" s="30"/>
+      <x:c r="L102" s="30"/>
+    </x:row>
+    <x:row r="103" ht="38" customHeight="1">
+      <x:c r="A103" s="45" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B103" s="45" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C103" s="45" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D103" s="45" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E103" s="45" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F103" s="45" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G103" s="45" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H103" s="45" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I103" s="45" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J103" s="45" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K103" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L103" s="45" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="23" customHeight="1">
+      <x:c r="A104" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B104" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C104" s="30" t="str">
+        <x:v>标准 TP 输出</x:v>
+      </x:c>
+      <x:c r="D104" s="34" t="n">
+        <x:f>(K65*2^20)/1e9</x:f>
+        <x:v>0.205520896</x:v>
+      </x:c>
+      <x:c r="E104" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F104" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G104" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E104),E104&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F104),F104&gt;=0,F104&lt;=1,ISNUMBER(J104),J104&gt;=0,J104&lt;=1),D104/E104*1000,NA())</x:f>
+        <x:v>2.0552089600000003</x:v>
+      </x:c>
+      <x:c r="H104" s="34" t="n">
+        <x:f>G104+I104</x:f>
+        <x:v>2.2835655111111115</x:v>
+      </x:c>
+      <x:c r="I104" s="34" t="n">
+        <x:f>G104*F104*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0.22835655111111114</x:v>
+      </x:c>
+      <x:c r="J104" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K104" s="34" t="n">
+        <x:f>I104*J104</x:f>
+        <x:v>0.22835655111111114</x:v>
+      </x:c>
+      <x:c r="L104" s="30" t="str">
+        <x:v>原通信行 65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="23" customHeight="1">
+      <x:c r="A105" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B105" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C105" s="30" t="str">
+        <x:v>Fine TP Token ID</x:v>
+      </x:c>
+      <x:c r="D105" s="34" t="n">
+        <x:f>(K66*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E105" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F105" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G105" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E105),E105&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F105),F105&gt;=0,F105&lt;=1,ISNUMBER(J105),J105&gt;=0,J105&lt;=1),D105/E105*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H105" s="34" t="n">
+        <x:f>G105+I105</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I105" s="34" t="n">
+        <x:f>G105*F105*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J105" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K105" s="34" t="n">
+        <x:f>I105*J105</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L105" s="30" t="str">
+        <x:v>原通信行 66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="23" customHeight="1">
+      <x:c r="A106" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B106" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C106" s="30" t="str">
+        <x:v>Fine TP Hidden</x:v>
+      </x:c>
+      <x:c r="D106" s="34" t="n">
+        <x:f>(K67*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E106" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F106" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G106" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E106),E106&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F106),F106&gt;=0,F106&lt;=1,ISNUMBER(J106),J106&gt;=0,J106&lt;=1),D106/E106*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H106" s="34" t="n">
+        <x:f>G106+I106</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I106" s="34" t="n">
+        <x:f>G106*F106*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J106" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K106" s="34" t="n">
+        <x:f>I106*J106</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L106" s="30" t="str">
+        <x:v>原通信行 67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="23" customHeight="1">
+      <x:c r="A107" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B107" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C107" s="30" t="str">
+        <x:v>Attention 前</x:v>
+      </x:c>
+      <x:c r="D107" s="34" t="n">
+        <x:f>(K68*2^20)/1e9</x:f>
+        <x:v>9.556721664</x:v>
+      </x:c>
+      <x:c r="E107" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F107" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G107" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E107),E107&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F107),F107&gt;=0,F107&lt;=1,ISNUMBER(J107),J107&gt;=0,J107&lt;=1),D107/E107*1000,NA())</x:f>
+        <x:v>95.56721664</x:v>
+      </x:c>
+      <x:c r="H107" s="34" t="n">
+        <x:f>G107+I107</x:f>
+        <x:v>106.18579626666667</x:v>
+      </x:c>
+      <x:c r="I107" s="34" t="n">
+        <x:f>G107*F107*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>10.618579626666666</x:v>
+      </x:c>
+      <x:c r="J107" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K107" s="34" t="n">
+        <x:f>I107*J107</x:f>
+        <x:v>10.618579626666666</x:v>
+      </x:c>
+      <x:c r="L107" s="30" t="str">
+        <x:v>原通信行 68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="23" customHeight="1">
+      <x:c r="A108" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B108" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C108" s="30" t="str">
+        <x:v>O Proj 后</x:v>
+      </x:c>
+      <x:c r="D108" s="34" t="n">
+        <x:f>(K69*2^20)/1e9</x:f>
+        <x:v>9.556721664</x:v>
+      </x:c>
+      <x:c r="E108" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F108" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G108" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E108),E108&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F108),F108&gt;=0,F108&lt;=1,ISNUMBER(J108),J108&gt;=0,J108&lt;=1),D108/E108*1000,NA())</x:f>
+        <x:v>95.56721664</x:v>
+      </x:c>
+      <x:c r="H108" s="34" t="n">
+        <x:f>G108+I108</x:f>
+        <x:v>106.18579626666667</x:v>
+      </x:c>
+      <x:c r="I108" s="34" t="n">
+        <x:f>G108*F108*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>10.618579626666666</x:v>
+      </x:c>
+      <x:c r="J108" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K108" s="34" t="n">
+        <x:f>I108*J108</x:f>
+        <x:v>10.618579626666666</x:v>
+      </x:c>
+      <x:c r="L108" s="30" t="str">
+        <x:v>原通信行 69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="23" customHeight="1">
+      <x:c r="A109" s="30" t="str">
+        <x:v>O Proj TP</x:v>
+      </x:c>
+      <x:c r="B109" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C109" s="30" t="str">
+        <x:v>非 SP 标准 TP</x:v>
+      </x:c>
+      <x:c r="D109" s="34" t="n">
+        <x:f>(K70*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E109" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F109" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G109" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E109),E109&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F109),F109&gt;=0,F109&lt;=1,ISNUMBER(J109),J109&gt;=0,J109&lt;=1),D109/E109*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H109" s="34" t="n">
+        <x:f>G109+I109</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I109" s="34" t="n">
+        <x:f>G109*F109*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J109" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K109" s="34" t="n">
+        <x:f>I109*J109</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L109" s="30" t="str">
+        <x:v>原通信行 70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="23" customHeight="1">
+      <x:c r="A110" s="30" t="str">
+        <x:v>Fine O TP</x:v>
+      </x:c>
+      <x:c r="B110" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C110" s="30" t="str">
+        <x:v>O Proj 输入</x:v>
+      </x:c>
+      <x:c r="D110" s="34" t="n">
+        <x:f>(K71*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E110" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F110" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G110" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E110),E110&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F110),F110&gt;=0,F110&lt;=1,ISNUMBER(J110),J110&gt;=0,J110&lt;=1),D110/E110*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H110" s="34" t="n">
+        <x:f>G110+I110</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I110" s="34" t="n">
+        <x:f>G110*F110*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J110" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K110" s="34" t="n">
+        <x:f>I110*J110</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L110" s="30" t="str">
+        <x:v>原通信行 71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="23" customHeight="1">
+      <x:c r="A111" s="30" t="str">
+        <x:v>Fine O TP</x:v>
+      </x:c>
+      <x:c r="B111" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C111" s="30" t="str">
+        <x:v>O Proj 输出</x:v>
+      </x:c>
+      <x:c r="D111" s="34" t="n">
+        <x:f>(K72*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E111" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F111" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G111" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E111),E111&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F111),F111&gt;=0,F111&lt;=1,ISNUMBER(J111),J111&gt;=0,J111&lt;=1),D111/E111*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H111" s="34" t="n">
+        <x:f>G111+I111</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I111" s="34" t="n">
+        <x:f>G111*F111*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J111" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K111" s="34" t="n">
+        <x:f>I111*J111</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L111" s="30" t="str">
+        <x:v>原通信行 72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="23" customHeight="1">
+      <x:c r="A112" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B112" s="30" t="str">
+        <x:v>Dense MLP</x:v>
+      </x:c>
+      <x:c r="C112" s="30" t="str">
+        <x:v>Down Proj 输出</x:v>
+      </x:c>
+      <x:c r="D112" s="34" t="n">
+        <x:f>(K73*2^20)/1e9</x:f>
+        <x:v>0.025690112</x:v>
+      </x:c>
+      <x:c r="E112" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F112" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G112" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E112),E112&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F112),F112&gt;=0,F112&lt;=1,ISNUMBER(J112),J112&gt;=0,J112&lt;=1),D112/E112*1000,NA())</x:f>
+        <x:v>0.25690112000000004</x:v>
+      </x:c>
+      <x:c r="H112" s="34" t="n">
+        <x:f>G112+I112</x:f>
+        <x:v>0.28544568888888894</x:v>
+      </x:c>
+      <x:c r="I112" s="34" t="n">
+        <x:f>G112*F112*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0.028544568888888892</x:v>
+      </x:c>
+      <x:c r="J112" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K112" s="34" t="n">
+        <x:f>I112*J112</x:f>
+        <x:v>0.028544568888888892</x:v>
+      </x:c>
+      <x:c r="L112" s="30" t="str">
+        <x:v>原通信行 73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="23" customHeight="1">
+      <x:c r="A113" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B113" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C113" s="30" t="str">
+        <x:v>Dispatch Hidden</x:v>
+      </x:c>
+      <x:c r="D113" s="34" t="n">
+        <x:f>(K74*2^20)/1e9</x:f>
+        <x:v>18.907922432</x:v>
+      </x:c>
+      <x:c r="E113" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F113" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G113" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E113),E113&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F113),F113&gt;=0,F113&lt;=1,ISNUMBER(J113),J113&gt;=0,J113&lt;=1),D113/E113*1000,NA())</x:f>
+        <x:v>189.07922431999998</x:v>
+      </x:c>
+      <x:c r="H113" s="34" t="n">
+        <x:f>G113+I113</x:f>
+        <x:v>210.0880270222222</x:v>
+      </x:c>
+      <x:c r="I113" s="34" t="n">
+        <x:f>G113*F113*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>21.008802702222223</x:v>
+      </x:c>
+      <x:c r="J113" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K113" s="34" t="n">
+        <x:f>I113*J113</x:f>
+        <x:v>21.008802702222223</x:v>
+      </x:c>
+      <x:c r="L113" s="30" t="str">
+        <x:v>原通信行 74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="23" customHeight="1">
+      <x:c r="A114" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B114" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C114" s="30" t="str">
+        <x:v>Combine Hidden</x:v>
+      </x:c>
+      <x:c r="D114" s="34" t="n">
+        <x:f>(K75*2^20)/1e9</x:f>
+        <x:v>18.907922432</x:v>
+      </x:c>
+      <x:c r="E114" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F114" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G114" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E114),E114&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F114),F114&gt;=0,F114&lt;=1,ISNUMBER(J114),J114&gt;=0,J114&lt;=1),D114/E114*1000,NA())</x:f>
+        <x:v>189.07922431999998</x:v>
+      </x:c>
+      <x:c r="H114" s="34" t="n">
+        <x:f>G114+I114</x:f>
+        <x:v>210.0880270222222</x:v>
+      </x:c>
+      <x:c r="I114" s="34" t="n">
+        <x:f>G114*F114*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>21.008802702222223</x:v>
+      </x:c>
+      <x:c r="J114" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K114" s="34" t="n">
+        <x:f>I114*J114</x:f>
+        <x:v>21.008802702222223</x:v>
+      </x:c>
+      <x:c r="L114" s="30" t="str">
+        <x:v>原通信行 75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="23" customHeight="1">
+      <x:c r="A115" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B115" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C115" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D115" s="34" t="n">
+        <x:f>(K76*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E115" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F115" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G115" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E115),E115&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F115),F115&gt;=0,F115&lt;=1,ISNUMBER(J115),J115&gt;=0,J115&lt;=1),D115/E115*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H115" s="34" t="n">
+        <x:f>G115+I115</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I115" s="34" t="n">
+        <x:f>G115*F115*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J115" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K115" s="34" t="n">
+        <x:f>I115*J115</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L115" s="30" t="str">
+        <x:v>原通信行 76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="23" customHeight="1">
+      <x:c r="A116" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B116" s="30" t="str">
+        <x:v>MoE Router</x:v>
+      </x:c>
+      <x:c r="C116" s="30" t="str">
+        <x:v>Router Logits</x:v>
+      </x:c>
+      <x:c r="D116" s="34" t="n">
+        <x:f>(K77*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E116" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F116" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G116" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E116),E116&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F116),F116&gt;=0,F116&lt;=1,ISNUMBER(J116),J116&gt;=0,J116&lt;=1),D116/E116*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H116" s="34" t="n">
+        <x:f>G116+I116</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I116" s="34" t="n">
+        <x:f>G116*F116*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J116" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K116" s="34" t="n">
+        <x:f>I116*J116</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L116" s="30" t="str">
+        <x:v>原通信行 77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="23" customHeight="1">
+      <x:c r="A117" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B117" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C117" s="30" t="str">
+        <x:v>Routed Expert 输出</x:v>
+      </x:c>
+      <x:c r="D117" s="34" t="n">
+        <x:f>(K78*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E117" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F117" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G117" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E117),E117&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F117),F117&gt;=0,F117&lt;=1,ISNUMBER(J117),J117&gt;=0,J117&lt;=1),D117/E117*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H117" s="34" t="n">
+        <x:f>G117+I117</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I117" s="34" t="n">
+        <x:f>G117*F117*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J117" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K117" s="34" t="n">
+        <x:f>I117*J117</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L117" s="30" t="str">
+        <x:v>原通信行 78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="23" customHeight="1">
+      <x:c r="A118" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B118" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C118" s="30" t="str">
+        <x:v>SP 输入</x:v>
+      </x:c>
+      <x:c r="D118" s="34" t="n">
+        <x:f>(K79*2^20)/1e9</x:f>
+        <x:v>9.453961216</x:v>
+      </x:c>
+      <x:c r="E118" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F118" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G118" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E118),E118&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F118),F118&gt;=0,F118&lt;=1,ISNUMBER(J118),J118&gt;=0,J118&lt;=1),D118/E118*1000,NA())</x:f>
+        <x:v>94.53961215999999</x:v>
+      </x:c>
+      <x:c r="H118" s="34" t="n">
+        <x:f>G118+I118</x:f>
+        <x:v>105.0440135111111</x:v>
+      </x:c>
+      <x:c r="I118" s="34" t="n">
+        <x:f>G118*F118*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>10.504401351111111</x:v>
+      </x:c>
+      <x:c r="J118" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K118" s="34" t="n">
+        <x:f>I118*J118</x:f>
+        <x:v>10.504401351111111</x:v>
+      </x:c>
+      <x:c r="L118" s="30" t="str">
+        <x:v>原通信行 79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="23" customHeight="1">
+      <x:c r="A119" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B119" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C119" s="30" t="str">
+        <x:v>SP 输出</x:v>
+      </x:c>
+      <x:c r="D119" s="34" t="n">
+        <x:f>(K80*2^20)/1e9</x:f>
+        <x:v>9.453961216</x:v>
+      </x:c>
+      <x:c r="E119" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F119" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G119" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E119),E119&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F119),F119&gt;=0,F119&lt;=1,ISNUMBER(J119),J119&gt;=0,J119&lt;=1),D119/E119*1000,NA())</x:f>
+        <x:v>94.53961215999999</x:v>
+      </x:c>
+      <x:c r="H119" s="34" t="n">
+        <x:f>G119+I119</x:f>
+        <x:v>105.0440135111111</x:v>
+      </x:c>
+      <x:c r="I119" s="34" t="n">
+        <x:f>G119*F119*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>10.504401351111111</x:v>
+      </x:c>
+      <x:c r="J119" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K119" s="34" t="n">
+        <x:f>I119*J119</x:f>
+        <x:v>10.504401351111111</x:v>
+      </x:c>
+      <x:c r="L119" s="30" t="str">
+        <x:v>原通信行 80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="23" customHeight="1">
+      <x:c r="A120" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B120" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C120" s="30" t="str">
+        <x:v>非 SP 输出</x:v>
+      </x:c>
+      <x:c r="D120" s="34" t="n">
+        <x:f>(K81*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E120" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F120" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G120" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E120),E120&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F120),F120&gt;=0,F120&lt;=1,ISNUMBER(J120),J120&gt;=0,J120&lt;=1),D120/E120*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H120" s="34" t="n">
+        <x:f>G120+I120</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I120" s="34" t="n">
+        <x:f>G120*F120*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J120" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K120" s="34" t="n">
+        <x:f>I120*J120</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L120" s="30" t="str">
+        <x:v>原通信行 81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="23" customHeight="1">
+      <x:c r="A121" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B121" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C121" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D121" s="34" t="n">
+        <x:f>(K82*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E121" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F121" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G121" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E121),E121&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F121),F121&gt;=0,F121&lt;=1,ISNUMBER(J121),J121&gt;=0,J121&lt;=1),D121/E121*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H121" s="34" t="n">
+        <x:f>G121+I121</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I121" s="34" t="n">
+        <x:f>G121*F121*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J121" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K121" s="34" t="n">
+        <x:f>I121*J121</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L121" s="30" t="str">
+        <x:v>原通信行 82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="23" customHeight="1">
+      <x:c r="A122" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B122" s="30" t="str">
+        <x:v>MoE Router</x:v>
+      </x:c>
+      <x:c r="C122" s="30" t="str">
+        <x:v>Router Logits</x:v>
+      </x:c>
+      <x:c r="D122" s="34" t="n">
+        <x:f>(K83*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E122" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F122" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G122" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E122),E122&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F122),F122&gt;=0,F122&lt;=1,ISNUMBER(J122),J122&gt;=0,J122&lt;=1),D122/E122*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H122" s="34" t="n">
+        <x:f>G122+I122</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I122" s="34" t="n">
+        <x:f>G122*F122*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J122" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K122" s="34" t="n">
+        <x:f>I122*J122</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L122" s="30" t="str">
+        <x:v>原通信行 83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="23" customHeight="1">
+      <x:c r="A123" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B123" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C123" s="30" t="str">
+        <x:v>Routed Expert 输出</x:v>
+      </x:c>
+      <x:c r="D123" s="34" t="n">
+        <x:f>(K84*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E123" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F123" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G123" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E123),E123&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F123),F123&gt;=0,F123&lt;=1,ISNUMBER(J123),J123&gt;=0,J123&lt;=1),D123/E123*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H123" s="34" t="n">
+        <x:f>G123+I123</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I123" s="34" t="n">
+        <x:f>G123*F123*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J123" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K123" s="34" t="n">
+        <x:f>I123*J123</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L123" s="30" t="str">
+        <x:v>原通信行 84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="23" customHeight="1">
+      <x:c r="A124" s="30" t="str">
+        <x:v>PCP</x:v>
+      </x:c>
+      <x:c r="B124" s="30" t="str">
+        <x:v>Attention KV</x:v>
+      </x:c>
+      <x:c r="C124" s="30" t="str">
+        <x:v>KV Cache 写入前</x:v>
+      </x:c>
+      <x:c r="D124" s="34" t="n">
+        <x:f>(K85*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E124" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F124" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G124" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E124),E124&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F124),F124&gt;=0,F124&lt;=1,ISNUMBER(J124),J124&gt;=0,J124&lt;=1),D124/E124*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H124" s="34" t="n">
+        <x:f>G124+I124</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I124" s="34" t="n">
+        <x:f>G124*F124*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J124" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K124" s="34" t="n">
+        <x:f>I124*J124</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L124" s="30" t="str">
+        <x:v>原通信行 85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="23" customHeight="1">
+      <x:c r="A125" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B125" s="30" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C125" s="30" t="str">
+        <x:v>Final Norm 后</x:v>
+      </x:c>
+      <x:c r="D125" s="34" t="n">
+        <x:f>(K86*2^20)/1e9</x:f>
+        <x:v>0.102760448</x:v>
+      </x:c>
+      <x:c r="E125" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F125" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G125" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E125),E125&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F125),F125&gt;=0,F125&lt;=1,ISNUMBER(J125),J125&gt;=0,J125&lt;=1),D125/E125*1000,NA())</x:f>
+        <x:v>1.0276044800000002</x:v>
+      </x:c>
+      <x:c r="H125" s="34" t="n">
+        <x:f>G125+I125</x:f>
+        <x:v>1.1417827555555558</x:v>
+      </x:c>
+      <x:c r="I125" s="34" t="n">
+        <x:f>G125*F125*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0.11417827555555557</x:v>
+      </x:c>
+      <x:c r="J125" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K125" s="34" t="n">
+        <x:f>I125*J125</x:f>
+        <x:v>0.11417827555555557</x:v>
+      </x:c>
+      <x:c r="L125" s="30" t="str">
+        <x:v>原通信行 86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="23" customHeight="1">
+      <x:c r="A126" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B126" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C126" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D126" s="34" t="n">
+        <x:f>(K87*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E126" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F126" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G126" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E126),E126&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F126),F126&gt;=0,F126&lt;=1,ISNUMBER(J126),J126&gt;=0,J126&lt;=1),D126/E126*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H126" s="34" t="n">
+        <x:f>G126+I126</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I126" s="34" t="n">
+        <x:f>G126*F126*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J126" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K126" s="34" t="n">
+        <x:f>I126*J126</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L126" s="30" t="str">
+        <x:v>原通信行 87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="23" customHeight="1">
+      <x:c r="A127" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B127" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C127" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D127" s="34" t="n">
+        <x:f>(K88*2^20)/1e9</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="E127" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F127" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G127" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E127),E127&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F127),F127&gt;=0,F127&lt;=1,ISNUMBER(J127),J127&gt;=0,J127&lt;=1),D127/E127*1000,NA())</x:f>
+        <x:v>0.01376256</x:v>
+      </x:c>
+      <x:c r="H127" s="34" t="n">
+        <x:f>G127+I127</x:f>
+        <x:v>0.015291733333333333</x:v>
+      </x:c>
+      <x:c r="I127" s="34" t="n">
+        <x:f>G127*F127*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0.0015291733333333336</x:v>
+      </x:c>
+      <x:c r="J127" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K127" s="34" t="n">
+        <x:f>I127*J127</x:f>
+        <x:v>0.0015291733333333336</x:v>
+      </x:c>
+      <x:c r="L127" s="30" t="str">
+        <x:v>原通信行 88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="23" customHeight="1">
+      <x:c r="A128" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B128" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C128" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D128" s="34" t="n">
+        <x:f>(K89*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E128" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F128" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G128" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E128),E128&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F128),F128&gt;=0,F128&lt;=1,ISNUMBER(J128),J128&gt;=0,J128&lt;=1),D128/E128*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H128" s="34" t="n">
+        <x:f>G128+I128</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I128" s="34" t="n">
+        <x:f>G128*F128*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J128" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K128" s="34" t="n">
+        <x:f>I128*J128</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L128" s="30" t="str">
+        <x:v>原通信行 89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="23" customHeight="1">
+      <x:c r="A129" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B129" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C129" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D129" s="34" t="n">
+        <x:f>(K90*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E129" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F129" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G129" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E129),E129&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F129),F129&gt;=0,F129&lt;=1,ISNUMBER(J129),J129&gt;=0,J129&lt;=1),D129/E129*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H129" s="34" t="n">
+        <x:f>G129+I129</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I129" s="34" t="n">
+        <x:f>G129*F129*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J129" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K129" s="34" t="n">
+        <x:f>I129*J129</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L129" s="30" t="str">
+        <x:v>原通信行 90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="23" customHeight="1">
+      <x:c r="A130" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B130" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C130" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D130" s="34" t="n">
+        <x:f>(K91*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E130" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F130" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G130" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E130),E130&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F130),F130&gt;=0,F130&lt;=1,ISNUMBER(J130),J130&gt;=0,J130&lt;=1),D130/E130*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H130" s="34" t="n">
+        <x:f>G130+I130</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I130" s="34" t="n">
+        <x:f>G130*F130*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J130" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K130" s="34" t="n">
+        <x:f>I130*J130</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L130" s="30" t="str">
+        <x:v>原通信行 91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="23" customHeight="1">
+      <x:c r="A131" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B131" s="30" t="str">
+        <x:v>MoE 计数</x:v>
+      </x:c>
+      <x:c r="C131" s="30" t="str">
+        <x:v>直方图 Ring AG</x:v>
+      </x:c>
+      <x:c r="D131" s="34" t="n">
+        <x:f>(IF(E74=0,0,H74*ROUNDUP(896/G74,0)*G74*4*(G74-1)))/1e9</x:f>
+        <x:v>0.002308096</x:v>
+      </x:c>
+      <x:c r="E131" s="51" t="n">
+        <x:f>$H$98</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F131" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G131" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E131),E131&gt;0,ISNUMBER($B$98),$B$98&gt;=0,$B$98&lt;1,ISNUMBER($D$98),$D$98&gt;=0,$D$98&lt;=1,ISNUMBER(F131),F131&gt;=0,F131&lt;=1,ISNUMBER(J131),J131&gt;=0,J131&lt;=1),D131/E131*1000,NA())</x:f>
+        <x:v>0.023080959999999998</x:v>
+      </x:c>
+      <x:c r="H131" s="34" t="n">
+        <x:f>G131+I131</x:f>
+        <x:v>0.02564551111111111</x:v>
+      </x:c>
+      <x:c r="I131" s="34" t="n">
+        <x:f>G131*F131*$D$98*$B$98/(1-$B$98)</x:f>
+        <x:v>0.002564551111111111</x:v>
+      </x:c>
+      <x:c r="J131" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K131" s="34" t="n">
+        <x:f>I131*J131</x:f>
+        <x:v>0.002564551111111111</x:v>
+      </x:c>
+      <x:c r="L131" s="30" t="str">
+        <x:v>额外控制量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="23" customHeight="1">
+      <x:c r="A132" s="53" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B132" s="53"/>
+      <x:c r="C132" s="53"/>
+      <x:c r="D132" s="54" t="n">
+        <x:f>SUM(D104:D131)</x:f>
+        <x:v>76.17486643199999</x:v>
+      </x:c>
+      <x:c r="E132" s="54"/>
+      <x:c r="F132" s="53"/>
+      <x:c r="G132" s="54" t="n">
+        <x:f>SUM(G104:G131)</x:f>
+        <x:v>761.74866432</x:v>
+      </x:c>
+      <x:c r="H132" s="54" t="n">
+        <x:f>SUM(H104:H131)</x:f>
+        <x:v>846.3874048</x:v>
+      </x:c>
+      <x:c r="I132" s="54" t="n">
+        <x:f>SUM(I104:I131)</x:f>
+        <x:v>84.63874048000001</x:v>
+      </x:c>
+      <x:c r="J132" s="53"/>
+      <x:c r="K132" s="54" t="n">
+        <x:f>SUM(K104:K131)</x:f>
+        <x:v>84.63874048000001</x:v>
+      </x:c>
+      <x:c r="L132" s="53"/>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="L100:L100">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -8767,7 +10339,1449 @@
       <x:c r="O91" s="30"/>
       <x:c r="P91" s="30"/>
     </x:row>
+    <x:row r="94" ht="23" customHeight="1">
+      <x:c r="A94" s="42" t="str">
+        <x:v>PD 带宽争用耗时评估</x:v>
+      </x:c>
+      <x:c r="B94" s="30"/>
+      <x:c r="C94" s="30"/>
+      <x:c r="D94" s="30"/>
+      <x:c r="E94" s="30"/>
+      <x:c r="F94" s="30"/>
+      <x:c r="G94" s="30"/>
+      <x:c r="H94" s="30"/>
+      <x:c r="I94" s="30"/>
+      <x:c r="J94" s="30"/>
+      <x:c r="K94" s="30"/>
+      <x:c r="L94" s="30"/>
+    </x:row>
+    <x:row r="95" ht="23" customHeight="1">
+      <x:c r="A95" s="30" t="str">
+        <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
+      </x:c>
+      <x:c r="B95" s="30"/>
+      <x:c r="C95" s="30"/>
+      <x:c r="D95" s="30"/>
+      <x:c r="E95" s="30"/>
+      <x:c r="F95" s="30"/>
+      <x:c r="G95" s="30"/>
+      <x:c r="H95" s="30"/>
+      <x:c r="I95" s="30"/>
+      <x:c r="J95" s="30"/>
+      <x:c r="K95" s="30"/>
+      <x:c r="L95" s="30"/>
+    </x:row>
+    <x:row r="96" ht="38" customHeight="1">
+      <x:c r="A96" s="45" t="str">
+        <x:v>带宽降幅</x:v>
+      </x:c>
+      <x:c r="B96" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="C96" s="45" t="str">
+        <x:v>争用覆盖率</x:v>
+      </x:c>
+      <x:c r="D96" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="E96" s="45" t="str">
+        <x:v>基线 forward ms</x:v>
+      </x:c>
+      <x:c r="F96" s="45" t="str">
+        <x:v>实测输入</x:v>
+      </x:c>
+      <x:c r="G96" s="45" t="str">
+        <x:v>默认带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="H96" s="45" t="str">
+        <x:v>输入</x:v>
+      </x:c>
+      <x:c r="I96" s="30"/>
+      <x:c r="J96" s="30"/>
+      <x:c r="K96" s="30"/>
+      <x:c r="L96" s="30"/>
+    </x:row>
+    <x:row r="97" ht="23" customHeight="1">
+      <x:c r="A97" s="30"/>
+      <x:c r="B97" s="47" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="C97" s="30"/>
+      <x:c r="D97" s="47" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E97" s="30"/>
+      <x:c r="F97" s="48"/>
+      <x:c r="G97" s="30"/>
+      <x:c r="H97" s="48" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="I97" s="30"/>
+      <x:c r="J97" s="30"/>
+      <x:c r="K97" s="30"/>
+      <x:c r="L97" s="30"/>
+    </x:row>
+    <x:row r="98" ht="38" customHeight="1">
+      <x:c r="A98" s="45" t="str">
+        <x:v>通信基线 ms</x:v>
+      </x:c>
+      <x:c r="B98" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="C98" s="45" t="str">
+        <x:v>通信争用后 ms</x:v>
+      </x:c>
+      <x:c r="D98" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="E98" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="F98" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="G98" s="45" t="str">
+        <x:v>forward 新耗时 ms</x:v>
+      </x:c>
+      <x:c r="H98" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="I98" s="45" t="str">
+        <x:v>forward 增幅</x:v>
+      </x:c>
+      <x:c r="J98" s="45" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+      <x:c r="K98" s="45" t="str">
+        <x:v>输入状态</x:v>
+      </x:c>
+      <x:c r="L98" s="45" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="23" customHeight="1">
+      <x:c r="A99" s="49"/>
+      <x:c r="B99" s="49" t="n">
+        <x:f>SUM(G103:G129)</x:f>
+        <x:v>97.08812288</x:v>
+      </x:c>
+      <x:c r="C99" s="49"/>
+      <x:c r="D99" s="49" t="n">
+        <x:f>SUM(H103:H129)</x:f>
+        <x:v>107.87569208888888</x:v>
+      </x:c>
+      <x:c r="E99" s="49"/>
+      <x:c r="F99" s="49" t="n">
+        <x:f>SUM(K103:K129)</x:f>
+        <x:v>10.787569208888891</x:v>
+      </x:c>
+      <x:c r="G99" s="49"/>
+      <x:c r="H99" s="49" t="str">
+        <x:f>IF(AND(ISNUMBER($F$97),$F$97&gt;0,$F$97&gt;=SUMPRODUCT(G103:G129,J103:J129)),$F$97+F99,"")</x:f>
+      </x:c>
+      <x:c r="I99" s="49"/>
+      <x:c r="J99" s="50" t="str">
+        <x:f>IF(AND(ISNUMBER($F$97),$F$97&gt;0,$F$97&gt;=SUMPRODUCT(G103:G129,J103:J129)),F99/$F$97,"")</x:f>
+      </x:c>
+      <x:c r="K99" s="49"/>
+      <x:c r="L99" s="49" t="str">
+        <x:f>IF($F$97="","待填基线",IF(AND(ISNUMBER($F$97),$F$97&gt;0,$F$97&gt;=SUMPRODUCT(G103:G129,J103:J129)),"已填基线","基线/暴露不一致"))</x:f>
+        <x:v>待填基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="23" customHeight="1">
+      <x:c r="A100" s="30" t="str">
+        <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
+      </x:c>
+      <x:c r="B100" s="30"/>
+      <x:c r="C100" s="30"/>
+      <x:c r="D100" s="30"/>
+      <x:c r="E100" s="30"/>
+      <x:c r="F100" s="30"/>
+      <x:c r="G100" s="30"/>
+      <x:c r="H100" s="30"/>
+      <x:c r="I100" s="30"/>
+      <x:c r="J100" s="30"/>
+      <x:c r="K100" s="30"/>
+      <x:c r="L100" s="30"/>
+    </x:row>
+    <x:row r="101" ht="23" customHeight="1">
+      <x:c r="A101" s="30" t="str">
+        <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
+      </x:c>
+      <x:c r="B101" s="30"/>
+      <x:c r="C101" s="30"/>
+      <x:c r="D101" s="30"/>
+      <x:c r="E101" s="30"/>
+      <x:c r="F101" s="30"/>
+      <x:c r="G101" s="30"/>
+      <x:c r="H101" s="30"/>
+      <x:c r="I101" s="30"/>
+      <x:c r="J101" s="30"/>
+      <x:c r="K101" s="30"/>
+      <x:c r="L101" s="30"/>
+    </x:row>
+    <x:row r="102" ht="38" customHeight="1">
+      <x:c r="A102" s="45" t="str">
+        <x:v>并行域</x:v>
+      </x:c>
+      <x:c r="B102" s="45" t="str">
+        <x:v>模块</x:v>
+      </x:c>
+      <x:c r="C102" s="45" t="str">
+        <x:v>通信事件</x:v>
+      </x:c>
+      <x:c r="D102" s="45" t="str">
+        <x:v>GB/Rank/Step</x:v>
+      </x:c>
+      <x:c r="E102" s="45" t="str">
+        <x:v>有效带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F102" s="45" t="str">
+        <x:v>共享比例</x:v>
+      </x:c>
+      <x:c r="G102" s="45" t="str">
+        <x:v>基线带宽项 ms</x:v>
+      </x:c>
+      <x:c r="H102" s="45" t="str">
+        <x:v>争用后带宽项 ms</x:v>
+      </x:c>
+      <x:c r="I102" s="45" t="str">
+        <x:v>通信增量 ms</x:v>
+      </x:c>
+      <x:c r="J102" s="45" t="str">
+        <x:v>暴露系数</x:v>
+      </x:c>
+      <x:c r="K102" s="45" t="str">
+        <x:v>forward 增量 ms</x:v>
+      </x:c>
+      <x:c r="L102" s="45" t="str">
+        <x:v>公式口径</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="23" customHeight="1">
+      <x:c r="A103" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B103" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C103" s="30" t="str">
+        <x:v>标准 TP 输出</x:v>
+      </x:c>
+      <x:c r="D103" s="34" t="n">
+        <x:f>(K65*2^20)/1e9</x:f>
+        <x:v>0.025690112</x:v>
+      </x:c>
+      <x:c r="E103" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F103" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G103" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E103),E103&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F103),F103&gt;=0,F103&lt;=1,ISNUMBER(J103),J103&gt;=0,J103&lt;=1),D103/E103*1000,NA())</x:f>
+        <x:v>0.25690112000000004</x:v>
+      </x:c>
+      <x:c r="H103" s="34" t="n">
+        <x:f>G103+I103</x:f>
+        <x:v>0.28544568888888894</x:v>
+      </x:c>
+      <x:c r="I103" s="34" t="n">
+        <x:f>G103*F103*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0.028544568888888892</x:v>
+      </x:c>
+      <x:c r="J103" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K103" s="34" t="n">
+        <x:f>I103*J103</x:f>
+        <x:v>0.028544568888888892</x:v>
+      </x:c>
+      <x:c r="L103" s="30" t="str">
+        <x:v>原通信行 65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="23" customHeight="1">
+      <x:c r="A104" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B104" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C104" s="30" t="str">
+        <x:v>Fine TP Token ID</x:v>
+      </x:c>
+      <x:c r="D104" s="34" t="n">
+        <x:f>(K66*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E104" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F104" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G104" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E104),E104&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F104),F104&gt;=0,F104&lt;=1,ISNUMBER(J104),J104&gt;=0,J104&lt;=1),D104/E104*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H104" s="34" t="n">
+        <x:f>G104+I104</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I104" s="34" t="n">
+        <x:f>G104*F104*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J104" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K104" s="34" t="n">
+        <x:f>I104*J104</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L104" s="30" t="str">
+        <x:v>原通信行 66</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="23" customHeight="1">
+      <x:c r="A105" s="30" t="str">
+        <x:v>Embedding TP</x:v>
+      </x:c>
+      <x:c r="B105" s="30" t="str">
+        <x:v>Embedding</x:v>
+      </x:c>
+      <x:c r="C105" s="30" t="str">
+        <x:v>Fine TP Hidden</x:v>
+      </x:c>
+      <x:c r="D105" s="34" t="n">
+        <x:f>(K67*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E105" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F105" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G105" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E105),E105&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F105),F105&gt;=0,F105&lt;=1,ISNUMBER(J105),J105&gt;=0,J105&lt;=1),D105/E105*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H105" s="34" t="n">
+        <x:f>G105+I105</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I105" s="34" t="n">
+        <x:f>G105*F105*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J105" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K105" s="34" t="n">
+        <x:f>I105*J105</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L105" s="30" t="str">
+        <x:v>原通信行 67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="23" customHeight="1">
+      <x:c r="A106" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B106" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C106" s="30" t="str">
+        <x:v>Attention 前</x:v>
+      </x:c>
+      <x:c r="D106" s="34" t="n">
+        <x:f>(K68*2^20)/1e9</x:f>
+        <x:v>1.194590208</x:v>
+      </x:c>
+      <x:c r="E106" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F106" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G106" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E106),E106&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F106),F106&gt;=0,F106&lt;=1,ISNUMBER(J106),J106&gt;=0,J106&lt;=1),D106/E106*1000,NA())</x:f>
+        <x:v>11.94590208</x:v>
+      </x:c>
+      <x:c r="H106" s="34" t="n">
+        <x:f>G106+I106</x:f>
+        <x:v>13.273224533333334</x:v>
+      </x:c>
+      <x:c r="I106" s="34" t="n">
+        <x:f>G106*F106*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>1.3273224533333332</x:v>
+      </x:c>
+      <x:c r="J106" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K106" s="34" t="n">
+        <x:f>I106*J106</x:f>
+        <x:v>1.3273224533333332</x:v>
+      </x:c>
+      <x:c r="L106" s="30" t="str">
+        <x:v>原通信行 68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="23" customHeight="1">
+      <x:c r="A107" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B107" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C107" s="30" t="str">
+        <x:v>O Proj 后</x:v>
+      </x:c>
+      <x:c r="D107" s="34" t="n">
+        <x:f>(K69*2^20)/1e9</x:f>
+        <x:v>1.194590208</x:v>
+      </x:c>
+      <x:c r="E107" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F107" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G107" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E107),E107&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F107),F107&gt;=0,F107&lt;=1,ISNUMBER(J107),J107&gt;=0,J107&lt;=1),D107/E107*1000,NA())</x:f>
+        <x:v>11.94590208</x:v>
+      </x:c>
+      <x:c r="H107" s="34" t="n">
+        <x:f>G107+I107</x:f>
+        <x:v>13.273224533333334</x:v>
+      </x:c>
+      <x:c r="I107" s="34" t="n">
+        <x:f>G107*F107*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>1.3273224533333332</x:v>
+      </x:c>
+      <x:c r="J107" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K107" s="34" t="n">
+        <x:f>I107*J107</x:f>
+        <x:v>1.3273224533333332</x:v>
+      </x:c>
+      <x:c r="L107" s="30" t="str">
+        <x:v>原通信行 69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="23" customHeight="1">
+      <x:c r="A108" s="30" t="str">
+        <x:v>O Proj TP</x:v>
+      </x:c>
+      <x:c r="B108" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C108" s="30" t="str">
+        <x:v>非 SP 标准 TP</x:v>
+      </x:c>
+      <x:c r="D108" s="34" t="n">
+        <x:f>(K70*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E108" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F108" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G108" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E108),E108&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F108),F108&gt;=0,F108&lt;=1,ISNUMBER(J108),J108&gt;=0,J108&lt;=1),D108/E108*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H108" s="34" t="n">
+        <x:f>G108+I108</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I108" s="34" t="n">
+        <x:f>G108*F108*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J108" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K108" s="34" t="n">
+        <x:f>I108*J108</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L108" s="30" t="str">
+        <x:v>原通信行 70</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="23" customHeight="1">
+      <x:c r="A109" s="30" t="str">
+        <x:v>Fine O TP</x:v>
+      </x:c>
+      <x:c r="B109" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C109" s="30" t="str">
+        <x:v>O Proj 输入</x:v>
+      </x:c>
+      <x:c r="D109" s="34" t="n">
+        <x:f>(K71*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E109" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F109" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G109" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E109),E109&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F109),F109&gt;=0,F109&lt;=1,ISNUMBER(J109),J109&gt;=0,J109&lt;=1),D109/E109*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H109" s="34" t="n">
+        <x:f>G109+I109</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I109" s="34" t="n">
+        <x:f>G109*F109*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J109" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K109" s="34" t="n">
+        <x:f>I109*J109</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L109" s="30" t="str">
+        <x:v>原通信行 71</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="23" customHeight="1">
+      <x:c r="A110" s="30" t="str">
+        <x:v>Fine O TP</x:v>
+      </x:c>
+      <x:c r="B110" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C110" s="30" t="str">
+        <x:v>O Proj 输出</x:v>
+      </x:c>
+      <x:c r="D110" s="34" t="n">
+        <x:f>(K72*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E110" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F110" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G110" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E110),E110&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F110),F110&gt;=0,F110&lt;=1,ISNUMBER(J110),J110&gt;=0,J110&lt;=1),D110/E110*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H110" s="34" t="n">
+        <x:f>G110+I110</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I110" s="34" t="n">
+        <x:f>G110*F110*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J110" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K110" s="34" t="n">
+        <x:f>I110*J110</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L110" s="30" t="str">
+        <x:v>原通信行 72</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="23" customHeight="1">
+      <x:c r="A111" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B111" s="30" t="str">
+        <x:v>Dense MLP</x:v>
+      </x:c>
+      <x:c r="C111" s="30" t="str">
+        <x:v>Down Proj 输出</x:v>
+      </x:c>
+      <x:c r="D111" s="34" t="n">
+        <x:f>(K73*2^20)/1e9</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="E111" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F111" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G111" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E111),E111&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F111),F111&gt;=0,F111&lt;=1,ISNUMBER(J111),J111&gt;=0,J111&lt;=1),D111/E111*1000,NA())</x:f>
+        <x:v>0.032112640000000005</x:v>
+      </x:c>
+      <x:c r="H111" s="34" t="n">
+        <x:f>G111+I111</x:f>
+        <x:v>0.03568071111111112</x:v>
+      </x:c>
+      <x:c r="I111" s="34" t="n">
+        <x:f>G111*F111*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0.0035680711111111115</x:v>
+      </x:c>
+      <x:c r="J111" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K111" s="34" t="n">
+        <x:f>I111*J111</x:f>
+        <x:v>0.0035680711111111115</x:v>
+      </x:c>
+      <x:c r="L111" s="30" t="str">
+        <x:v>原通信行 73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="23" customHeight="1">
+      <x:c r="A112" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B112" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C112" s="30" t="str">
+        <x:v>MC2 FullMesh Dispatch</x:v>
+      </x:c>
+      <x:c r="D112" s="34" t="n">
+        <x:f>(IF(F74=2,E74/7168*H74*(ROUNDUP((ROUNDUP(7168*F74/32,0)*32+32)/480,0)*512),NA()))/1e9</x:f>
+        <x:v>2.53231104</x:v>
+      </x:c>
+      <x:c r="E112" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F112" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G112" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E112),E112&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F112),F112&gt;=0,F112&lt;=1,ISNUMBER(J112),J112&gt;=0,J112&lt;=1),D112/E112*1000,NA())</x:f>
+        <x:v>25.3231104</x:v>
+      </x:c>
+      <x:c r="H112" s="34" t="n">
+        <x:f>G112+I112</x:f>
+        <x:v>28.136789333333333</x:v>
+      </x:c>
+      <x:c r="I112" s="34" t="n">
+        <x:f>G112*F112*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>2.8136789333333336</x:v>
+      </x:c>
+      <x:c r="J112" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K112" s="34" t="n">
+        <x:f>I112*J112</x:f>
+        <x:v>2.8136789333333336</x:v>
+      </x:c>
+      <x:c r="L112" s="30" t="str">
+        <x:v>原通信行 74</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="23" customHeight="1">
+      <x:c r="A113" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B113" s="30" t="str">
+        <x:v>Routed Experts</x:v>
+      </x:c>
+      <x:c r="C113" s="30" t="str">
+        <x:v>MC2 Combine + flags</x:v>
+      </x:c>
+      <x:c r="D113" s="34" t="n">
+        <x:f>(IF(F75=2,K75*2^20+E75/7168*H75*32,NA()))/1e9</x:f>
+        <x:v>2.368765952</x:v>
+      </x:c>
+      <x:c r="E113" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F113" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G113" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E113),E113&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F113),F113&gt;=0,F113&lt;=1,ISNUMBER(J113),J113&gt;=0,J113&lt;=1),D113/E113*1000,NA())</x:f>
+        <x:v>23.68765952</x:v>
+      </x:c>
+      <x:c r="H113" s="34" t="n">
+        <x:f>G113+I113</x:f>
+        <x:v>26.31962168888889</x:v>
+      </x:c>
+      <x:c r="I113" s="34" t="n">
+        <x:f>G113*F113*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>2.631962168888889</x:v>
+      </x:c>
+      <x:c r="J113" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K113" s="34" t="n">
+        <x:f>I113*J113</x:f>
+        <x:v>2.631962168888889</x:v>
+      </x:c>
+      <x:c r="L113" s="30" t="str">
+        <x:v>原通信行 75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="23" customHeight="1">
+      <x:c r="A114" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B114" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C114" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D114" s="34" t="n">
+        <x:f>(K76*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E114" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F114" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G114" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E114),E114&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F114),F114&gt;=0,F114&lt;=1,ISNUMBER(J114),J114&gt;=0,J114&lt;=1),D114/E114*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H114" s="34" t="n">
+        <x:f>G114+I114</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I114" s="34" t="n">
+        <x:f>G114*F114*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J114" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K114" s="34" t="n">
+        <x:f>I114*J114</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L114" s="30" t="str">
+        <x:v>原通信行 76</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="23" customHeight="1">
+      <x:c r="A115" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B115" s="30" t="str">
+        <x:v>MoE Router</x:v>
+      </x:c>
+      <x:c r="C115" s="30" t="str">
+        <x:v>Router Logits</x:v>
+      </x:c>
+      <x:c r="D115" s="34" t="n">
+        <x:f>(K77*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E115" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F115" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G115" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E115),E115&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F115),F115&gt;=0,F115&lt;=1,ISNUMBER(J115),J115&gt;=0,J115&lt;=1),D115/E115*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H115" s="34" t="n">
+        <x:f>G115+I115</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I115" s="34" t="n">
+        <x:f>G115*F115*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J115" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K115" s="34" t="n">
+        <x:f>I115*J115</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L115" s="30" t="str">
+        <x:v>原通信行 77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="23" customHeight="1">
+      <x:c r="A116" s="30" t="str">
+        <x:v>DP</x:v>
+      </x:c>
+      <x:c r="B116" s="30" t="str">
+        <x:v>MoE</x:v>
+      </x:c>
+      <x:c r="C116" s="30" t="str">
+        <x:v>Routed Expert 输出</x:v>
+      </x:c>
+      <x:c r="D116" s="34" t="n">
+        <x:f>(K78*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E116" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F116" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G116" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E116),E116&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F116),F116&gt;=0,F116&lt;=1,ISNUMBER(J116),J116&gt;=0,J116&lt;=1),D116/E116*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H116" s="34" t="n">
+        <x:f>G116+I116</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I116" s="34" t="n">
+        <x:f>G116*F116*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J116" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K116" s="34" t="n">
+        <x:f>I116*J116</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L116" s="30" t="str">
+        <x:v>原通信行 78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="23" customHeight="1">
+      <x:c r="A117" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B117" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C117" s="30" t="str">
+        <x:v>SP 输入</x:v>
+      </x:c>
+      <x:c r="D117" s="34" t="n">
+        <x:f>(K79*2^20)/1e9</x:f>
+        <x:v>1.181745152</x:v>
+      </x:c>
+      <x:c r="E117" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F117" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G117" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E117),E117&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F117),F117&gt;=0,F117&lt;=1,ISNUMBER(J117),J117&gt;=0,J117&lt;=1),D117/E117*1000,NA())</x:f>
+        <x:v>11.817451519999999</x:v>
+      </x:c>
+      <x:c r="H117" s="34" t="n">
+        <x:f>G117+I117</x:f>
+        <x:v>13.130501688888888</x:v>
+      </x:c>
+      <x:c r="I117" s="34" t="n">
+        <x:f>G117*F117*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>1.313050168888889</x:v>
+      </x:c>
+      <x:c r="J117" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K117" s="34" t="n">
+        <x:f>I117*J117</x:f>
+        <x:v>1.313050168888889</x:v>
+      </x:c>
+      <x:c r="L117" s="30" t="str">
+        <x:v>原通信行 79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="23" customHeight="1">
+      <x:c r="A118" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B118" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C118" s="30" t="str">
+        <x:v>SP 输出</x:v>
+      </x:c>
+      <x:c r="D118" s="34" t="n">
+        <x:f>(K80*2^20)/1e9</x:f>
+        <x:v>1.181745152</x:v>
+      </x:c>
+      <x:c r="E118" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F118" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G118" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E118),E118&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F118),F118&gt;=0,F118&lt;=1,ISNUMBER(J118),J118&gt;=0,J118&lt;=1),D118/E118*1000,NA())</x:f>
+        <x:v>11.817451519999999</x:v>
+      </x:c>
+      <x:c r="H118" s="34" t="n">
+        <x:f>G118+I118</x:f>
+        <x:v>13.130501688888888</x:v>
+      </x:c>
+      <x:c r="I118" s="34" t="n">
+        <x:f>G118*F118*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>1.313050168888889</x:v>
+      </x:c>
+      <x:c r="J118" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K118" s="34" t="n">
+        <x:f>I118*J118</x:f>
+        <x:v>1.313050168888889</x:v>
+      </x:c>
+      <x:c r="L118" s="30" t="str">
+        <x:v>原通信行 80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="23" customHeight="1">
+      <x:c r="A119" s="30" t="str">
+        <x:v>共享专家 TP</x:v>
+      </x:c>
+      <x:c r="B119" s="30" t="str">
+        <x:v>Shared Experts</x:v>
+      </x:c>
+      <x:c r="C119" s="30" t="str">
+        <x:v>非 SP 输出</x:v>
+      </x:c>
+      <x:c r="D119" s="34" t="n">
+        <x:f>(K81*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E119" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F119" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G119" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E119),E119&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F119),F119&gt;=0,F119&lt;=1,ISNUMBER(J119),J119&gt;=0,J119&lt;=1),D119/E119*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H119" s="34" t="n">
+        <x:f>G119+I119</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I119" s="34" t="n">
+        <x:f>G119*F119*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J119" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K119" s="34" t="n">
+        <x:f>I119*J119</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L119" s="30" t="str">
+        <x:v>原通信行 81</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="23" customHeight="1">
+      <x:c r="A120" s="30" t="str">
+        <x:v>DCP</x:v>
+      </x:c>
+      <x:c r="B120" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C120" s="30" t="str">
+        <x:v>Query</x:v>
+      </x:c>
+      <x:c r="D120" s="34" t="n">
+        <x:f>(K82*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E120" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F120" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G120" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E120),E120&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F120),F120&gt;=0,F120&lt;=1,ISNUMBER(J120),J120&gt;=0,J120&lt;=1),D120/E120*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H120" s="34" t="n">
+        <x:f>G120+I120</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I120" s="34" t="n">
+        <x:f>G120*F120*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J120" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K120" s="34" t="n">
+        <x:f>I120*J120</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L120" s="30" t="str">
+        <x:v>原通信行 82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="23" customHeight="1">
+      <x:c r="A121" s="30" t="str">
+        <x:v>DCP</x:v>
+      </x:c>
+      <x:c r="B121" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C121" s="30" t="str">
+        <x:v>LSE</x:v>
+      </x:c>
+      <x:c r="D121" s="34" t="n">
+        <x:f>(K83*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E121" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F121" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G121" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E121),E121&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F121),F121&gt;=0,F121&lt;=1,ISNUMBER(J121),J121&gt;=0,J121&lt;=1),D121/E121*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H121" s="34" t="n">
+        <x:f>G121+I121</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I121" s="34" t="n">
+        <x:f>G121*F121*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J121" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K121" s="34" t="n">
+        <x:f>I121*J121</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L121" s="30" t="str">
+        <x:v>原通信行 83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="23" customHeight="1">
+      <x:c r="A122" s="30" t="str">
+        <x:v>DCP</x:v>
+      </x:c>
+      <x:c r="B122" s="30" t="str">
+        <x:v>Attention</x:v>
+      </x:c>
+      <x:c r="C122" s="30" t="str">
+        <x:v>Attention 输出</x:v>
+      </x:c>
+      <x:c r="D122" s="34" t="n">
+        <x:f>(K84*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E122" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F122" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G122" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E122),E122&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F122),F122&gt;=0,F122&lt;=1,ISNUMBER(J122),J122&gt;=0,J122&lt;=1),D122/E122*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H122" s="34" t="n">
+        <x:f>G122+I122</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I122" s="34" t="n">
+        <x:f>G122*F122*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J122" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K122" s="34" t="n">
+        <x:f>I122*J122</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L122" s="30" t="str">
+        <x:v>原通信行 84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="23" customHeight="1">
+      <x:c r="A123" s="30" t="str">
+        <x:v>SP</x:v>
+      </x:c>
+      <x:c r="B123" s="30" t="str">
+        <x:v>Model Output</x:v>
+      </x:c>
+      <x:c r="C123" s="30" t="str">
+        <x:v>Final Norm 后</x:v>
+      </x:c>
+      <x:c r="D123" s="34" t="n">
+        <x:f>(K85*2^20)/1e9</x:f>
+        <x:v>0.012845056</x:v>
+      </x:c>
+      <x:c r="E123" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F123" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G123" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E123),E123&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F123),F123&gt;=0,F123&lt;=1,ISNUMBER(J123),J123&gt;=0,J123&lt;=1),D123/E123*1000,NA())</x:f>
+        <x:v>0.12845056000000002</x:v>
+      </x:c>
+      <x:c r="H123" s="34" t="n">
+        <x:f>G123+I123</x:f>
+        <x:v>0.14272284444444447</x:v>
+      </x:c>
+      <x:c r="I123" s="34" t="n">
+        <x:f>G123*F123*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0.014272284444444446</x:v>
+      </x:c>
+      <x:c r="J123" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K123" s="34" t="n">
+        <x:f>I123*J123</x:f>
+        <x:v>0.014272284444444446</x:v>
+      </x:c>
+      <x:c r="L123" s="30" t="str">
+        <x:v>原通信行 85</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="23" customHeight="1">
+      <x:c r="A124" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B124" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C124" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D124" s="34" t="n">
+        <x:f>(K86*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E124" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F124" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G124" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E124),E124&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F124),F124&gt;=0,F124&lt;=1,ISNUMBER(J124),J124&gt;=0,J124&lt;=1),D124/E124*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H124" s="34" t="n">
+        <x:f>G124+I124</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I124" s="34" t="n">
+        <x:f>G124*F124*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J124" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K124" s="34" t="n">
+        <x:f>I124*J124</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L124" s="30" t="str">
+        <x:v>原通信行 86</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="23" customHeight="1">
+      <x:c r="A125" s="30" t="str">
+        <x:v>LM Head TP</x:v>
+      </x:c>
+      <x:c r="B125" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C125" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D125" s="34" t="n">
+        <x:f>(K87*2^20)/1e9</x:f>
+        <x:v>0.011010048</x:v>
+      </x:c>
+      <x:c r="E125" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F125" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G125" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E125),E125&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F125),F125&gt;=0,F125&lt;=1,ISNUMBER(J125),J125&gt;=0,J125&lt;=1),D125/E125*1000,NA())</x:f>
+        <x:v>0.11010048</x:v>
+      </x:c>
+      <x:c r="H125" s="34" t="n">
+        <x:f>G125+I125</x:f>
+        <x:v>0.12233386666666667</x:v>
+      </x:c>
+      <x:c r="I125" s="34" t="n">
+        <x:f>G125*F125*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0.012233386666666669</x:v>
+      </x:c>
+      <x:c r="J125" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K125" s="34" t="n">
+        <x:f>I125*J125</x:f>
+        <x:v>0.012233386666666669</x:v>
+      </x:c>
+      <x:c r="L125" s="30" t="str">
+        <x:v>原通信行 87</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="23" customHeight="1">
+      <x:c r="A126" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B126" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C126" s="30" t="str">
+        <x:v>Hidden 输入</x:v>
+      </x:c>
+      <x:c r="D126" s="34" t="n">
+        <x:f>(K88*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E126" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F126" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G126" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E126),E126&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F126),F126&gt;=0,F126&lt;=1,ISNUMBER(J126),J126&gt;=0,J126&lt;=1),D126/E126*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H126" s="34" t="n">
+        <x:f>G126+I126</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I126" s="34" t="n">
+        <x:f>G126*F126*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J126" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K126" s="34" t="n">
+        <x:f>I126*J126</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L126" s="30" t="str">
+        <x:v>原通信行 88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="23" customHeight="1">
+      <x:c r="A127" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B127" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C127" s="30" t="str">
+        <x:v>完整 Logits</x:v>
+      </x:c>
+      <x:c r="D127" s="34" t="n">
+        <x:f>(K89*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E127" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F127" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G127" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E127),E127&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F127),F127&gt;=0,F127&lt;=1,ISNUMBER(J127),J127&gt;=0,J127&lt;=1),D127/E127*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H127" s="34" t="n">
+        <x:f>G127+I127</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I127" s="34" t="n">
+        <x:f>G127*F127*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J127" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K127" s="34" t="n">
+        <x:f>I127*J127</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L127" s="30" t="str">
+        <x:v>原通信行 89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="23" customHeight="1">
+      <x:c r="A128" s="30" t="str">
+        <x:v>Fine LM Head TP</x:v>
+      </x:c>
+      <x:c r="B128" s="30" t="str">
+        <x:v>LM Head</x:v>
+      </x:c>
+      <x:c r="C128" s="30" t="str">
+        <x:v>Reduce Sample</x:v>
+      </x:c>
+      <x:c r="D128" s="34" t="n">
+        <x:f>(K90*2^20)/1e9</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E128" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F128" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G128" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E128),E128&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F128),F128&gt;=0,F128&lt;=1,ISNUMBER(J128),J128&gt;=0,J128&lt;=1),D128/E128*1000,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H128" s="34" t="n">
+        <x:f>G128+I128</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I128" s="34" t="n">
+        <x:f>G128*F128*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J128" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K128" s="34" t="n">
+        <x:f>I128*J128</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L128" s="30" t="str">
+        <x:v>原通信行 90</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="23" customHeight="1">
+      <x:c r="A129" s="30" t="str">
+        <x:v>EP</x:v>
+      </x:c>
+      <x:c r="B129" s="30" t="str">
+        <x:v>MoE 计数</x:v>
+      </x:c>
+      <x:c r="C129" s="30" t="str">
+        <x:v>MC2 count 写入</x:v>
+      </x:c>
+      <x:c r="D129" s="34" t="n">
+        <x:f>(IF(E74=0,0,H74*ROUNDUP(896/G74,0)*(G74-1)*32))/1e9</x:f>
+        <x:v>0.002308096</x:v>
+      </x:c>
+      <x:c r="E129" s="51" t="n">
+        <x:f>$H$97</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F129" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G129" s="34" t="n">
+        <x:f>IF(AND(ISNUMBER(E129),E129&gt;0,ISNUMBER($B$97),$B$97&gt;=0,$B$97&lt;1,ISNUMBER($D$97),$D$97&gt;=0,$D$97&lt;=1,ISNUMBER(F129),F129&gt;=0,F129&lt;=1,ISNUMBER(J129),J129&gt;=0,J129&lt;=1),D129/E129*1000,NA())</x:f>
+        <x:v>0.023080959999999998</x:v>
+      </x:c>
+      <x:c r="H129" s="34" t="n">
+        <x:f>G129+I129</x:f>
+        <x:v>0.02564551111111111</x:v>
+      </x:c>
+      <x:c r="I129" s="34" t="n">
+        <x:f>G129*F129*$D$97*$B$97/(1-$B$97)</x:f>
+        <x:v>0.002564551111111111</x:v>
+      </x:c>
+      <x:c r="J129" s="52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K129" s="34" t="n">
+        <x:f>I129*J129</x:f>
+        <x:v>0.002564551111111111</x:v>
+      </x:c>
+      <x:c r="L129" s="30" t="str">
+        <x:v>额外控制量</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="23" customHeight="1">
+      <x:c r="A130" s="53" t="str">
+        <x:v>所列事件串行相加</x:v>
+      </x:c>
+      <x:c r="B130" s="53"/>
+      <x:c r="C130" s="53"/>
+      <x:c r="D130" s="54" t="n">
+        <x:f>SUM(D103:D129)</x:f>
+        <x:v>9.708812287999999</x:v>
+      </x:c>
+      <x:c r="E130" s="54"/>
+      <x:c r="F130" s="53"/>
+      <x:c r="G130" s="54" t="n">
+        <x:f>SUM(G103:G129)</x:f>
+        <x:v>97.08812288</x:v>
+      </x:c>
+      <x:c r="H130" s="54" t="n">
+        <x:f>SUM(H103:H129)</x:f>
+        <x:v>107.87569208888888</x:v>
+      </x:c>
+      <x:c r="I130" s="54" t="n">
+        <x:f>SUM(I103:I129)</x:f>
+        <x:v>10.787569208888891</x:v>
+      </x:c>
+      <x:c r="J130" s="53"/>
+      <x:c r="K130" s="54" t="n">
+        <x:f>SUM(K103:K129)</x:f>
+        <x:v>10.787569208888891</x:v>
+      </x:c>
+      <x:c r="L130" s="53"/>
+    </x:row>
   </x:sheetData>
+  <x:conditionalFormatting sqref="L99:L99">
+    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="不一致"/>
+  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/models/kimi-k3/kimi-k3-analysis.xlsx
+++ b/models/kimi-k3/kimi-k3-analysis.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R89bce39f71bf4098"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R7eb98dc02dcc493d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rcf5e61380727478b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R791602ac66134472"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,7 +52,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -87,6 +87,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE8EEF5"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -124,7 +129,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -236,6 +241,36 @@
     <x:xf numFmtId="203" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -246,7 +281,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -256,7 +291,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -4677,8 +4712,8 @@
       <x:c r="O92" s="30"/>
       <x:c r="P92" s="30"/>
     </x:row>
-    <x:row r="95" ht="23" customHeight="1">
-      <x:c r="A95" s="42" t="str">
+    <x:row r="95" ht="15" customHeight="1">
+      <x:c r="A95" s="40" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B95" s="30"/>
@@ -4693,7 +4728,7 @@
       <x:c r="K95" s="30"/>
       <x:c r="L95" s="30"/>
     </x:row>
-    <x:row r="96" ht="23" customHeight="1">
+    <x:row r="96" ht="15" customHeight="1">
       <x:c r="A96" s="30" t="str">
         <x:v>Prefill 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -4709,29 +4744,29 @@
       <x:c r="K96" s="30"/>
       <x:c r="L96" s="30"/>
     </x:row>
-    <x:row r="97" ht="38" customHeight="1">
-      <x:c r="A97" s="45" t="str">
+    <x:row r="97" ht="30" customHeight="1">
+      <x:c r="A97" s="62" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B97" s="45" t="str">
+      <x:c r="B97" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C97" s="45" t="str">
+      <x:c r="C97" s="62" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D97" s="45" t="str">
+      <x:c r="D97" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E97" s="45" t="str">
+      <x:c r="E97" s="62" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F97" s="45" t="str">
+      <x:c r="F97" s="62" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G97" s="45" t="str">
+      <x:c r="G97" s="62" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H97" s="45" t="str">
+      <x:c r="H97" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I97" s="30"/>
@@ -4739,19 +4774,19 @@
       <x:c r="K97" s="30"/>
       <x:c r="L97" s="30"/>
     </x:row>
-    <x:row r="98" ht="23" customHeight="1">
+    <x:row r="98" ht="15" customHeight="1">
       <x:c r="A98" s="30"/>
-      <x:c r="B98" s="47" t="n">
+      <x:c r="B98" s="63" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C98" s="30"/>
-      <x:c r="D98" s="47" t="n">
+      <x:c r="D98" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E98" s="30"/>
-      <x:c r="F98" s="48"/>
+      <x:c r="F98" s="38"/>
       <x:c r="G98" s="30"/>
-      <x:c r="H98" s="48" t="n">
+      <x:c r="H98" s="36" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I98" s="30"/>
@@ -4759,45 +4794,45 @@
       <x:c r="K98" s="30"/>
       <x:c r="L98" s="30"/>
     </x:row>
-    <x:row r="99" ht="38" customHeight="1">
-      <x:c r="A99" s="45" t="str">
+    <x:row r="99" ht="30" customHeight="1">
+      <x:c r="A99" s="62" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B99" s="45" t="str">
+      <x:c r="B99" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C99" s="45" t="str">
+      <x:c r="C99" s="62" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D99" s="45" t="str">
+      <x:c r="D99" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E99" s="45" t="str">
+      <x:c r="E99" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F99" s="45" t="str">
+      <x:c r="F99" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G99" s="45" t="str">
+      <x:c r="G99" s="62" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H99" s="45" t="str">
+      <x:c r="H99" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I99" s="45" t="str">
+      <x:c r="I99" s="62" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J99" s="45" t="str">
+      <x:c r="J99" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K99" s="45" t="str">
+      <x:c r="K99" s="62" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L99" s="45" t="str">
+      <x:c r="L99" s="62" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="23" customHeight="1">
+    <x:row r="100" ht="15" customHeight="1">
       <x:c r="A100" s="49"/>
       <x:c r="B100" s="49" t="n">
         <x:f>SUM(G104:G131)</x:f>
@@ -4827,7 +4862,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="23" customHeight="1">
+    <x:row r="101" ht="15" customHeight="1">
       <x:c r="A101" s="30" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -4843,7 +4878,7 @@
       <x:c r="K101" s="30"/>
       <x:c r="L101" s="30"/>
     </x:row>
-    <x:row r="102" ht="23" customHeight="1">
+    <x:row r="102" ht="15" customHeight="1">
       <x:c r="A102" s="30" t="str">
         <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
       </x:c>
@@ -4859,45 +4894,45 @@
       <x:c r="K102" s="30"/>
       <x:c r="L102" s="30"/>
     </x:row>
-    <x:row r="103" ht="38" customHeight="1">
-      <x:c r="A103" s="45" t="str">
+    <x:row r="103" ht="30" customHeight="1">
+      <x:c r="A103" s="62" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B103" s="45" t="str">
+      <x:c r="B103" s="62" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C103" s="45" t="str">
+      <x:c r="C103" s="62" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D103" s="45" t="str">
+      <x:c r="D103" s="62" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E103" s="45" t="str">
+      <x:c r="E103" s="62" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F103" s="45" t="str">
+      <x:c r="F103" s="62" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G103" s="45" t="str">
+      <x:c r="G103" s="62" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H103" s="45" t="str">
+      <x:c r="H103" s="62" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I103" s="45" t="str">
+      <x:c r="I103" s="62" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J103" s="45" t="str">
+      <x:c r="J103" s="62" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K103" s="45" t="str">
+      <x:c r="K103" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L103" s="45" t="str">
+      <x:c r="L103" s="62" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="23" customHeight="1">
+    <x:row r="104" ht="15" customHeight="1">
       <x:c r="A104" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -4911,11 +4946,11 @@
         <x:f>(K65*2^20)/1e9</x:f>
         <x:v>0.205520896</x:v>
       </x:c>
-      <x:c r="E104" s="51" t="n">
+      <x:c r="E104" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F104" s="52" t="n">
+      <x:c r="F104" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G104" s="34" t="n">
@@ -4930,7 +4965,7 @@
         <x:f>G104*F104*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0.22835655111111114</x:v>
       </x:c>
-      <x:c r="J104" s="52" t="n">
+      <x:c r="J104" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K104" s="34" t="n">
@@ -4941,7 +4976,7 @@
         <x:v>原通信行 65</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="23" customHeight="1">
+    <x:row r="105" ht="15" customHeight="1">
       <x:c r="A105" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -4955,11 +4990,11 @@
         <x:f>(K66*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E105" s="51" t="n">
+      <x:c r="E105" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F105" s="52" t="n">
+      <x:c r="F105" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G105" s="34" t="n">
@@ -4974,7 +5009,7 @@
         <x:f>G105*F105*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J105" s="52" t="n">
+      <x:c r="J105" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K105" s="34" t="n">
@@ -4985,7 +5020,7 @@
         <x:v>原通信行 66</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="23" customHeight="1">
+    <x:row r="106" ht="15" customHeight="1">
       <x:c r="A106" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -4999,11 +5034,11 @@
         <x:f>(K67*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E106" s="51" t="n">
+      <x:c r="E106" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F106" s="52" t="n">
+      <x:c r="F106" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G106" s="34" t="n">
@@ -5018,7 +5053,7 @@
         <x:f>G106*F106*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J106" s="52" t="n">
+      <x:c r="J106" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K106" s="34" t="n">
@@ -5029,7 +5064,7 @@
         <x:v>原通信行 67</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="23" customHeight="1">
+    <x:row r="107" ht="15" customHeight="1">
       <x:c r="A107" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -5043,11 +5078,11 @@
         <x:f>(K68*2^20)/1e9</x:f>
         <x:v>9.556721664</x:v>
       </x:c>
-      <x:c r="E107" s="51" t="n">
+      <x:c r="E107" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F107" s="52" t="n">
+      <x:c r="F107" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G107" s="34" t="n">
@@ -5062,7 +5097,7 @@
         <x:f>G107*F107*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>10.618579626666666</x:v>
       </x:c>
-      <x:c r="J107" s="52" t="n">
+      <x:c r="J107" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K107" s="34" t="n">
@@ -5073,7 +5108,7 @@
         <x:v>原通信行 68</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="23" customHeight="1">
+    <x:row r="108" ht="15" customHeight="1">
       <x:c r="A108" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -5087,11 +5122,11 @@
         <x:f>(K69*2^20)/1e9</x:f>
         <x:v>9.556721664</x:v>
       </x:c>
-      <x:c r="E108" s="51" t="n">
+      <x:c r="E108" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F108" s="52" t="n">
+      <x:c r="F108" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G108" s="34" t="n">
@@ -5106,7 +5141,7 @@
         <x:f>G108*F108*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>10.618579626666666</x:v>
       </x:c>
-      <x:c r="J108" s="52" t="n">
+      <x:c r="J108" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K108" s="34" t="n">
@@ -5117,7 +5152,7 @@
         <x:v>原通信行 69</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="23" customHeight="1">
+    <x:row r="109" ht="15" customHeight="1">
       <x:c r="A109" s="30" t="str">
         <x:v>O Proj TP</x:v>
       </x:c>
@@ -5131,11 +5166,11 @@
         <x:f>(K70*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E109" s="51" t="n">
+      <x:c r="E109" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F109" s="52" t="n">
+      <x:c r="F109" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G109" s="34" t="n">
@@ -5150,7 +5185,7 @@
         <x:f>G109*F109*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J109" s="52" t="n">
+      <x:c r="J109" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K109" s="34" t="n">
@@ -5161,7 +5196,7 @@
         <x:v>原通信行 70</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="23" customHeight="1">
+    <x:row r="110" ht="15" customHeight="1">
       <x:c r="A110" s="30" t="str">
         <x:v>Fine O TP</x:v>
       </x:c>
@@ -5175,11 +5210,11 @@
         <x:f>(K71*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E110" s="51" t="n">
+      <x:c r="E110" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F110" s="52" t="n">
+      <x:c r="F110" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G110" s="34" t="n">
@@ -5194,7 +5229,7 @@
         <x:f>G110*F110*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J110" s="52" t="n">
+      <x:c r="J110" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K110" s="34" t="n">
@@ -5205,7 +5240,7 @@
         <x:v>原通信行 71</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="23" customHeight="1">
+    <x:row r="111" ht="15" customHeight="1">
       <x:c r="A111" s="30" t="str">
         <x:v>Fine O TP</x:v>
       </x:c>
@@ -5219,11 +5254,11 @@
         <x:f>(K72*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E111" s="51" t="n">
+      <x:c r="E111" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F111" s="52" t="n">
+      <x:c r="F111" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G111" s="34" t="n">
@@ -5238,7 +5273,7 @@
         <x:f>G111*F111*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J111" s="52" t="n">
+      <x:c r="J111" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K111" s="34" t="n">
@@ -5249,7 +5284,7 @@
         <x:v>原通信行 72</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="23" customHeight="1">
+    <x:row r="112" ht="15" customHeight="1">
       <x:c r="A112" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -5263,11 +5298,11 @@
         <x:f>(K73*2^20)/1e9</x:f>
         <x:v>0.025690112</x:v>
       </x:c>
-      <x:c r="E112" s="51" t="n">
+      <x:c r="E112" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F112" s="52" t="n">
+      <x:c r="F112" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G112" s="34" t="n">
@@ -5282,7 +5317,7 @@
         <x:f>G112*F112*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0.028544568888888892</x:v>
       </x:c>
-      <x:c r="J112" s="52" t="n">
+      <x:c r="J112" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K112" s="34" t="n">
@@ -5293,7 +5328,7 @@
         <x:v>原通信行 73</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="23" customHeight="1">
+    <x:row r="113" ht="15" customHeight="1">
       <x:c r="A113" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -5307,11 +5342,11 @@
         <x:f>(K74*2^20)/1e9</x:f>
         <x:v>18.907922432</x:v>
       </x:c>
-      <x:c r="E113" s="51" t="n">
+      <x:c r="E113" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F113" s="52" t="n">
+      <x:c r="F113" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G113" s="34" t="n">
@@ -5326,7 +5361,7 @@
         <x:f>G113*F113*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>21.008802702222223</x:v>
       </x:c>
-      <x:c r="J113" s="52" t="n">
+      <x:c r="J113" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K113" s="34" t="n">
@@ -5337,7 +5372,7 @@
         <x:v>原通信行 74</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="23" customHeight="1">
+    <x:row r="114" ht="15" customHeight="1">
       <x:c r="A114" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -5351,11 +5386,11 @@
         <x:f>(K75*2^20)/1e9</x:f>
         <x:v>18.907922432</x:v>
       </x:c>
-      <x:c r="E114" s="51" t="n">
+      <x:c r="E114" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F114" s="52" t="n">
+      <x:c r="F114" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G114" s="34" t="n">
@@ -5370,7 +5405,7 @@
         <x:f>G114*F114*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>21.008802702222223</x:v>
       </x:c>
-      <x:c r="J114" s="52" t="n">
+      <x:c r="J114" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K114" s="34" t="n">
@@ -5381,7 +5416,7 @@
         <x:v>原通信行 75</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="23" customHeight="1">
+    <x:row r="115" ht="15" customHeight="1">
       <x:c r="A115" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -5395,11 +5430,11 @@
         <x:f>(K76*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E115" s="51" t="n">
+      <x:c r="E115" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F115" s="52" t="n">
+      <x:c r="F115" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G115" s="34" t="n">
@@ -5414,7 +5449,7 @@
         <x:f>G115*F115*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J115" s="52" t="n">
+      <x:c r="J115" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K115" s="34" t="n">
@@ -5425,7 +5460,7 @@
         <x:v>原通信行 76</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="23" customHeight="1">
+    <x:row r="116" ht="15" customHeight="1">
       <x:c r="A116" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -5439,11 +5474,11 @@
         <x:f>(K77*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E116" s="51" t="n">
+      <x:c r="E116" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F116" s="52" t="n">
+      <x:c r="F116" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G116" s="34" t="n">
@@ -5458,7 +5493,7 @@
         <x:f>G116*F116*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J116" s="52" t="n">
+      <x:c r="J116" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K116" s="34" t="n">
@@ -5469,7 +5504,7 @@
         <x:v>原通信行 77</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="23" customHeight="1">
+    <x:row r="117" ht="15" customHeight="1">
       <x:c r="A117" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -5483,11 +5518,11 @@
         <x:f>(K78*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E117" s="51" t="n">
+      <x:c r="E117" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F117" s="52" t="n">
+      <x:c r="F117" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G117" s="34" t="n">
@@ -5502,7 +5537,7 @@
         <x:f>G117*F117*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J117" s="52" t="n">
+      <x:c r="J117" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K117" s="34" t="n">
@@ -5513,7 +5548,7 @@
         <x:v>原通信行 78</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="23" customHeight="1">
+    <x:row r="118" ht="15" customHeight="1">
       <x:c r="A118" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -5527,11 +5562,11 @@
         <x:f>(K79*2^20)/1e9</x:f>
         <x:v>9.453961216</x:v>
       </x:c>
-      <x:c r="E118" s="51" t="n">
+      <x:c r="E118" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F118" s="52" t="n">
+      <x:c r="F118" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G118" s="34" t="n">
@@ -5546,7 +5581,7 @@
         <x:f>G118*F118*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>10.504401351111111</x:v>
       </x:c>
-      <x:c r="J118" s="52" t="n">
+      <x:c r="J118" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K118" s="34" t="n">
@@ -5557,7 +5592,7 @@
         <x:v>原通信行 79</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="23" customHeight="1">
+    <x:row r="119" ht="15" customHeight="1">
       <x:c r="A119" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -5571,11 +5606,11 @@
         <x:f>(K80*2^20)/1e9</x:f>
         <x:v>9.453961216</x:v>
       </x:c>
-      <x:c r="E119" s="51" t="n">
+      <x:c r="E119" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F119" s="52" t="n">
+      <x:c r="F119" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G119" s="34" t="n">
@@ -5590,7 +5625,7 @@
         <x:f>G119*F119*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>10.504401351111111</x:v>
       </x:c>
-      <x:c r="J119" s="52" t="n">
+      <x:c r="J119" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K119" s="34" t="n">
@@ -5601,7 +5636,7 @@
         <x:v>原通信行 80</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="23" customHeight="1">
+    <x:row r="120" ht="15" customHeight="1">
       <x:c r="A120" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -5615,11 +5650,11 @@
         <x:f>(K81*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E120" s="51" t="n">
+      <x:c r="E120" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F120" s="52" t="n">
+      <x:c r="F120" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G120" s="34" t="n">
@@ -5634,7 +5669,7 @@
         <x:f>G120*F120*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J120" s="52" t="n">
+      <x:c r="J120" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K120" s="34" t="n">
@@ -5645,7 +5680,7 @@
         <x:v>原通信行 81</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="23" customHeight="1">
+    <x:row r="121" ht="15" customHeight="1">
       <x:c r="A121" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -5659,11 +5694,11 @@
         <x:f>(K82*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E121" s="51" t="n">
+      <x:c r="E121" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F121" s="52" t="n">
+      <x:c r="F121" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G121" s="34" t="n">
@@ -5678,7 +5713,7 @@
         <x:f>G121*F121*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J121" s="52" t="n">
+      <x:c r="J121" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K121" s="34" t="n">
@@ -5689,7 +5724,7 @@
         <x:v>原通信行 82</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="23" customHeight="1">
+    <x:row r="122" ht="15" customHeight="1">
       <x:c r="A122" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -5703,11 +5738,11 @@
         <x:f>(K83*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E122" s="51" t="n">
+      <x:c r="E122" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F122" s="52" t="n">
+      <x:c r="F122" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G122" s="34" t="n">
@@ -5722,7 +5757,7 @@
         <x:f>G122*F122*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J122" s="52" t="n">
+      <x:c r="J122" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K122" s="34" t="n">
@@ -5733,7 +5768,7 @@
         <x:v>原通信行 83</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="23" customHeight="1">
+    <x:row r="123" ht="15" customHeight="1">
       <x:c r="A123" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -5747,11 +5782,11 @@
         <x:f>(K84*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E123" s="51" t="n">
+      <x:c r="E123" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F123" s="52" t="n">
+      <x:c r="F123" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G123" s="34" t="n">
@@ -5766,7 +5801,7 @@
         <x:f>G123*F123*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J123" s="52" t="n">
+      <x:c r="J123" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K123" s="34" t="n">
@@ -5777,7 +5812,7 @@
         <x:v>原通信行 84</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="23" customHeight="1">
+    <x:row r="124" ht="15" customHeight="1">
       <x:c r="A124" s="30" t="str">
         <x:v>PCP</x:v>
       </x:c>
@@ -5791,11 +5826,11 @@
         <x:f>(K85*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E124" s="51" t="n">
+      <x:c r="E124" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F124" s="52" t="n">
+      <x:c r="F124" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G124" s="34" t="n">
@@ -5810,7 +5845,7 @@
         <x:f>G124*F124*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J124" s="52" t="n">
+      <x:c r="J124" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K124" s="34" t="n">
@@ -5821,7 +5856,7 @@
         <x:v>原通信行 85</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="23" customHeight="1">
+    <x:row r="125" ht="15" customHeight="1">
       <x:c r="A125" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -5835,11 +5870,11 @@
         <x:f>(K86*2^20)/1e9</x:f>
         <x:v>0.102760448</x:v>
       </x:c>
-      <x:c r="E125" s="51" t="n">
+      <x:c r="E125" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F125" s="52" t="n">
+      <x:c r="F125" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G125" s="34" t="n">
@@ -5854,7 +5889,7 @@
         <x:f>G125*F125*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0.11417827555555557</x:v>
       </x:c>
-      <x:c r="J125" s="52" t="n">
+      <x:c r="J125" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K125" s="34" t="n">
@@ -5865,7 +5900,7 @@
         <x:v>原通信行 86</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="23" customHeight="1">
+    <x:row r="126" ht="15" customHeight="1">
       <x:c r="A126" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -5879,11 +5914,11 @@
         <x:f>(K87*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E126" s="51" t="n">
+      <x:c r="E126" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F126" s="52" t="n">
+      <x:c r="F126" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G126" s="34" t="n">
@@ -5898,7 +5933,7 @@
         <x:f>G126*F126*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J126" s="52" t="n">
+      <x:c r="J126" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K126" s="34" t="n">
@@ -5909,7 +5944,7 @@
         <x:v>原通信行 87</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="23" customHeight="1">
+    <x:row r="127" ht="15" customHeight="1">
       <x:c r="A127" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -5923,11 +5958,11 @@
         <x:f>(K88*2^20)/1e9</x:f>
         <x:v>0.001376256</x:v>
       </x:c>
-      <x:c r="E127" s="51" t="n">
+      <x:c r="E127" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F127" s="52" t="n">
+      <x:c r="F127" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G127" s="34" t="n">
@@ -5942,7 +5977,7 @@
         <x:f>G127*F127*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0.0015291733333333336</x:v>
       </x:c>
-      <x:c r="J127" s="52" t="n">
+      <x:c r="J127" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K127" s="34" t="n">
@@ -5953,7 +5988,7 @@
         <x:v>原通信行 88</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="23" customHeight="1">
+    <x:row r="128" ht="15" customHeight="1">
       <x:c r="A128" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -5967,11 +6002,11 @@
         <x:f>(K89*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E128" s="51" t="n">
+      <x:c r="E128" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F128" s="52" t="n">
+      <x:c r="F128" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G128" s="34" t="n">
@@ -5986,7 +6021,7 @@
         <x:f>G128*F128*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J128" s="52" t="n">
+      <x:c r="J128" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K128" s="34" t="n">
@@ -5997,7 +6032,7 @@
         <x:v>原通信行 89</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="23" customHeight="1">
+    <x:row r="129" ht="15" customHeight="1">
       <x:c r="A129" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -6011,11 +6046,11 @@
         <x:f>(K90*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E129" s="51" t="n">
+      <x:c r="E129" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F129" s="52" t="n">
+      <x:c r="F129" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G129" s="34" t="n">
@@ -6030,7 +6065,7 @@
         <x:f>G129*F129*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J129" s="52" t="n">
+      <x:c r="J129" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K129" s="34" t="n">
@@ -6041,7 +6076,7 @@
         <x:v>原通信行 90</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="23" customHeight="1">
+    <x:row r="130" ht="15" customHeight="1">
       <x:c r="A130" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -6055,11 +6090,11 @@
         <x:f>(K91*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E130" s="51" t="n">
+      <x:c r="E130" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F130" s="52" t="n">
+      <x:c r="F130" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G130" s="34" t="n">
@@ -6074,7 +6109,7 @@
         <x:f>G130*F130*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J130" s="52" t="n">
+      <x:c r="J130" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K130" s="34" t="n">
@@ -6085,7 +6120,7 @@
         <x:v>原通信行 91</x:v>
       </x:c>
     </x:row>
-    <x:row r="131" ht="23" customHeight="1">
+    <x:row r="131" ht="15" customHeight="1">
       <x:c r="A131" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -6099,11 +6134,11 @@
         <x:f>(IF(E74=0,0,H74*ROUNDUP(896/G74,0)*G74*4*(G74-1)))/1e9</x:f>
         <x:v>0.002308096</x:v>
       </x:c>
-      <x:c r="E131" s="51" t="n">
+      <x:c r="E131" s="64" t="n">
         <x:f>$H$98</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F131" s="52" t="n">
+      <x:c r="F131" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G131" s="34" t="n">
@@ -6118,7 +6153,7 @@
         <x:f>G131*F131*$D$98*$B$98/(1-$B$98)</x:f>
         <x:v>0.002564551111111111</x:v>
       </x:c>
-      <x:c r="J131" s="52" t="n">
+      <x:c r="J131" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K131" s="34" t="n">
@@ -6129,36 +6164,36 @@
         <x:v>额外控制量</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="23" customHeight="1">
-      <x:c r="A132" s="53" t="str">
+    <x:row r="132" ht="15" customHeight="1">
+      <x:c r="A132" s="40" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B132" s="53"/>
-      <x:c r="C132" s="53"/>
-      <x:c r="D132" s="54" t="n">
+      <x:c r="B132" s="40"/>
+      <x:c r="C132" s="40"/>
+      <x:c r="D132" s="41" t="n">
         <x:f>SUM(D104:D131)</x:f>
         <x:v>76.17486643199999</x:v>
       </x:c>
-      <x:c r="E132" s="54"/>
-      <x:c r="F132" s="53"/>
-      <x:c r="G132" s="54" t="n">
+      <x:c r="E132" s="40"/>
+      <x:c r="F132" s="40"/>
+      <x:c r="G132" s="41" t="n">
         <x:f>SUM(G104:G131)</x:f>
         <x:v>761.74866432</x:v>
       </x:c>
-      <x:c r="H132" s="54" t="n">
+      <x:c r="H132" s="41" t="n">
         <x:f>SUM(H104:H131)</x:f>
         <x:v>846.3874048</x:v>
       </x:c>
-      <x:c r="I132" s="54" t="n">
+      <x:c r="I132" s="41" t="n">
         <x:f>SUM(I104:I131)</x:f>
         <x:v>84.63874048000001</x:v>
       </x:c>
-      <x:c r="J132" s="53"/>
-      <x:c r="K132" s="54" t="n">
+      <x:c r="J132" s="40"/>
+      <x:c r="K132" s="41" t="n">
         <x:f>SUM(K104:K131)</x:f>
         <x:v>84.63874048000001</x:v>
       </x:c>
-      <x:c r="L132" s="53"/>
+      <x:c r="L132" s="40"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="L100:L100">
@@ -10339,8 +10374,8 @@
       <x:c r="O91" s="30"/>
       <x:c r="P91" s="30"/>
     </x:row>
-    <x:row r="94" ht="23" customHeight="1">
-      <x:c r="A94" s="42" t="str">
+    <x:row r="94" ht="15" customHeight="1">
+      <x:c r="A94" s="40" t="str">
         <x:v>PD 带宽争用耗时评估</x:v>
       </x:c>
       <x:c r="B94" s="30"/>
@@ -10355,7 +10390,7 @@
       <x:c r="K94" s="30"/>
       <x:c r="L94" s="30"/>
     </x:row>
-    <x:row r="95" ht="23" customHeight="1">
+    <x:row r="95" ht="15" customHeight="1">
       <x:c r="A95" s="30" t="str">
         <x:v>Decode 当前表参数；100 GB/s 为归一化示例。所列事件的带宽项，不等于完整 forward 耗时。</x:v>
       </x:c>
@@ -10371,29 +10406,29 @@
       <x:c r="K95" s="30"/>
       <x:c r="L95" s="30"/>
     </x:row>
-    <x:row r="96" ht="38" customHeight="1">
-      <x:c r="A96" s="45" t="str">
+    <x:row r="96" ht="30" customHeight="1">
+      <x:c r="A96" s="62" t="str">
         <x:v>带宽降幅</x:v>
       </x:c>
-      <x:c r="B96" s="45" t="str">
+      <x:c r="B96" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="C96" s="45" t="str">
+      <x:c r="C96" s="62" t="str">
         <x:v>争用覆盖率</x:v>
       </x:c>
-      <x:c r="D96" s="45" t="str">
+      <x:c r="D96" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
-      <x:c r="E96" s="45" t="str">
+      <x:c r="E96" s="62" t="str">
         <x:v>基线 forward ms</x:v>
       </x:c>
-      <x:c r="F96" s="45" t="str">
+      <x:c r="F96" s="62" t="str">
         <x:v>实测输入</x:v>
       </x:c>
-      <x:c r="G96" s="45" t="str">
+      <x:c r="G96" s="62" t="str">
         <x:v>默认带宽 GB/s</x:v>
       </x:c>
-      <x:c r="H96" s="45" t="str">
+      <x:c r="H96" s="62" t="str">
         <x:v>输入</x:v>
       </x:c>
       <x:c r="I96" s="30"/>
@@ -10401,19 +10436,19 @@
       <x:c r="K96" s="30"/>
       <x:c r="L96" s="30"/>
     </x:row>
-    <x:row r="97" ht="23" customHeight="1">
+    <x:row r="97" ht="15" customHeight="1">
       <x:c r="A97" s="30"/>
-      <x:c r="B97" s="47" t="n">
+      <x:c r="B97" s="63" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C97" s="30"/>
-      <x:c r="D97" s="47" t="n">
+      <x:c r="D97" s="63" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="E97" s="30"/>
-      <x:c r="F97" s="48"/>
+      <x:c r="F97" s="38"/>
       <x:c r="G97" s="30"/>
-      <x:c r="H97" s="48" t="n">
+      <x:c r="H97" s="36" t="n">
         <x:v>100</x:v>
       </x:c>
       <x:c r="I97" s="30"/>
@@ -10421,45 +10456,45 @@
       <x:c r="K97" s="30"/>
       <x:c r="L97" s="30"/>
     </x:row>
-    <x:row r="98" ht="38" customHeight="1">
-      <x:c r="A98" s="45" t="str">
+    <x:row r="98" ht="30" customHeight="1">
+      <x:c r="A98" s="62" t="str">
         <x:v>通信基线 ms</x:v>
       </x:c>
-      <x:c r="B98" s="45" t="str">
+      <x:c r="B98" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="C98" s="45" t="str">
+      <x:c r="C98" s="62" t="str">
         <x:v>通信争用后 ms</x:v>
       </x:c>
-      <x:c r="D98" s="45" t="str">
+      <x:c r="D98" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="E98" s="45" t="str">
+      <x:c r="E98" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="F98" s="45" t="str">
+      <x:c r="F98" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="G98" s="45" t="str">
+      <x:c r="G98" s="62" t="str">
         <x:v>forward 新耗时 ms</x:v>
       </x:c>
-      <x:c r="H98" s="45" t="str">
+      <x:c r="H98" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="I98" s="45" t="str">
+      <x:c r="I98" s="62" t="str">
         <x:v>forward 增幅</x:v>
       </x:c>
-      <x:c r="J98" s="45" t="str">
+      <x:c r="J98" s="62" t="str">
         <x:v>结果</x:v>
       </x:c>
-      <x:c r="K98" s="45" t="str">
+      <x:c r="K98" s="62" t="str">
         <x:v>输入状态</x:v>
       </x:c>
-      <x:c r="L98" s="45" t="str">
+      <x:c r="L98" s="62" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="23" customHeight="1">
+    <x:row r="99" ht="15" customHeight="1">
       <x:c r="A99" s="49"/>
       <x:c r="B99" s="49" t="n">
         <x:f>SUM(G103:G129)</x:f>
@@ -10489,7 +10524,7 @@
         <x:v>待填基线</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="23" customHeight="1">
+    <x:row r="100" ht="15" customHeight="1">
       <x:c r="A100" s="30" t="str">
         <x:v>共享比例=0 表示独立链路；暴露系数=0 表示增量完全隐藏。默认均为 1，降幅只作用于带宽项。</x:v>
       </x:c>
@@ -10505,7 +10540,7 @@
       <x:c r="K100" s="30"/>
       <x:c r="L100" s="30"/>
     </x:row>
-    <x:row r="101" ht="23" customHeight="1">
+    <x:row r="101" ht="15" customHeight="1">
       <x:c r="A101" s="30" t="str">
         <x:v>P: AllToAllV + 4 B 计数 Ring；D: A3 BF16 MC2 FullMesh。每事件带宽按端点发送量定义。</x:v>
       </x:c>
@@ -10521,45 +10556,45 @@
       <x:c r="K101" s="30"/>
       <x:c r="L101" s="30"/>
     </x:row>
-    <x:row r="102" ht="38" customHeight="1">
-      <x:c r="A102" s="45" t="str">
+    <x:row r="102" ht="30" customHeight="1">
+      <x:c r="A102" s="62" t="str">
         <x:v>并行域</x:v>
       </x:c>
-      <x:c r="B102" s="45" t="str">
+      <x:c r="B102" s="62" t="str">
         <x:v>模块</x:v>
       </x:c>
-      <x:c r="C102" s="45" t="str">
+      <x:c r="C102" s="62" t="str">
         <x:v>通信事件</x:v>
       </x:c>
-      <x:c r="D102" s="45" t="str">
+      <x:c r="D102" s="62" t="str">
         <x:v>GB/Rank/Step</x:v>
       </x:c>
-      <x:c r="E102" s="45" t="str">
+      <x:c r="E102" s="62" t="str">
         <x:v>有效带宽 GB/s</x:v>
       </x:c>
-      <x:c r="F102" s="45" t="str">
+      <x:c r="F102" s="62" t="str">
         <x:v>共享比例</x:v>
       </x:c>
-      <x:c r="G102" s="45" t="str">
+      <x:c r="G102" s="62" t="str">
         <x:v>基线带宽项 ms</x:v>
       </x:c>
-      <x:c r="H102" s="45" t="str">
+      <x:c r="H102" s="62" t="str">
         <x:v>争用后带宽项 ms</x:v>
       </x:c>
-      <x:c r="I102" s="45" t="str">
+      <x:c r="I102" s="62" t="str">
         <x:v>通信增量 ms</x:v>
       </x:c>
-      <x:c r="J102" s="45" t="str">
+      <x:c r="J102" s="62" t="str">
         <x:v>暴露系数</x:v>
       </x:c>
-      <x:c r="K102" s="45" t="str">
+      <x:c r="K102" s="62" t="str">
         <x:v>forward 增量 ms</x:v>
       </x:c>
-      <x:c r="L102" s="45" t="str">
+      <x:c r="L102" s="62" t="str">
         <x:v>公式口径</x:v>
       </x:c>
     </x:row>
-    <x:row r="103" ht="23" customHeight="1">
+    <x:row r="103" ht="15" customHeight="1">
       <x:c r="A103" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -10573,11 +10608,11 @@
         <x:f>(K65*2^20)/1e9</x:f>
         <x:v>0.025690112</x:v>
       </x:c>
-      <x:c r="E103" s="51" t="n">
+      <x:c r="E103" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F103" s="52" t="n">
+      <x:c r="F103" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G103" s="34" t="n">
@@ -10592,7 +10627,7 @@
         <x:f>G103*F103*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0.028544568888888892</x:v>
       </x:c>
-      <x:c r="J103" s="52" t="n">
+      <x:c r="J103" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K103" s="34" t="n">
@@ -10603,7 +10638,7 @@
         <x:v>原通信行 65</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="23" customHeight="1">
+    <x:row r="104" ht="15" customHeight="1">
       <x:c r="A104" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -10617,11 +10652,11 @@
         <x:f>(K66*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E104" s="51" t="n">
+      <x:c r="E104" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F104" s="52" t="n">
+      <x:c r="F104" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G104" s="34" t="n">
@@ -10636,7 +10671,7 @@
         <x:f>G104*F104*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J104" s="52" t="n">
+      <x:c r="J104" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K104" s="34" t="n">
@@ -10647,7 +10682,7 @@
         <x:v>原通信行 66</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="23" customHeight="1">
+    <x:row r="105" ht="15" customHeight="1">
       <x:c r="A105" s="30" t="str">
         <x:v>Embedding TP</x:v>
       </x:c>
@@ -10661,11 +10696,11 @@
         <x:f>(K67*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E105" s="51" t="n">
+      <x:c r="E105" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F105" s="52" t="n">
+      <x:c r="F105" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G105" s="34" t="n">
@@ -10680,7 +10715,7 @@
         <x:f>G105*F105*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J105" s="52" t="n">
+      <x:c r="J105" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K105" s="34" t="n">
@@ -10691,7 +10726,7 @@
         <x:v>原通信行 67</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="23" customHeight="1">
+    <x:row r="106" ht="15" customHeight="1">
       <x:c r="A106" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -10705,11 +10740,11 @@
         <x:f>(K68*2^20)/1e9</x:f>
         <x:v>1.194590208</x:v>
       </x:c>
-      <x:c r="E106" s="51" t="n">
+      <x:c r="E106" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F106" s="52" t="n">
+      <x:c r="F106" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G106" s="34" t="n">
@@ -10724,7 +10759,7 @@
         <x:f>G106*F106*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>1.3273224533333332</x:v>
       </x:c>
-      <x:c r="J106" s="52" t="n">
+      <x:c r="J106" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K106" s="34" t="n">
@@ -10735,7 +10770,7 @@
         <x:v>原通信行 68</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="23" customHeight="1">
+    <x:row r="107" ht="15" customHeight="1">
       <x:c r="A107" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -10749,11 +10784,11 @@
         <x:f>(K69*2^20)/1e9</x:f>
         <x:v>1.194590208</x:v>
       </x:c>
-      <x:c r="E107" s="51" t="n">
+      <x:c r="E107" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F107" s="52" t="n">
+      <x:c r="F107" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G107" s="34" t="n">
@@ -10768,7 +10803,7 @@
         <x:f>G107*F107*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>1.3273224533333332</x:v>
       </x:c>
-      <x:c r="J107" s="52" t="n">
+      <x:c r="J107" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K107" s="34" t="n">
@@ -10779,7 +10814,7 @@
         <x:v>原通信行 69</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="23" customHeight="1">
+    <x:row r="108" ht="15" customHeight="1">
       <x:c r="A108" s="30" t="str">
         <x:v>O Proj TP</x:v>
       </x:c>
@@ -10793,11 +10828,11 @@
         <x:f>(K70*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E108" s="51" t="n">
+      <x:c r="E108" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F108" s="52" t="n">
+      <x:c r="F108" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G108" s="34" t="n">
@@ -10812,7 +10847,7 @@
         <x:f>G108*F108*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J108" s="52" t="n">
+      <x:c r="J108" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K108" s="34" t="n">
@@ -10823,7 +10858,7 @@
         <x:v>原通信行 70</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="23" customHeight="1">
+    <x:row r="109" ht="15" customHeight="1">
       <x:c r="A109" s="30" t="str">
         <x:v>Fine O TP</x:v>
       </x:c>
@@ -10837,11 +10872,11 @@
         <x:f>(K71*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E109" s="51" t="n">
+      <x:c r="E109" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F109" s="52" t="n">
+      <x:c r="F109" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G109" s="34" t="n">
@@ -10856,7 +10891,7 @@
         <x:f>G109*F109*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J109" s="52" t="n">
+      <x:c r="J109" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K109" s="34" t="n">
@@ -10867,7 +10902,7 @@
         <x:v>原通信行 71</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="23" customHeight="1">
+    <x:row r="110" ht="15" customHeight="1">
       <x:c r="A110" s="30" t="str">
         <x:v>Fine O TP</x:v>
       </x:c>
@@ -10881,11 +10916,11 @@
         <x:f>(K72*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E110" s="51" t="n">
+      <x:c r="E110" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F110" s="52" t="n">
+      <x:c r="F110" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G110" s="34" t="n">
@@ -10900,7 +10935,7 @@
         <x:f>G110*F110*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J110" s="52" t="n">
+      <x:c r="J110" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K110" s="34" t="n">
@@ -10911,7 +10946,7 @@
         <x:v>原通信行 72</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="23" customHeight="1">
+    <x:row r="111" ht="15" customHeight="1">
       <x:c r="A111" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -10925,11 +10960,11 @@
         <x:f>(K73*2^20)/1e9</x:f>
         <x:v>0.003211264</x:v>
       </x:c>
-      <x:c r="E111" s="51" t="n">
+      <x:c r="E111" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F111" s="52" t="n">
+      <x:c r="F111" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G111" s="34" t="n">
@@ -10944,7 +10979,7 @@
         <x:f>G111*F111*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0.0035680711111111115</x:v>
       </x:c>
-      <x:c r="J111" s="52" t="n">
+      <x:c r="J111" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K111" s="34" t="n">
@@ -10955,7 +10990,7 @@
         <x:v>原通信行 73</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="23" customHeight="1">
+    <x:row r="112" ht="15" customHeight="1">
       <x:c r="A112" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -10969,11 +11004,11 @@
         <x:f>(IF(F74=2,E74/7168*H74*(ROUNDUP((ROUNDUP(7168*F74/32,0)*32+32)/480,0)*512),NA()))/1e9</x:f>
         <x:v>2.53231104</x:v>
       </x:c>
-      <x:c r="E112" s="51" t="n">
+      <x:c r="E112" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F112" s="52" t="n">
+      <x:c r="F112" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G112" s="34" t="n">
@@ -10988,7 +11023,7 @@
         <x:f>G112*F112*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>2.8136789333333336</x:v>
       </x:c>
-      <x:c r="J112" s="52" t="n">
+      <x:c r="J112" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K112" s="34" t="n">
@@ -10999,7 +11034,7 @@
         <x:v>原通信行 74</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="23" customHeight="1">
+    <x:row r="113" ht="15" customHeight="1">
       <x:c r="A113" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -11013,11 +11048,11 @@
         <x:f>(IF(F75=2,K75*2^20+E75/7168*H75*32,NA()))/1e9</x:f>
         <x:v>2.368765952</x:v>
       </x:c>
-      <x:c r="E113" s="51" t="n">
+      <x:c r="E113" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F113" s="52" t="n">
+      <x:c r="F113" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G113" s="34" t="n">
@@ -11032,7 +11067,7 @@
         <x:f>G113*F113*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>2.631962168888889</x:v>
       </x:c>
-      <x:c r="J113" s="52" t="n">
+      <x:c r="J113" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K113" s="34" t="n">
@@ -11043,7 +11078,7 @@
         <x:v>原通信行 75</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="23" customHeight="1">
+    <x:row r="114" ht="15" customHeight="1">
       <x:c r="A114" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -11057,11 +11092,11 @@
         <x:f>(K76*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E114" s="51" t="n">
+      <x:c r="E114" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F114" s="52" t="n">
+      <x:c r="F114" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G114" s="34" t="n">
@@ -11076,7 +11111,7 @@
         <x:f>G114*F114*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J114" s="52" t="n">
+      <x:c r="J114" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K114" s="34" t="n">
@@ -11087,7 +11122,7 @@
         <x:v>原通信行 76</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="23" customHeight="1">
+    <x:row r="115" ht="15" customHeight="1">
       <x:c r="A115" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -11101,11 +11136,11 @@
         <x:f>(K77*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E115" s="51" t="n">
+      <x:c r="E115" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F115" s="52" t="n">
+      <x:c r="F115" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G115" s="34" t="n">
@@ -11120,7 +11155,7 @@
         <x:f>G115*F115*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J115" s="52" t="n">
+      <x:c r="J115" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K115" s="34" t="n">
@@ -11131,7 +11166,7 @@
         <x:v>原通信行 77</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="23" customHeight="1">
+    <x:row r="116" ht="15" customHeight="1">
       <x:c r="A116" s="30" t="str">
         <x:v>DP</x:v>
       </x:c>
@@ -11145,11 +11180,11 @@
         <x:f>(K78*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E116" s="51" t="n">
+      <x:c r="E116" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F116" s="52" t="n">
+      <x:c r="F116" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G116" s="34" t="n">
@@ -11164,7 +11199,7 @@
         <x:f>G116*F116*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J116" s="52" t="n">
+      <x:c r="J116" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K116" s="34" t="n">
@@ -11175,7 +11210,7 @@
         <x:v>原通信行 78</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="23" customHeight="1">
+    <x:row r="117" ht="15" customHeight="1">
       <x:c r="A117" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -11189,11 +11224,11 @@
         <x:f>(K79*2^20)/1e9</x:f>
         <x:v>1.181745152</x:v>
       </x:c>
-      <x:c r="E117" s="51" t="n">
+      <x:c r="E117" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F117" s="52" t="n">
+      <x:c r="F117" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G117" s="34" t="n">
@@ -11208,7 +11243,7 @@
         <x:f>G117*F117*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>1.313050168888889</x:v>
       </x:c>
-      <x:c r="J117" s="52" t="n">
+      <x:c r="J117" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K117" s="34" t="n">
@@ -11219,7 +11254,7 @@
         <x:v>原通信行 79</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="23" customHeight="1">
+    <x:row r="118" ht="15" customHeight="1">
       <x:c r="A118" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -11233,11 +11268,11 @@
         <x:f>(K80*2^20)/1e9</x:f>
         <x:v>1.181745152</x:v>
       </x:c>
-      <x:c r="E118" s="51" t="n">
+      <x:c r="E118" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F118" s="52" t="n">
+      <x:c r="F118" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G118" s="34" t="n">
@@ -11252,7 +11287,7 @@
         <x:f>G118*F118*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>1.313050168888889</x:v>
       </x:c>
-      <x:c r="J118" s="52" t="n">
+      <x:c r="J118" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K118" s="34" t="n">
@@ -11263,7 +11298,7 @@
         <x:v>原通信行 80</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="23" customHeight="1">
+    <x:row r="119" ht="15" customHeight="1">
       <x:c r="A119" s="30" t="str">
         <x:v>共享专家 TP</x:v>
       </x:c>
@@ -11277,11 +11312,11 @@
         <x:f>(K81*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E119" s="51" t="n">
+      <x:c r="E119" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F119" s="52" t="n">
+      <x:c r="F119" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G119" s="34" t="n">
@@ -11296,7 +11331,7 @@
         <x:f>G119*F119*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J119" s="52" t="n">
+      <x:c r="J119" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K119" s="34" t="n">
@@ -11307,7 +11342,7 @@
         <x:v>原通信行 81</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="23" customHeight="1">
+    <x:row r="120" ht="15" customHeight="1">
       <x:c r="A120" s="30" t="str">
         <x:v>DCP</x:v>
       </x:c>
@@ -11321,11 +11356,11 @@
         <x:f>(K82*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E120" s="51" t="n">
+      <x:c r="E120" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F120" s="52" t="n">
+      <x:c r="F120" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G120" s="34" t="n">
@@ -11340,7 +11375,7 @@
         <x:f>G120*F120*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J120" s="52" t="n">
+      <x:c r="J120" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K120" s="34" t="n">
@@ -11351,7 +11386,7 @@
         <x:v>原通信行 82</x:v>
       </x:c>
     </x:row>
-    <x:row r="121" ht="23" customHeight="1">
+    <x:row r="121" ht="15" customHeight="1">
       <x:c r="A121" s="30" t="str">
         <x:v>DCP</x:v>
       </x:c>
@@ -11365,11 +11400,11 @@
         <x:f>(K83*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E121" s="51" t="n">
+      <x:c r="E121" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F121" s="52" t="n">
+      <x:c r="F121" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G121" s="34" t="n">
@@ -11384,7 +11419,7 @@
         <x:f>G121*F121*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J121" s="52" t="n">
+      <x:c r="J121" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K121" s="34" t="n">
@@ -11395,7 +11430,7 @@
         <x:v>原通信行 83</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="23" customHeight="1">
+    <x:row r="122" ht="15" customHeight="1">
       <x:c r="A122" s="30" t="str">
         <x:v>DCP</x:v>
       </x:c>
@@ -11409,11 +11444,11 @@
         <x:f>(K84*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E122" s="51" t="n">
+      <x:c r="E122" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F122" s="52" t="n">
+      <x:c r="F122" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G122" s="34" t="n">
@@ -11428,7 +11463,7 @@
         <x:f>G122*F122*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J122" s="52" t="n">
+      <x:c r="J122" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K122" s="34" t="n">
@@ -11439,7 +11474,7 @@
         <x:v>原通信行 84</x:v>
       </x:c>
     </x:row>
-    <x:row r="123" ht="23" customHeight="1">
+    <x:row r="123" ht="15" customHeight="1">
       <x:c r="A123" s="30" t="str">
         <x:v>SP</x:v>
       </x:c>
@@ -11453,11 +11488,11 @@
         <x:f>(K85*2^20)/1e9</x:f>
         <x:v>0.012845056</x:v>
       </x:c>
-      <x:c r="E123" s="51" t="n">
+      <x:c r="E123" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F123" s="52" t="n">
+      <x:c r="F123" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G123" s="34" t="n">
@@ -11472,7 +11507,7 @@
         <x:f>G123*F123*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0.014272284444444446</x:v>
       </x:c>
-      <x:c r="J123" s="52" t="n">
+      <x:c r="J123" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K123" s="34" t="n">
@@ -11483,7 +11518,7 @@
         <x:v>原通信行 85</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="23" customHeight="1">
+    <x:row r="124" ht="15" customHeight="1">
       <x:c r="A124" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -11497,11 +11532,11 @@
         <x:f>(K86*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E124" s="51" t="n">
+      <x:c r="E124" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F124" s="52" t="n">
+      <x:c r="F124" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G124" s="34" t="n">
@@ -11516,7 +11551,7 @@
         <x:f>G124*F124*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J124" s="52" t="n">
+      <x:c r="J124" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K124" s="34" t="n">
@@ -11527,7 +11562,7 @@
         <x:v>原通信行 86</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="23" customHeight="1">
+    <x:row r="125" ht="15" customHeight="1">
       <x:c r="A125" s="30" t="str">
         <x:v>LM Head TP</x:v>
       </x:c>
@@ -11541,11 +11576,11 @@
         <x:f>(K87*2^20)/1e9</x:f>
         <x:v>0.011010048</x:v>
       </x:c>
-      <x:c r="E125" s="51" t="n">
+      <x:c r="E125" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F125" s="52" t="n">
+      <x:c r="F125" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G125" s="34" t="n">
@@ -11560,7 +11595,7 @@
         <x:f>G125*F125*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0.012233386666666669</x:v>
       </x:c>
-      <x:c r="J125" s="52" t="n">
+      <x:c r="J125" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K125" s="34" t="n">
@@ -11571,7 +11606,7 @@
         <x:v>原通信行 87</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="23" customHeight="1">
+    <x:row r="126" ht="15" customHeight="1">
       <x:c r="A126" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -11585,11 +11620,11 @@
         <x:f>(K88*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E126" s="51" t="n">
+      <x:c r="E126" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F126" s="52" t="n">
+      <x:c r="F126" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G126" s="34" t="n">
@@ -11604,7 +11639,7 @@
         <x:f>G126*F126*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J126" s="52" t="n">
+      <x:c r="J126" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K126" s="34" t="n">
@@ -11615,7 +11650,7 @@
         <x:v>原通信行 88</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="23" customHeight="1">
+    <x:row r="127" ht="15" customHeight="1">
       <x:c r="A127" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -11629,11 +11664,11 @@
         <x:f>(K89*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E127" s="51" t="n">
+      <x:c r="E127" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F127" s="52" t="n">
+      <x:c r="F127" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G127" s="34" t="n">
@@ -11648,7 +11683,7 @@
         <x:f>G127*F127*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J127" s="52" t="n">
+      <x:c r="J127" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K127" s="34" t="n">
@@ -11659,7 +11694,7 @@
         <x:v>原通信行 89</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="23" customHeight="1">
+    <x:row r="128" ht="15" customHeight="1">
       <x:c r="A128" s="30" t="str">
         <x:v>Fine LM Head TP</x:v>
       </x:c>
@@ -11673,11 +11708,11 @@
         <x:f>(K90*2^20)/1e9</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E128" s="51" t="n">
+      <x:c r="E128" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F128" s="52" t="n">
+      <x:c r="F128" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G128" s="34" t="n">
@@ -11692,7 +11727,7 @@
         <x:f>G128*F128*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J128" s="52" t="n">
+      <x:c r="J128" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K128" s="34" t="n">
@@ -11703,7 +11738,7 @@
         <x:v>原通信行 90</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="23" customHeight="1">
+    <x:row r="129" ht="15" customHeight="1">
       <x:c r="A129" s="30" t="str">
         <x:v>EP</x:v>
       </x:c>
@@ -11717,11 +11752,11 @@
         <x:f>(IF(E74=0,0,H74*ROUNDUP(896/G74,0)*(G74-1)*32))/1e9</x:f>
         <x:v>0.002308096</x:v>
       </x:c>
-      <x:c r="E129" s="51" t="n">
+      <x:c r="E129" s="64" t="n">
         <x:f>$H$97</x:f>
         <x:v>100</x:v>
       </x:c>
-      <x:c r="F129" s="52" t="n">
+      <x:c r="F129" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G129" s="34" t="n">
@@ -11736,7 +11771,7 @@
         <x:f>G129*F129*$D$97*$B$97/(1-$B$97)</x:f>
         <x:v>0.002564551111111111</x:v>
       </x:c>
-      <x:c r="J129" s="52" t="n">
+      <x:c r="J129" s="59" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K129" s="34" t="n">
@@ -11747,36 +11782,36 @@
         <x:v>额外控制量</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="23" customHeight="1">
-      <x:c r="A130" s="53" t="str">
+    <x:row r="130" ht="15" customHeight="1">
+      <x:c r="A130" s="40" t="str">
         <x:v>所列事件串行相加</x:v>
       </x:c>
-      <x:c r="B130" s="53"/>
-      <x:c r="C130" s="53"/>
-      <x:c r="D130" s="54" t="n">
+      <x:c r="B130" s="40"/>
+      <x:c r="C130" s="40"/>
+      <x:c r="D130" s="41" t="n">
         <x:f>SUM(D103:D129)</x:f>
         <x:v>9.708812287999999</x:v>
       </x:c>
-      <x:c r="E130" s="54"/>
-      <x:c r="F130" s="53"/>
-      <x:c r="G130" s="54" t="n">
+      <x:c r="E130" s="40"/>
+      <x:c r="F130" s="40"/>
+      <x:c r="G130" s="41" t="n">
         <x:f>SUM(G103:G129)</x:f>
         <x:v>97.08812288</x:v>
       </x:c>
-      <x:c r="H130" s="54" t="n">
+      <x:c r="H130" s="41" t="n">
         <x:f>SUM(H103:H129)</x:f>
         <x:v>107.87569208888888</x:v>
       </x:c>
-      <x:c r="I130" s="54" t="n">
+      <x:c r="I130" s="41" t="n">
         <x:f>SUM(I103:I129)</x:f>
         <x:v>10.787569208888891</x:v>
       </x:c>
-      <x:c r="J130" s="53"/>
-      <x:c r="K130" s="54" t="n">
+      <x:c r="J130" s="40"/>
+      <x:c r="K130" s="41" t="n">
         <x:f>SUM(K103:K129)</x:f>
         <x:v>10.787569208888891</x:v>
       </x:c>
-      <x:c r="L130" s="53"/>
+      <x:c r="L130" s="40"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="L99:L99">

--- a/models/kimi-k3/kimi-k3-analysis.xlsx
+++ b/models/kimi-k3/kimi-k3-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R89183242af1b4e63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R9008018a6f6b4344"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R7e71530fe6754c97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rf5363412741648ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R3801da1042f745aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="Rea38094374774576"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -30,7 +30,7 @@
     <x:numFmt numFmtId="211" formatCode="#,##0.000000"/>
     <x:numFmt numFmtId="212" formatCode="0.000000%"/>
   </x:numFmts>
-  <x:fonts count="5">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -57,8 +57,19 @@
       <x:color rgb="FF000000"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -110,6 +121,16 @@
         <x:fgColor rgb="FFD9E2F3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E1F2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -145,7 +166,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="81">
+  <x:cellXfs count="104">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -335,6 +356,65 @@
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="209" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="6" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -365,7 +445,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -375,7 +455,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -385,7 +465,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -395,7 +475,7 @@
         <x:color rgb="FFA32020"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE9E7"/>
         </x:patternFill>
       </x:fill>
@@ -11947,15 +12027,29 @@
     <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="30" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
-    <x:col min="22" max="22" width="18" hidden="0" customWidth="1"/>
-    <x:col min="23" max="23" width="18" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="19" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="19" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="19" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="19" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="19" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="19" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="19" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="19" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="19" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="19" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="19" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="19" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="19" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="19" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="19" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="19" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="19" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="19" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="19" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="19" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="19" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="19" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="19" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -12014,7 +12108,7 @@
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="30" t="str">
-        <x:v>稳态相位平均估算。每层以等长 EP 通信段建模；未使用逐层 profiling，次数可为小数。</x:v>
+        <x:v>按层分布等效 EP、TP 通信段，次数按一分钟统计。</x:v>
       </x:c>
       <x:c r="B3" s="30"/>
       <x:c r="C3" s="30"/>
@@ -12212,7 +12306,7 @@
       <x:c r="C9" s="30"/>
       <x:c r="D9" s="30"/>
       <x:c r="E9" s="30" t="str">
-        <x:v>通信共享比例</x:v>
+        <x:v>EP 共享比例</x:v>
       </x:c>
       <x:c r="F9" s="68" t="n">
         <x:v>1</x:v>
@@ -12220,7 +12314,7 @@
       <x:c r="G9" s="30"/>
       <x:c r="H9" s="30"/>
       <x:c r="I9" s="30" t="str">
-        <x:v>关键路径暴露率</x:v>
+        <x:v>EP 暴露率</x:v>
       </x:c>
       <x:c r="J9" s="68" t="n">
         <x:v>1</x:v>
@@ -12278,19 +12372,29 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="C11" s="30"/>
-      <x:c r="D11" s="30" t="str">
-        <x:v>TTFT 暂作 P 批次间隔；步间隔＝TPOT×平均产出。每周期 1 批表示各 P DP 同步交接。</x:v>
-      </x:c>
-      <x:c r="E11" s="30"/>
-      <x:c r="F11" s="30"/>
+      <x:c r="D11" s="30" t="str"/>
+      <x:c r="E11" s="30" t="str">
+        <x:v>TP 带宽 GB/s</x:v>
+      </x:c>
+      <x:c r="F11" s="83" t="n">
+        <x:v>4800</x:v>
+      </x:c>
       <x:c r="G11" s="30"/>
       <x:c r="H11" s="30"/>
-      <x:c r="I11" s="30"/>
-      <x:c r="J11" s="30"/>
+      <x:c r="I11" s="30" t="str">
+        <x:v>TP 共享比例</x:v>
+      </x:c>
+      <x:c r="J11" s="85" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="K11" s="30"/>
       <x:c r="L11" s="30"/>
-      <x:c r="M11" s="30"/>
-      <x:c r="N11" s="30"/>
+      <x:c r="M11" s="30" t="str">
+        <x:v>TP 暴露率</x:v>
+      </x:c>
+      <x:c r="N11" s="85" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="O11" s="30"/>
       <x:c r="P11" s="30"/>
       <x:c r="Q11" s="30"/>
@@ -12303,7 +12407,9 @@
       <x:c r="X11" s="30"/>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="30"/>
+      <x:c r="A12" s="30" t="str">
+        <x:v>TTFT 作为批次周期；EP 与 TP 带宽分别填写。TP 不与 KV 共用链路时，将 TP 共享比例设为 0。</x:v>
+      </x:c>
       <x:c r="B12" s="30"/>
       <x:c r="C12" s="30"/>
       <x:c r="D12" s="30"/>
@@ -12517,7 +12623,7 @@
       </x:c>
       <x:c r="G18" s="30"/>
       <x:c r="H18" s="30" t="str">
-        <x:v>全 EP＝该步所有等效 EP 通信段都在 KV 窗口内；不代表整步持续时间都重叠。</x:v>
+        <x:v>全通信＝该步所有等效 EP＋TP 段都在 KV 窗口内；TP 首尾通信均摊到层段。</x:v>
       </x:c>
       <x:c r="I18" s="30"/>
       <x:c r="J18" s="30"/>
@@ -12660,12 +12766,24 @@
       <x:c r="O22" s="73" t="str">
         <x:v>配置条件</x:v>
       </x:c>
-      <x:c r="P22" s="30"/>
-      <x:c r="Q22" s="30"/>
-      <x:c r="R22" s="30"/>
-      <x:c r="S22" s="30"/>
-      <x:c r="T22" s="30"/>
-      <x:c r="U22" s="30"/>
+      <x:c r="P22" s="90" t="str">
+        <x:v>TP GB/s 输入</x:v>
+      </x:c>
+      <x:c r="Q22" s="90" t="str">
+        <x:v>TP 共享比例</x:v>
+      </x:c>
+      <x:c r="R22" s="90" t="str">
+        <x:v>TP 暴露率</x:v>
+      </x:c>
+      <x:c r="S22" s="90" t="str">
+        <x:v>Attention 层数</x:v>
+      </x:c>
+      <x:c r="T22" s="90" t="str">
+        <x:v>Dense 层数</x:v>
+      </x:c>
+      <x:c r="U22" s="90" t="str">
+        <x:v>共享专家 TP 层数</x:v>
+      </x:c>
       <x:c r="V22" s="30"/>
       <x:c r="W22" s="30"/>
       <x:c r="X22" s="30"/>
@@ -12722,12 +12840,27 @@
       <x:c r="O23" s="30" t="str">
         <x:v>运行未验证</x:v>
       </x:c>
-      <x:c r="P23" s="30"/>
-      <x:c r="Q23" s="30"/>
-      <x:c r="R23" s="30"/>
-      <x:c r="S23" s="30"/>
-      <x:c r="T23" s="30"/>
-      <x:c r="U23" s="30"/>
+      <x:c r="P23" s="98" t="n">
+        <x:f>$F$11</x:f>
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="Q23" s="99" t="n">
+        <x:f>$J$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R23" s="99" t="n">
+        <x:f>$N$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S23" s="100" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="T23" s="100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U23" s="100" t="n">
+        <x:v>92</x:v>
+      </x:c>
       <x:c r="V23" s="30"/>
       <x:c r="W23" s="30"/>
       <x:c r="X23" s="30"/>
@@ -12784,12 +12917,27 @@
       <x:c r="O24" s="30" t="str">
         <x:v>需 128 个冗余专家槽</x:v>
       </x:c>
-      <x:c r="P24" s="30"/>
-      <x:c r="Q24" s="30"/>
-      <x:c r="R24" s="30"/>
-      <x:c r="S24" s="30"/>
-      <x:c r="T24" s="30"/>
-      <x:c r="U24" s="30"/>
+      <x:c r="P24" s="98" t="n">
+        <x:f>$F$11</x:f>
+        <x:v>4800</x:v>
+      </x:c>
+      <x:c r="Q24" s="99" t="n">
+        <x:f>$J$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="R24" s="99" t="n">
+        <x:f>$N$11</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="S24" s="100" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="T24" s="100" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U24" s="100" t="n">
+        <x:v>92</x:v>
+      </x:c>
       <x:c r="V24" s="30"/>
       <x:c r="W24" s="30"/>
       <x:c r="X24" s="30"/>
@@ -12923,16 +13071,16 @@
         <x:v>KV 窗口 ms/次</x:v>
       </x:c>
       <x:c r="H29" s="73" t="str">
-        <x:v>重叠 FW 次/min</x:v>
+        <x:v>EP+TP 重叠 FW/min</x:v>
       </x:c>
       <x:c r="I29" s="73" t="str">
-        <x:v>全 EP FW 次/min</x:v>
+        <x:v>全通信 FW/min</x:v>
       </x:c>
       <x:c r="J29" s="73" t="str">
-        <x:v>部分 EP FW 次/min</x:v>
+        <x:v>部分通信 FW/min</x:v>
       </x:c>
       <x:c r="K29" s="73" t="str">
-        <x:v>重叠层调用 次/min</x:v>
+        <x:v>重叠层段 次/min</x:v>
       </x:c>
       <x:c r="L29" s="73" t="str">
         <x:v>60s 工作增时 ms</x:v>
@@ -12947,12 +13095,20 @@
         <x:v>结果条件</x:v>
       </x:c>
       <x:c r="P29" s="73" t="str">
-        <x:v>最低 EP GB/s</x:v>
-      </x:c>
-      <x:c r="Q29" s="30"/>
-      <x:c r="R29" s="30"/>
-      <x:c r="S29" s="30"/>
-      <x:c r="T29" s="30"/>
+        <x:v>最低 EP GB/s（扣 TP）</x:v>
+      </x:c>
+      <x:c r="Q29" s="90" t="str">
+        <x:v>TP GB/Rank/步</x:v>
+      </x:c>
+      <x:c r="R29" s="90" t="str">
+        <x:v>TP 带宽项 ms</x:v>
+      </x:c>
+      <x:c r="S29" s="90" t="str">
+        <x:v>EP 增时 ms/60s</x:v>
+      </x:c>
+      <x:c r="T29" s="90" t="str">
+        <x:v>TP 增时 ms/60s</x:v>
+      </x:c>
       <x:c r="U29" s="30"/>
       <x:c r="V29" s="30"/>
       <x:c r="W29" s="30"/>
@@ -12988,45 +13144,56 @@
         <x:v>1.7120256</x:v>
       </x:c>
       <x:c r="H30" s="75" t="n">
-        <x:f>IF(W60="估算",U60*R60,"")</x:f>
-        <x:v>19.977658521738384</x:v>
+        <x:f>IF(W60="",U60*R60,"")</x:f>
+        <x:v>19.981739217390437</x:v>
       </x:c>
       <x:c r="I30" s="75" t="n">
-        <x:f>IF(W60="估算",U60*S60,"")</x:f>
+        <x:f>IF(W60="",U60*S60,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J30" s="75" t="n">
-        <x:f>IF(W60="估算",U60*MAX(0,R60-S60),"")</x:f>
-        <x:v>19.977658521738384</x:v>
+        <x:f>IF(W60="",U60*MAX(0,R60-S60),"")</x:f>
+        <x:v>19.981739217390437</x:v>
       </x:c>
       <x:c r="K30" s="75" t="n">
-        <x:f>IF(W60="估算",IF(OR(O60=0,K60=0),0,U60*E23*MIN(1,(K60+P60)/L60)),"")</x:f>
-        <x:v>472.944584</x:v>
+        <x:f>IF(W60="",IF(OR(AK60=0,K60=0),0,U60*E23*MIN(1,(K60+AL60)/L60)),"")</x:f>
+        <x:v>473.32000800000003</x:v>
       </x:c>
       <x:c r="L30" s="34" t="n">
-        <x:f>IF(W60="估算",V60,"")</x:f>
-        <x:v>0.08094021640356477</x:v>
+        <x:f>IF(W60="",V60,"")</x:f>
+        <x:v>0.15235211958680156</x:v>
       </x:c>
       <x:c r="M30" s="34" t="n">
-        <x:f>IF(W60="估算",E30*V60/60,"")</x:f>
-        <x:v>0.006745018033630397</x:v>
+        <x:f>IF(W60="",E30*V60/60,"")</x:f>
+        <x:v>0.012696009965566798</x:v>
       </x:c>
       <x:c r="N30" s="34" t="n">
-        <x:f>IF(W60="估算",V60/60000*1e6,"")</x:f>
-        <x:v>1.3490036067260796</x:v>
+        <x:f>IF(W60="",V60/60000*1e6,"")</x:f>
+        <x:v>2.5392019931133594</x:v>
       </x:c>
       <x:c r="O30" s="30" t="str">
-        <x:f>IF(W60="估算","相位平均估算",W60)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W60="","",W60)</x:f>
       </x:c>
       <x:c r="P30" s="49" t="n">
         <x:f>Q60</x:f>
-        <x:v>136.165888</x:v>
-      </x:c>
-      <x:c r="Q30" s="30"/>
-      <x:c r="R30" s="30"/>
-      <x:c r="S30" s="30"/>
-      <x:c r="T30" s="30"/>
+        <x:v>139.66137001168445</x:v>
+      </x:c>
+      <x:c r="Q30" s="102" t="n">
+        <x:f>AE60</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R30" s="102" t="n">
+        <x:f>AF60</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S30" s="102" t="n">
+        <x:f>IF(W60="",AI60,"")</x:f>
+        <x:v>0.08094021640356477</x:v>
+      </x:c>
+      <x:c r="T30" s="102" t="n">
+        <x:f>IF(W60="",AJ60,"")</x:f>
+        <x:v>0.07141190318323679</x:v>
+      </x:c>
       <x:c r="U30" s="30"/>
       <x:c r="V30" s="30"/>
       <x:c r="W30" s="30"/>
@@ -13062,45 +13229,56 @@
         <x:v>1.7120256</x:v>
       </x:c>
       <x:c r="H31" s="75" t="n">
-        <x:f>IF(W61="估算",U61*R61,"")</x:f>
-        <x:v>17.407307521739135</x:v>
+        <x:f>IF(W61="",U61*R61,"")</x:f>
+        <x:v>17.40934786956516</x:v>
       </x:c>
       <x:c r="I31" s="75" t="n">
-        <x:f>IF(W61="估算",U61*S61,"")</x:f>
+        <x:f>IF(W61="",U61*S61,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J31" s="75" t="n">
-        <x:f>IF(W61="估算",U61*MAX(0,R61-S61),"")</x:f>
-        <x:v>17.407307521739135</x:v>
+        <x:f>IF(W61="",U61*MAX(0,R61-S61),"")</x:f>
+        <x:v>17.40934786956516</x:v>
       </x:c>
       <x:c r="K31" s="75" t="n">
-        <x:f>IF(W61="估算",IF(OR(O61=0,K61=0),0,U61*E23*MIN(1,(K61+P61)/L61)),"")</x:f>
-        <x:v>236.472292</x:v>
+        <x:f>IF(W61="",IF(OR(AK61=0,K61=0),0,U61*E23*MIN(1,(K61+AL61)/L61)),"")</x:f>
+        <x:v>236.66000400000001</x:v>
       </x:c>
       <x:c r="L31" s="34" t="n">
-        <x:f>IF(W61="估算",V61,"")</x:f>
-        <x:v>0.04047010820178239</x:v>
+        <x:f>IF(W61="",V61,"")</x:f>
+        <x:v>0.07617605979340078</x:v>
       </x:c>
       <x:c r="M31" s="34" t="n">
-        <x:f>IF(W61="估算",E31*V61/60,"")</x:f>
-        <x:v>0.006745018033630397</x:v>
+        <x:f>IF(W61="",E31*V61/60,"")</x:f>
+        <x:v>0.012696009965566798</x:v>
       </x:c>
       <x:c r="N31" s="34" t="n">
-        <x:f>IF(W61="估算",V61/60000*1e6,"")</x:f>
-        <x:v>0.6745018033630398</x:v>
+        <x:f>IF(W61="",V61/60000*1e6,"")</x:f>
+        <x:v>1.2696009965566797</x:v>
       </x:c>
       <x:c r="O31" s="30" t="str">
-        <x:f>IF(W61="估算","相位平均估算",W61)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W61="","",W61)</x:f>
       </x:c>
       <x:c r="P31" s="49" t="n">
         <x:f>Q61</x:f>
-        <x:v>68.082944</x:v>
-      </x:c>
-      <x:c r="Q31" s="30"/>
-      <x:c r="R31" s="30"/>
-      <x:c r="S31" s="30"/>
-      <x:c r="T31" s="30"/>
+        <x:v>68.94574018544603</x:v>
+      </x:c>
+      <x:c r="Q31" s="102" t="n">
+        <x:f>AE61</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R31" s="102" t="n">
+        <x:f>AF61</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S31" s="102" t="n">
+        <x:f>IF(W61="",AI61,"")</x:f>
+        <x:v>0.04047010820178239</x:v>
+      </x:c>
+      <x:c r="T31" s="102" t="n">
+        <x:f>IF(W61="",AJ61,"")</x:f>
+        <x:v>0.03570595159161839</x:v>
+      </x:c>
       <x:c r="U31" s="30"/>
       <x:c r="V31" s="30"/>
       <x:c r="W31" s="30"/>
@@ -13136,45 +13314,56 @@
         <x:v>1.7120256</x:v>
       </x:c>
       <x:c r="H32" s="75" t="n">
-        <x:f>IF(W62="估算",U62*R62,"")</x:f>
-        <x:v>16.122132021738842</x:v>
+        <x:f>IF(W62="",U62*R62,"")</x:f>
+        <x:v>16.12315219565186</x:v>
       </x:c>
       <x:c r="I32" s="75" t="n">
-        <x:f>IF(W62="估算",U62*S62,"")</x:f>
+        <x:f>IF(W62="",U62*S62,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J32" s="75" t="n">
-        <x:f>IF(W62="估算",U62*MAX(0,R62-S62),"")</x:f>
-        <x:v>16.122132021738842</x:v>
+        <x:f>IF(W62="",U62*MAX(0,R62-S62),"")</x:f>
+        <x:v>16.12315219565186</x:v>
       </x:c>
       <x:c r="K32" s="75" t="n">
-        <x:f>IF(W62="估算",IF(OR(O62=0,K62=0),0,U62*E23*MIN(1,(K62+P62)/L62)),"")</x:f>
-        <x:v>118.236146</x:v>
+        <x:f>IF(W62="",IF(OR(AK62=0,K62=0),0,U62*E23*MIN(1,(K62+AL62)/L62)),"")</x:f>
+        <x:v>118.33000200000001</x:v>
       </x:c>
       <x:c r="L32" s="34" t="n">
-        <x:f>IF(W62="估算",V62,"")</x:f>
-        <x:v>0.020235054100891194</x:v>
+        <x:f>IF(W62="",V62,"")</x:f>
+        <x:v>0.03808802989670039</x:v>
       </x:c>
       <x:c r="M32" s="34" t="n">
-        <x:f>IF(W62="估算",E32*V62/60,"")</x:f>
-        <x:v>0.006745018033630397</x:v>
+        <x:f>IF(W62="",E32*V62/60,"")</x:f>
+        <x:v>0.012696009965566798</x:v>
       </x:c>
       <x:c r="N32" s="34" t="n">
-        <x:f>IF(W62="估算",V62/60000*1e6,"")</x:f>
-        <x:v>0.3372509016815199</x:v>
+        <x:f>IF(W62="",V62/60000*1e6,"")</x:f>
+        <x:v>0.6348004982783398</x:v>
       </x:c>
       <x:c r="O32" s="30" t="str">
-        <x:f>IF(W62="估算","相位平均估算",W62)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W62="","",W62)</x:f>
       </x:c>
       <x:c r="P32" s="49" t="n">
         <x:f>Q62</x:f>
-        <x:v>34.041472</x:v>
-      </x:c>
-      <x:c r="Q32" s="30"/>
-      <x:c r="R32" s="30"/>
-      <x:c r="S32" s="30"/>
-      <x:c r="T32" s="30"/>
+        <x:v>34.25581290506786</x:v>
+      </x:c>
+      <x:c r="Q32" s="102" t="n">
+        <x:f>AE62</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R32" s="102" t="n">
+        <x:f>AF62</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S32" s="102" t="n">
+        <x:f>IF(W62="",AI62,"")</x:f>
+        <x:v>0.020235054100891194</x:v>
+      </x:c>
+      <x:c r="T32" s="102" t="n">
+        <x:f>IF(W62="",AJ62,"")</x:f>
+        <x:v>0.017852975795809196</x:v>
+      </x:c>
       <x:c r="U32" s="30"/>
       <x:c r="V32" s="30"/>
       <x:c r="W32" s="30"/>
@@ -13210,45 +13399,56 @@
         <x:v>1.7120256</x:v>
       </x:c>
       <x:c r="H33" s="75" t="n">
-        <x:f>IF(W63="估算",U63*R63,"")</x:f>
-        <x:v>15.693740188405636</x:v>
+        <x:f>IF(W63="",U63*R63,"")</x:f>
+        <x:v>15.694420304347645</x:v>
       </x:c>
       <x:c r="I33" s="75" t="n">
-        <x:f>IF(W63="估算",U63*S63,"")</x:f>
+        <x:f>IF(W63="",U63*S63,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J33" s="75" t="n">
-        <x:f>IF(W63="估算",U63*MAX(0,R63-S63),"")</x:f>
-        <x:v>15.693740188405636</x:v>
+        <x:f>IF(W63="",U63*MAX(0,R63-S63),"")</x:f>
+        <x:v>15.694420304347645</x:v>
       </x:c>
       <x:c r="K33" s="75" t="n">
-        <x:f>IF(W63="估算",IF(OR(O63=0,K63=0),0,U63*E23*MIN(1,(K63+P63)/L63)),"")</x:f>
-        <x:v>78.82409733333334</x:v>
+        <x:f>IF(W63="",IF(OR(AK63=0,K63=0),0,U63*E23*MIN(1,(K63+AL63)/L63)),"")</x:f>
+        <x:v>78.886668</x:v>
       </x:c>
       <x:c r="L33" s="34" t="n">
-        <x:f>IF(W63="估算",V63,"")</x:f>
-        <x:v>0.013490036067260796</x:v>
+        <x:f>IF(W63="",V63,"")</x:f>
+        <x:v>0.025392019931133596</x:v>
       </x:c>
       <x:c r="M33" s="34" t="n">
-        <x:f>IF(W63="估算",E33*V63/60,"")</x:f>
-        <x:v>0.006745018033630398</x:v>
+        <x:f>IF(W63="",E33*V63/60,"")</x:f>
+        <x:v>0.012696009965566798</x:v>
       </x:c>
       <x:c r="N33" s="34" t="n">
-        <x:f>IF(W63="估算",V63/60000*1e6,"")</x:f>
-        <x:v>0.2248339344543466</x:v>
+        <x:f>IF(W63="",V63/60000*1e6,"")</x:f>
+        <x:v>0.42320033218555997</x:v>
       </x:c>
       <x:c r="O33" s="30" t="str">
-        <x:f>IF(W63="估算","相位平均估算",W63)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W63="","",W63)</x:f>
       </x:c>
       <x:c r="P33" s="49" t="n">
         <x:f>Q63</x:f>
-        <x:v>22.694314666666667</x:v>
-      </x:c>
-      <x:c r="Q33" s="30"/>
-      <x:c r="R33" s="30"/>
-      <x:c r="S33" s="30"/>
-      <x:c r="T33" s="30"/>
+        <x:v>22.789377770668615</x:v>
+      </x:c>
+      <x:c r="Q33" s="102" t="n">
+        <x:f>AE63</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R33" s="102" t="n">
+        <x:f>AF63</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S33" s="102" t="n">
+        <x:f>IF(W63="",AI63,"")</x:f>
+        <x:v>0.013490036067260796</x:v>
+      </x:c>
+      <x:c r="T33" s="102" t="n">
+        <x:f>IF(W63="",AJ63,"")</x:f>
+        <x:v>0.011901983863872798</x:v>
+      </x:c>
       <x:c r="U33" s="30"/>
       <x:c r="V33" s="30"/>
       <x:c r="W33" s="30"/>
@@ -13284,45 +13484,56 @@
         <x:v>24.3612672</x:v>
       </x:c>
       <x:c r="H34" s="75" t="n">
-        <x:f>IF(W64="估算",U64*R64,"")</x:f>
-        <x:v>17.585076664349497</x:v>
+        <x:f>IF(W64="",U64*R64,"")</x:f>
+        <x:v>17.58589280347911</x:v>
       </x:c>
       <x:c r="I34" s="75" t="n">
-        <x:f>IF(W64="估算",U64*S64,"")</x:f>
-        <x:v>11.648443975653677</x:v>
+        <x:f>IF(W64="",U64*S64,"")</x:f>
+        <x:v>11.647627836522734</x:v>
       </x:c>
       <x:c r="J34" s="75" t="n">
-        <x:f>IF(W64="估算",U64*MAX(0,R64-S64),"")</x:f>
-        <x:v>5.93663268869582</x:v>
+        <x:f>IF(W64="",U64*MAX(0,R64-S64),"")</x:f>
+        <x:v>5.938264966956375</x:v>
       </x:c>
       <x:c r="K34" s="75" t="n">
-        <x:f>IF(W64="估算",IF(OR(O64=0,K64=0),0,U64*E23*MIN(1,(K64+P64)/L64)),"")</x:f>
-        <x:v>1344.82705312</x:v>
+        <x:f>IF(W64="",IF(OR(AK64=0,K64=0),0,U64*E23*MIN(1,(K64+AL64)/L64)),"")</x:f>
+        <x:v>1344.9021379199999</x:v>
       </x:c>
       <x:c r="L34" s="34" t="n">
-        <x:f>IF(W64="估算",V64,"")</x:f>
-        <x:v>0.23035846654394496</x:v>
+        <x:f>IF(W64="",V64,"")</x:f>
+        <x:v>0.43359793336811225</x:v>
       </x:c>
       <x:c r="M34" s="34" t="n">
-        <x:f>IF(W64="估算",E34*V64/60,"")</x:f>
-        <x:v>0.01919653887866208</x:v>
+        <x:f>IF(W64="",E34*V64/60,"")</x:f>
+        <x:v>0.036133161114009354</x:v>
       </x:c>
       <x:c r="N34" s="34" t="n">
-        <x:f>IF(W64="估算",V64/60000*1e6,"")</x:f>
-        <x:v>3.8393077757324154</x:v>
+        <x:f>IF(W64="",V64/60000*1e6,"")</x:f>
+        <x:v>7.226632222801871</x:v>
       </x:c>
       <x:c r="O34" s="30" t="str">
-        <x:f>IF(W64="估算","相位平均估算",W64)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W64="","",W64)</x:f>
       </x:c>
       <x:c r="P34" s="49" t="n">
         <x:f>Q64</x:f>
-        <x:v>136.165888</x:v>
-      </x:c>
-      <x:c r="Q34" s="30"/>
-      <x:c r="R34" s="30"/>
-      <x:c r="S34" s="30"/>
-      <x:c r="T34" s="30"/>
+        <x:v>139.66137001168445</x:v>
+      </x:c>
+      <x:c r="Q34" s="102" t="n">
+        <x:f>AE64</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R34" s="102" t="n">
+        <x:f>AF64</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S34" s="102" t="n">
+        <x:f>IF(W64="",AI64,"")</x:f>
+        <x:v>0.23035846654394496</x:v>
+      </x:c>
+      <x:c r="T34" s="102" t="n">
+        <x:f>IF(W64="",AJ64,"")</x:f>
+        <x:v>0.20323946682416733</x:v>
+      </x:c>
       <x:c r="U34" s="30"/>
       <x:c r="V34" s="30"/>
       <x:c r="W34" s="30"/>
@@ -13358,45 +13569,56 @@
         <x:v>24.3612672</x:v>
       </x:c>
       <x:c r="H35" s="75" t="n">
-        <x:f>IF(W65="估算",U65*R65,"")</x:f>
-        <x:v>10.276233984348071</x:v>
+        <x:f>IF(W65="",U65*R65,"")</x:f>
+        <x:v>10.276642053914209</x:v>
       </x:c>
       <x:c r="I35" s="75" t="n">
-        <x:f>IF(W65="估算",U65*S65,"")</x:f>
-        <x:v>4.34052633565285</x:v>
+        <x:f>IF(W65="",U65*S65,"")</x:f>
+        <x:v>4.340118266086712</x:v>
       </x:c>
       <x:c r="J35" s="75" t="n">
-        <x:f>IF(W65="估算",U65*MAX(0,R65-S65),"")</x:f>
-        <x:v>5.935707648695221</x:v>
+        <x:f>IF(W65="",U65*MAX(0,R65-S65),"")</x:f>
+        <x:v>5.936523787827497</x:v>
       </x:c>
       <x:c r="K35" s="75" t="n">
-        <x:f>IF(W65="估算",IF(OR(O65=0,K65=0),0,U65*E23*MIN(1,(K65+P65)/L65)),"")</x:f>
-        <x:v>672.41352656</x:v>
+        <x:f>IF(W65="",IF(OR(AK65=0,K65=0),0,U65*E23*MIN(1,(K65+AL65)/L65)),"")</x:f>
+        <x:v>672.4510689599999</x:v>
       </x:c>
       <x:c r="L35" s="34" t="n">
-        <x:f>IF(W65="估算",V65,"")</x:f>
-        <x:v>0.11517923327197248</x:v>
+        <x:f>IF(W65="",V65,"")</x:f>
+        <x:v>0.21679896668405613</x:v>
       </x:c>
       <x:c r="M35" s="34" t="n">
-        <x:f>IF(W65="估算",E35*V65/60,"")</x:f>
-        <x:v>0.01919653887866208</x:v>
+        <x:f>IF(W65="",E35*V65/60,"")</x:f>
+        <x:v>0.036133161114009354</x:v>
       </x:c>
       <x:c r="N35" s="34" t="n">
-        <x:f>IF(W65="估算",V65/60000*1e6,"")</x:f>
-        <x:v>1.9196538878662077</x:v>
+        <x:f>IF(W65="",V65/60000*1e6,"")</x:f>
+        <x:v>3.6133161114009353</x:v>
       </x:c>
       <x:c r="O35" s="30" t="str">
-        <x:f>IF(W65="估算","相位平均估算",W65)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W65="","",W65)</x:f>
       </x:c>
       <x:c r="P35" s="49" t="n">
         <x:f>Q65</x:f>
-        <x:v>68.082944</x:v>
-      </x:c>
-      <x:c r="Q35" s="30"/>
-      <x:c r="R35" s="30"/>
-      <x:c r="S35" s="30"/>
-      <x:c r="T35" s="30"/>
+        <x:v>68.94574018544603</x:v>
+      </x:c>
+      <x:c r="Q35" s="102" t="n">
+        <x:f>AE65</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R35" s="102" t="n">
+        <x:f>AF65</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S35" s="102" t="n">
+        <x:f>IF(W65="",AI65,"")</x:f>
+        <x:v>0.11517923327197248</x:v>
+      </x:c>
+      <x:c r="T35" s="102" t="n">
+        <x:f>IF(W65="",AJ65,"")</x:f>
+        <x:v>0.10161973341208366</x:v>
+      </x:c>
       <x:c r="U35" s="30"/>
       <x:c r="V35" s="30"/>
       <x:c r="W35" s="30"/>
@@ -13432,45 +13654,56 @@
         <x:v>24.3612672</x:v>
       </x:c>
       <x:c r="H36" s="75" t="n">
-        <x:f>IF(W66="估算",U66*R66,"")</x:f>
-        <x:v>6.621812644348357</x:v>
+        <x:f>IF(W66="",U66*R66,"")</x:f>
+        <x:v>6.62201667913076</x:v>
       </x:c>
       <x:c r="I36" s="75" t="n">
-        <x:f>IF(W66="估算",U66*S66,"")</x:f>
-        <x:v>0.6865675156524365</x:v>
+        <x:f>IF(W66="",U66*S66,"")</x:f>
+        <x:v>0.6863634808697006</x:v>
       </x:c>
       <x:c r="J36" s="75" t="n">
-        <x:f>IF(W66="估算",U66*MAX(0,R66-S66),"")</x:f>
-        <x:v>5.935245128695921</x:v>
+        <x:f>IF(W66="",U66*MAX(0,R66-S66),"")</x:f>
+        <x:v>5.935653198261059</x:v>
       </x:c>
       <x:c r="K36" s="75" t="n">
-        <x:f>IF(W66="估算",IF(OR(O66=0,K66=0),0,U66*E23*MIN(1,(K66+P66)/L66)),"")</x:f>
-        <x:v>336.20676328</x:v>
+        <x:f>IF(W66="",IF(OR(AK66=0,K66=0),0,U66*E23*MIN(1,(K66+AL66)/L66)),"")</x:f>
+        <x:v>336.22553447999996</x:v>
       </x:c>
       <x:c r="L36" s="34" t="n">
-        <x:f>IF(W66="估算",V66,"")</x:f>
-        <x:v>0.05758961663598624</x:v>
+        <x:f>IF(W66="",V66,"")</x:f>
+        <x:v>0.10839948334202806</x:v>
       </x:c>
       <x:c r="M36" s="34" t="n">
-        <x:f>IF(W66="估算",E36*V66/60,"")</x:f>
-        <x:v>0.01919653887866208</x:v>
+        <x:f>IF(W66="",E36*V66/60,"")</x:f>
+        <x:v>0.036133161114009354</x:v>
       </x:c>
       <x:c r="N36" s="34" t="n">
-        <x:f>IF(W66="估算",V66/60000*1e6,"")</x:f>
-        <x:v>0.9598269439331039</x:v>
+        <x:f>IF(W66="",V66/60000*1e6,"")</x:f>
+        <x:v>1.8066580557004677</x:v>
       </x:c>
       <x:c r="O36" s="30" t="str">
-        <x:f>IF(W66="估算","相位平均估算",W66)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W66="","",W66)</x:f>
       </x:c>
       <x:c r="P36" s="49" t="n">
         <x:f>Q66</x:f>
-        <x:v>34.041472</x:v>
-      </x:c>
-      <x:c r="Q36" s="30"/>
-      <x:c r="R36" s="30"/>
-      <x:c r="S36" s="30"/>
-      <x:c r="T36" s="30"/>
+        <x:v>34.25581290506786</x:v>
+      </x:c>
+      <x:c r="Q36" s="102" t="n">
+        <x:f>AE66</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R36" s="102" t="n">
+        <x:f>AF66</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S36" s="102" t="n">
+        <x:f>IF(W66="",AI66,"")</x:f>
+        <x:v>0.05758961663598624</x:v>
+      </x:c>
+      <x:c r="T36" s="102" t="n">
+        <x:f>IF(W66="",AJ66,"")</x:f>
+        <x:v>0.05080986670604183</x:v>
+      </x:c>
       <x:c r="U36" s="30"/>
       <x:c r="V36" s="30"/>
       <x:c r="W36" s="30"/>
@@ -13506,45 +13739,56 @@
         <x:v>24.3612672</x:v>
       </x:c>
       <x:c r="H37" s="75" t="n">
-        <x:f>IF(W67="估算",U67*R67,"")</x:f>
-        <x:v>5.40367219768112</x:v>
+        <x:f>IF(W67="",U67*R67,"")</x:f>
+        <x:v>5.403808220869832</x:v>
       </x:c>
       <x:c r="I37" s="75" t="n">
-        <x:f>IF(W67="估算",U67*S67,"")</x:f>
+        <x:f>IF(W67="",U67*S67,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J37" s="75" t="n">
-        <x:f>IF(W67="估算",U67*MAX(0,R67-S67),"")</x:f>
-        <x:v>5.40367219768112</x:v>
+        <x:f>IF(W67="",U67*MAX(0,R67-S67),"")</x:f>
+        <x:v>5.403808220869832</x:v>
       </x:c>
       <x:c r="K37" s="75" t="n">
-        <x:f>IF(W67="估算",IF(OR(O67=0,K67=0),0,U67*E23*MIN(1,(K67+P67)/L67)),"")</x:f>
-        <x:v>224.13784218666666</x:v>
+        <x:f>IF(W67="",IF(OR(AK67=0,K67=0),0,U67*E23*MIN(1,(K67+AL67)/L67)),"")</x:f>
+        <x:v>224.15035632</x:v>
       </x:c>
       <x:c r="L37" s="34" t="n">
-        <x:f>IF(W67="估算",V67,"")</x:f>
-        <x:v>0.03839307775732416</x:v>
+        <x:f>IF(W67="",V67,"")</x:f>
+        <x:v>0.07226632222801871</x:v>
       </x:c>
       <x:c r="M37" s="34" t="n">
-        <x:f>IF(W67="估算",E37*V67/60,"")</x:f>
-        <x:v>0.01919653887866208</x:v>
+        <x:f>IF(W67="",E37*V67/60,"")</x:f>
+        <x:v>0.036133161114009354</x:v>
       </x:c>
       <x:c r="N37" s="34" t="n">
-        <x:f>IF(W67="估算",V67/60000*1e6,"")</x:f>
-        <x:v>0.639884629288736</x:v>
+        <x:f>IF(W67="",V67/60000*1e6,"")</x:f>
+        <x:v>1.204438703800312</x:v>
       </x:c>
       <x:c r="O37" s="30" t="str">
-        <x:f>IF(W67="估算","相位平均估算",W67)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W67="","",W67)</x:f>
       </x:c>
       <x:c r="P37" s="49" t="n">
         <x:f>Q67</x:f>
-        <x:v>22.694314666666667</x:v>
-      </x:c>
-      <x:c r="Q37" s="30"/>
-      <x:c r="R37" s="30"/>
-      <x:c r="S37" s="30"/>
-      <x:c r="T37" s="30"/>
+        <x:v>22.789377770668615</x:v>
+      </x:c>
+      <x:c r="Q37" s="102" t="n">
+        <x:f>AE67</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R37" s="102" t="n">
+        <x:f>AF67</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S37" s="102" t="n">
+        <x:f>IF(W67="",AI67,"")</x:f>
+        <x:v>0.03839307775732416</x:v>
+      </x:c>
+      <x:c r="T37" s="102" t="n">
+        <x:f>IF(W67="",AJ67,"")</x:f>
+        <x:v>0.03387324447069455</x:v>
+      </x:c>
       <x:c r="U37" s="30"/>
       <x:c r="V37" s="30"/>
       <x:c r="W37" s="30"/>
@@ -13580,45 +13824,56 @@
         <x:v>96.83884032</x:v>
       </x:c>
       <x:c r="H38" s="75" t="n">
-        <x:f>IF(W68="估算",U68*R68,"")</x:f>
-        <x:v>20.357206845449838</x:v>
+        <x:f>IF(W68="",U68*R68,"")</x:f>
+        <x:v>20.357478891827263</x:v>
       </x:c>
       <x:c r="I38" s="75" t="n">
-        <x:f>IF(W68="估算",U68*S68,"")</x:f>
-        <x:v>18.378329282550787</x:v>
+        <x:f>IF(W68="",U68*S68,"")</x:f>
+        <x:v>18.378057236173362</x:v>
       </x:c>
       <x:c r="J38" s="75" t="n">
-        <x:f>IF(W68="估算",U68*MAX(0,R68-S68),"")</x:f>
-        <x:v>1.9788775628990507</x:v>
+        <x:f>IF(W68="",U68*MAX(0,R68-S68),"")</x:f>
+        <x:v>1.9794216556539013</x:v>
       </x:c>
       <x:c r="K38" s="75" t="n">
-        <x:f>IF(W68="估算",IF(OR(O68=0,K68=0),0,U68*E23*MIN(1,(K68+P68)/L68)),"")</x:f>
-        <x:v>1781.8630297813336</x:v>
+        <x:f>IF(W68="",IF(OR(AK68=0,K68=0),0,U68*E23*MIN(1,(K68+AL68)/L68)),"")</x:f>
+        <x:v>1781.888058048</x:v>
       </x:c>
       <x:c r="L38" s="34" t="n">
-        <x:f>IF(W68="估算",V68,"")</x:f>
-        <x:v>0.30523460699542915</x:v>
+        <x:f>IF(W68="",V68,"")</x:f>
+        <x:v>0.5745353212035063</x:v>
       </x:c>
       <x:c r="M38" s="34" t="n">
-        <x:f>IF(W68="估算",E38*V68/60,"")</x:f>
-        <x:v>0.025436217249619093</x:v>
+        <x:f>IF(W68="",E38*V68/60,"")</x:f>
+        <x:v>0.047877943433625524</x:v>
       </x:c>
       <x:c r="N38" s="34" t="n">
-        <x:f>IF(W68="估算",V68/60000*1e6,"")</x:f>
-        <x:v>5.087243449923819</x:v>
+        <x:f>IF(W68="",V68/60000*1e6,"")</x:f>
+        <x:v>9.575588686725103</x:v>
       </x:c>
       <x:c r="O38" s="30" t="str">
-        <x:f>IF(W68="估算","相位平均估算",W68)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W68="","",W68)</x:f>
       </x:c>
       <x:c r="P38" s="49" t="n">
         <x:f>Q68</x:f>
-        <x:v>136.165888</x:v>
-      </x:c>
-      <x:c r="Q38" s="30"/>
-      <x:c r="R38" s="30"/>
-      <x:c r="S38" s="30"/>
-      <x:c r="T38" s="30"/>
+        <x:v>139.66137001168445</x:v>
+      </x:c>
+      <x:c r="Q38" s="102" t="n">
+        <x:f>AE68</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R38" s="102" t="n">
+        <x:f>AF68</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S38" s="102" t="n">
+        <x:f>IF(W68="",AI68,"")</x:f>
+        <x:v>0.30523460699542915</x:v>
+      </x:c>
+      <x:c r="T38" s="102" t="n">
+        <x:f>IF(W68="",AJ68,"")</x:f>
+        <x:v>0.26930071420807705</x:v>
+      </x:c>
       <x:c r="U38" s="30"/>
       <x:c r="V38" s="30"/>
       <x:c r="W38" s="30"/>
@@ -13654,45 +13909,56 @@
         <x:v>96.83884032</x:v>
       </x:c>
       <x:c r="H39" s="75" t="n">
-        <x:f>IF(W69="估算",U69*R69,"")</x:f>
-        <x:v>10.673168640115582</x:v>
+        <x:f>IF(W69="",U69*R69,"")</x:f>
+        <x:v>10.673304663304295</x:v>
       </x:c>
       <x:c r="I39" s="75" t="n">
-        <x:f>IF(W69="估算",U69*S69,"")</x:f>
-        <x:v>8.694599423884064</x:v>
+        <x:f>IF(W69="",U69*S69,"")</x:f>
+        <x:v>8.694463400695351</x:v>
       </x:c>
       <x:c r="J39" s="75" t="n">
-        <x:f>IF(W69="估算",U69*MAX(0,R69-S69),"")</x:f>
-        <x:v>1.9785692162315183</x:v>
+        <x:f>IF(W69="",U69*MAX(0,R69-S69),"")</x:f>
+        <x:v>1.9788412626089436</x:v>
       </x:c>
       <x:c r="K39" s="75" t="n">
-        <x:f>IF(W69="估算",IF(OR(O69=0,K69=0),0,U69*E23*MIN(1,(K69+P69)/L69)),"")</x:f>
-        <x:v>890.9315148906668</x:v>
+        <x:f>IF(W69="",IF(OR(AK69=0,K69=0),0,U69*E23*MIN(1,(K69+AL69)/L69)),"")</x:f>
+        <x:v>890.944029024</x:v>
       </x:c>
       <x:c r="L39" s="34" t="n">
-        <x:f>IF(W69="估算",V69,"")</x:f>
-        <x:v>0.15261730349771457</x:v>
+        <x:f>IF(W69="",V69,"")</x:f>
+        <x:v>0.2872676606017531</x:v>
       </x:c>
       <x:c r="M39" s="34" t="n">
-        <x:f>IF(W69="估算",E39*V69/60,"")</x:f>
-        <x:v>0.025436217249619093</x:v>
+        <x:f>IF(W69="",E39*V69/60,"")</x:f>
+        <x:v>0.047877943433625524</x:v>
       </x:c>
       <x:c r="N39" s="34" t="n">
-        <x:f>IF(W69="估算",V69/60000*1e6,"")</x:f>
-        <x:v>2.5436217249619095</x:v>
+        <x:f>IF(W69="",V69/60000*1e6,"")</x:f>
+        <x:v>4.787794343362552</x:v>
       </x:c>
       <x:c r="O39" s="30" t="str">
-        <x:f>IF(W69="估算","相位平均估算",W69)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W69="","",W69)</x:f>
       </x:c>
       <x:c r="P39" s="49" t="n">
         <x:f>Q69</x:f>
-        <x:v>68.082944</x:v>
-      </x:c>
-      <x:c r="Q39" s="30"/>
-      <x:c r="R39" s="30"/>
-      <x:c r="S39" s="30"/>
-      <x:c r="T39" s="30"/>
+        <x:v>68.94574018544603</x:v>
+      </x:c>
+      <x:c r="Q39" s="102" t="n">
+        <x:f>AE69</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R39" s="102" t="n">
+        <x:f>AF69</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S39" s="102" t="n">
+        <x:f>IF(W69="",AI69,"")</x:f>
+        <x:v>0.15261730349771457</x:v>
+      </x:c>
+      <x:c r="T39" s="102" t="n">
+        <x:f>IF(W69="",AJ69,"")</x:f>
+        <x:v>0.13465035710403853</x:v>
+      </x:c>
       <x:c r="U39" s="30"/>
       <x:c r="V39" s="30"/>
       <x:c r="W39" s="30"/>
@@ -13728,45 +13994,56 @@
         <x:v>96.83884032</x:v>
       </x:c>
       <x:c r="H40" s="75" t="n">
-        <x:f>IF(W70="估算",U70*R70,"")</x:f>
-        <x:v>5.831149537449121</x:v>
+        <x:f>IF(W70="",U70*R70,"")</x:f>
+        <x:v>5.831217549043477</x:v>
       </x:c>
       <x:c r="I40" s="75" t="n">
-        <x:f>IF(W70="估算",U70*S70,"")</x:f>
-        <x:v>3.8527344945510356</x:v>
+        <x:f>IF(W70="",U70*S70,"")</x:f>
+        <x:v>3.8526664829566792</x:v>
       </x:c>
       <x:c r="J40" s="75" t="n">
-        <x:f>IF(W70="估算",U70*MAX(0,R70-S70),"")</x:f>
-        <x:v>1.9784150428980851</x:v>
+        <x:f>IF(W70="",U70*MAX(0,R70-S70),"")</x:f>
+        <x:v>1.9785510660867978</x:v>
       </x:c>
       <x:c r="K40" s="75" t="n">
-        <x:f>IF(W70="估算",IF(OR(O70=0,K70=0),0,U70*E23*MIN(1,(K70+P70)/L70)),"")</x:f>
-        <x:v>445.4657574453334</x:v>
+        <x:f>IF(W70="",IF(OR(AK70=0,K70=0),0,U70*E23*MIN(1,(K70+AL70)/L70)),"")</x:f>
+        <x:v>445.472014512</x:v>
       </x:c>
       <x:c r="L40" s="34" t="n">
-        <x:f>IF(W70="估算",V70,"")</x:f>
-        <x:v>0.07630865174885729</x:v>
+        <x:f>IF(W70="",V70,"")</x:f>
+        <x:v>0.14363383030087656</x:v>
       </x:c>
       <x:c r="M40" s="34" t="n">
-        <x:f>IF(W70="估算",E40*V70/60,"")</x:f>
-        <x:v>0.025436217249619093</x:v>
+        <x:f>IF(W70="",E40*V70/60,"")</x:f>
+        <x:v>0.047877943433625524</x:v>
       </x:c>
       <x:c r="N40" s="34" t="n">
-        <x:f>IF(W70="估算",V70/60000*1e6,"")</x:f>
-        <x:v>1.2718108624809548</x:v>
+        <x:f>IF(W70="",V70/60000*1e6,"")</x:f>
+        <x:v>2.393897171681276</x:v>
       </x:c>
       <x:c r="O40" s="30" t="str">
-        <x:f>IF(W70="估算","相位平均估算",W70)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W70="","",W70)</x:f>
       </x:c>
       <x:c r="P40" s="49" t="n">
         <x:f>Q70</x:f>
-        <x:v>34.041472</x:v>
-      </x:c>
-      <x:c r="Q40" s="30"/>
-      <x:c r="R40" s="30"/>
-      <x:c r="S40" s="30"/>
-      <x:c r="T40" s="30"/>
+        <x:v>34.25581290506786</x:v>
+      </x:c>
+      <x:c r="Q40" s="102" t="n">
+        <x:f>AE70</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R40" s="102" t="n">
+        <x:f>AF70</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S40" s="102" t="n">
+        <x:f>IF(W70="",AI70,"")</x:f>
+        <x:v>0.07630865174885729</x:v>
+      </x:c>
+      <x:c r="T40" s="102" t="n">
+        <x:f>IF(W70="",AJ70,"")</x:f>
+        <x:v>0.06732517855201926</x:v>
+      </x:c>
       <x:c r="U40" s="30"/>
       <x:c r="V40" s="30"/>
       <x:c r="W40" s="30"/>
@@ -13802,45 +14079,56 @@
         <x:v>96.83884032</x:v>
       </x:c>
       <x:c r="H41" s="75" t="n">
-        <x:f>IF(W71="估算",U71*R71,"")</x:f>
-        <x:v>4.2171431698938555</x:v>
+        <x:f>IF(W71="",U71*R71,"")</x:f>
+        <x:v>4.217188510956538</x:v>
       </x:c>
       <x:c r="I41" s="75" t="n">
-        <x:f>IF(W71="估算",U71*S71,"")</x:f>
-        <x:v>2.2387795181062486</x:v>
+        <x:f>IF(W71="",U71*S71,"")</x:f>
+        <x:v>2.2387341770435665</x:v>
       </x:c>
       <x:c r="J41" s="75" t="n">
-        <x:f>IF(W71="估算",U71*MAX(0,R71-S71),"")</x:f>
-        <x:v>1.9783636517876069</x:v>
+        <x:f>IF(W71="",U71*MAX(0,R71-S71),"")</x:f>
+        <x:v>1.9784543339129712</x:v>
       </x:c>
       <x:c r="K41" s="75" t="n">
-        <x:f>IF(W71="估算",IF(OR(O71=0,K71=0),0,U71*E23*MIN(1,(K71+P71)/L71)),"")</x:f>
-        <x:v>296.97717163022224</x:v>
+        <x:f>IF(W71="",IF(OR(AK71=0,K71=0),0,U71*E23*MIN(1,(K71+AL71)/L71)),"")</x:f>
+        <x:v>296.981343008</x:v>
       </x:c>
       <x:c r="L41" s="34" t="n">
-        <x:f>IF(W71="估算",V71,"")</x:f>
-        <x:v>0.05087243449923819</x:v>
+        <x:f>IF(W71="",V71,"")</x:f>
+        <x:v>0.09575588686725103</x:v>
       </x:c>
       <x:c r="M41" s="34" t="n">
-        <x:f>IF(W71="估算",E41*V71/60,"")</x:f>
-        <x:v>0.025436217249619093</x:v>
+        <x:f>IF(W71="",E41*V71/60,"")</x:f>
+        <x:v>0.04787794343362552</x:v>
       </x:c>
       <x:c r="N41" s="34" t="n">
-        <x:f>IF(W71="估算",V71/60000*1e6,"")</x:f>
-        <x:v>0.8478739083206365</x:v>
+        <x:f>IF(W71="",V71/60000*1e6,"")</x:f>
+        <x:v>1.5959314477875173</x:v>
       </x:c>
       <x:c r="O41" s="30" t="str">
-        <x:f>IF(W71="估算","相位平均估算",W71)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W71="","",W71)</x:f>
       </x:c>
       <x:c r="P41" s="49" t="n">
         <x:f>Q71</x:f>
-        <x:v>22.694314666666667</x:v>
-      </x:c>
-      <x:c r="Q41" s="30"/>
-      <x:c r="R41" s="30"/>
-      <x:c r="S41" s="30"/>
-      <x:c r="T41" s="30"/>
+        <x:v>22.789377770668615</x:v>
+      </x:c>
+      <x:c r="Q41" s="102" t="n">
+        <x:f>AE71</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R41" s="102" t="n">
+        <x:f>AF71</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S41" s="102" t="n">
+        <x:f>IF(W71="",AI71,"")</x:f>
+        <x:v>0.05087243449923819</x:v>
+      </x:c>
+      <x:c r="T41" s="102" t="n">
+        <x:f>IF(W71="",AJ71,"")</x:f>
+        <x:v>0.04488345236801285</x:v>
+      </x:c>
       <x:c r="U41" s="30"/>
       <x:c r="V41" s="30"/>
       <x:c r="W41" s="30"/>
@@ -13876,45 +14164,56 @@
         <x:v>1.7120256</x:v>
       </x:c>
       <x:c r="H42" s="75" t="n">
-        <x:f>IF(W72="估算",U72*R72,"")</x:f>
-        <x:v>19.97779162173874</x:v>
+        <x:f>IF(W72="",U72*R72,"")</x:f>
+        <x:v>19.981872317390792</x:v>
       </x:c>
       <x:c r="I42" s="75" t="n">
-        <x:f>IF(W72="估算",U72*S72,"")</x:f>
+        <x:f>IF(W72="",U72*S72,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J42" s="75" t="n">
-        <x:f>IF(W72="估算",U72*MAX(0,R72-S72),"")</x:f>
-        <x:v>19.97779162173874</x:v>
+        <x:f>IF(W72="",U72*MAX(0,R72-S72),"")</x:f>
+        <x:v>19.981872317390792</x:v>
       </x:c>
       <x:c r="K42" s="75" t="n">
-        <x:f>IF(W72="估算",IF(OR(O72=0,K72=0),0,U72*E24*MIN(1,(K72+P72)/L72)),"")</x:f>
-        <x:v>472.95682919999996</x:v>
+        <x:f>IF(W72="",IF(OR(AK72=0,K72=0),0,U72*E24*MIN(1,(K72+AL72)/L72)),"")</x:f>
+        <x:v>473.3322532</x:v>
       </x:c>
       <x:c r="L42" s="34" t="n">
-        <x:f>IF(W72="估算",V72,"")</x:f>
-        <x:v>0.08326932396432667</x:v>
+        <x:f>IF(W72="",V72,"")</x:f>
+        <x:v>0.15468122714756344</x:v>
       </x:c>
       <x:c r="M42" s="34" t="n">
-        <x:f>IF(W72="估算",E42*V72/60,"")</x:f>
-        <x:v>0.006939110330360556</x:v>
+        <x:f>IF(W72="",E42*V72/60,"")</x:f>
+        <x:v>0.012890102262296954</x:v>
       </x:c>
       <x:c r="N42" s="34" t="n">
-        <x:f>IF(W72="估算",V72/60000*1e6,"")</x:f>
-        <x:v>1.3878220660721112</x:v>
+        <x:f>IF(W72="",V72/60000*1e6,"")</x:f>
+        <x:v>2.578020452459391</x:v>
       </x:c>
       <x:c r="O42" s="30" t="str">
-        <x:f>IF(W72="估算","相位平均估算",W72)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W72="","",W72)</x:f>
       </x:c>
       <x:c r="P42" s="49" t="n">
         <x:f>Q72</x:f>
-        <x:v>140.084352</x:v>
-      </x:c>
-      <x:c r="Q42" s="30"/>
-      <x:c r="R42" s="30"/>
-      <x:c r="S42" s="30"/>
-      <x:c r="T42" s="30"/>
+        <x:v>143.68042396579565</x:v>
+      </x:c>
+      <x:c r="Q42" s="102" t="n">
+        <x:f>AE72</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R42" s="102" t="n">
+        <x:f>AF72</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S42" s="102" t="n">
+        <x:f>IF(W72="",AI72,"")</x:f>
+        <x:v>0.08326932396432667</x:v>
+      </x:c>
+      <x:c r="T42" s="102" t="n">
+        <x:f>IF(W72="",AJ72,"")</x:f>
+        <x:v>0.07141190318323679</x:v>
+      </x:c>
       <x:c r="U42" s="30"/>
       <x:c r="V42" s="30"/>
       <x:c r="W42" s="30"/>
@@ -13950,45 +14249,56 @@
         <x:v>1.7120256</x:v>
       </x:c>
       <x:c r="H43" s="75" t="n">
-        <x:f>IF(W73="估算",U73*R73,"")</x:f>
-        <x:v>17.407374071739312</x:v>
+        <x:f>IF(W73="",U73*R73,"")</x:f>
+        <x:v>17.409414419565337</x:v>
       </x:c>
       <x:c r="I43" s="75" t="n">
-        <x:f>IF(W73="估算",U73*S73,"")</x:f>
+        <x:f>IF(W73="",U73*S73,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J43" s="75" t="n">
-        <x:f>IF(W73="估算",U73*MAX(0,R73-S73),"")</x:f>
-        <x:v>17.407374071739312</x:v>
+        <x:f>IF(W73="",U73*MAX(0,R73-S73),"")</x:f>
+        <x:v>17.409414419565337</x:v>
       </x:c>
       <x:c r="K43" s="75" t="n">
-        <x:f>IF(W73="估算",IF(OR(O73=0,K73=0),0,U73*E24*MIN(1,(K73+P73)/L73)),"")</x:f>
-        <x:v>236.47841459999998</x:v>
+        <x:f>IF(W73="",IF(OR(AK73=0,K73=0),0,U73*E24*MIN(1,(K73+AL73)/L73)),"")</x:f>
+        <x:v>236.6661266</x:v>
       </x:c>
       <x:c r="L43" s="34" t="n">
-        <x:f>IF(W73="估算",V73,"")</x:f>
-        <x:v>0.04163466198216333</x:v>
+        <x:f>IF(W73="",V73,"")</x:f>
+        <x:v>0.07734061357378172</x:v>
       </x:c>
       <x:c r="M43" s="34" t="n">
-        <x:f>IF(W73="估算",E43*V73/60,"")</x:f>
-        <x:v>0.006939110330360556</x:v>
+        <x:f>IF(W73="",E43*V73/60,"")</x:f>
+        <x:v>0.012890102262296954</x:v>
       </x:c>
       <x:c r="N43" s="34" t="n">
-        <x:f>IF(W73="估算",V73/60000*1e6,"")</x:f>
-        <x:v>0.6939110330360556</x:v>
+        <x:f>IF(W73="",V73/60000*1e6,"")</x:f>
+        <x:v>1.2890102262296954</x:v>
       </x:c>
       <x:c r="O43" s="30" t="str">
-        <x:f>IF(W73="估算","相位平均估算",W73)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W73="","",W73)</x:f>
       </x:c>
       <x:c r="P43" s="49" t="n">
         <x:f>Q73</x:f>
-        <x:v>70.042176</x:v>
-      </x:c>
-      <x:c r="Q43" s="30"/>
-      <x:c r="R43" s="30"/>
-      <x:c r="S43" s="30"/>
-      <x:c r="T43" s="30"/>
+        <x:v>70.92980098685632</x:v>
+      </x:c>
+      <x:c r="Q43" s="102" t="n">
+        <x:f>AE73</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R43" s="102" t="n">
+        <x:f>AF73</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S43" s="102" t="n">
+        <x:f>IF(W73="",AI73,"")</x:f>
+        <x:v>0.04163466198216333</x:v>
+      </x:c>
+      <x:c r="T43" s="102" t="n">
+        <x:f>IF(W73="",AJ73,"")</x:f>
+        <x:v>0.03570595159161839</x:v>
+      </x:c>
       <x:c r="U43" s="30"/>
       <x:c r="V43" s="30"/>
       <x:c r="W43" s="30"/>
@@ -14024,45 +14334,56 @@
         <x:v>1.7120256</x:v>
       </x:c>
       <x:c r="H44" s="75" t="n">
-        <x:f>IF(W74="估算",U74*R74,"")</x:f>
-        <x:v>16.122165296738935</x:v>
+        <x:f>IF(W74="",U74*R74,"")</x:f>
+        <x:v>16.123185470651947</x:v>
       </x:c>
       <x:c r="I44" s="75" t="n">
-        <x:f>IF(W74="估算",U74*S74,"")</x:f>
+        <x:f>IF(W74="",U74*S74,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J44" s="75" t="n">
-        <x:f>IF(W74="估算",U74*MAX(0,R74-S74),"")</x:f>
-        <x:v>16.122165296738935</x:v>
+        <x:f>IF(W74="",U74*MAX(0,R74-S74),"")</x:f>
+        <x:v>16.123185470651947</x:v>
       </x:c>
       <x:c r="K44" s="75" t="n">
-        <x:f>IF(W74="估算",IF(OR(O74=0,K74=0),0,U74*E24*MIN(1,(K74+P74)/L74)),"")</x:f>
-        <x:v>118.23920729999999</x:v>
+        <x:f>IF(W74="",IF(OR(AK74=0,K74=0),0,U74*E24*MIN(1,(K74+AL74)/L74)),"")</x:f>
+        <x:v>118.3330633</x:v>
       </x:c>
       <x:c r="L44" s="34" t="n">
-        <x:f>IF(W74="估算",V74,"")</x:f>
-        <x:v>0.020817330991081667</x:v>
+        <x:f>IF(W74="",V74,"")</x:f>
+        <x:v>0.03867030678689086</x:v>
       </x:c>
       <x:c r="M44" s="34" t="n">
-        <x:f>IF(W74="估算",E44*V74/60,"")</x:f>
-        <x:v>0.006939110330360556</x:v>
+        <x:f>IF(W74="",E44*V74/60,"")</x:f>
+        <x:v>0.012890102262296954</x:v>
       </x:c>
       <x:c r="N44" s="34" t="n">
-        <x:f>IF(W74="估算",V74/60000*1e6,"")</x:f>
-        <x:v>0.3469555165180278</x:v>
+        <x:f>IF(W74="",V74/60000*1e6,"")</x:f>
+        <x:v>0.6445051131148477</x:v>
       </x:c>
       <x:c r="O44" s="30" t="str">
-        <x:f>IF(W74="估算","相位平均估算",W74)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W74="","",W74)</x:f>
       </x:c>
       <x:c r="P44" s="49" t="n">
         <x:f>Q74</x:f>
-        <x:v>35.021088</x:v>
-      </x:c>
-      <x:c r="Q44" s="30"/>
-      <x:c r="R44" s="30"/>
-      <x:c r="S44" s="30"/>
-      <x:c r="T44" s="30"/>
+        <x:v>35.24159702200649</x:v>
+      </x:c>
+      <x:c r="Q44" s="102" t="n">
+        <x:f>AE74</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R44" s="102" t="n">
+        <x:f>AF74</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S44" s="102" t="n">
+        <x:f>IF(W74="",AI74,"")</x:f>
+        <x:v>0.020817330991081667</x:v>
+      </x:c>
+      <x:c r="T44" s="102" t="n">
+        <x:f>IF(W74="",AJ74,"")</x:f>
+        <x:v>0.017852975795809196</x:v>
+      </x:c>
       <x:c r="U44" s="30"/>
       <x:c r="V44" s="30"/>
       <x:c r="W44" s="30"/>
@@ -14098,45 +14419,56 @@
         <x:v>1.7120256</x:v>
       </x:c>
       <x:c r="H45" s="75" t="n">
-        <x:f>IF(W75="估算",U75*R75,"")</x:f>
-        <x:v>15.693762371739028</x:v>
+        <x:f>IF(W75="",U75*R75,"")</x:f>
+        <x:v>15.694442487681037</x:v>
       </x:c>
       <x:c r="I45" s="75" t="n">
-        <x:f>IF(W75="估算",U75*S75,"")</x:f>
+        <x:f>IF(W75="",U75*S75,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J45" s="75" t="n">
-        <x:f>IF(W75="估算",U75*MAX(0,R75-S75),"")</x:f>
-        <x:v>15.693762371739028</x:v>
+        <x:f>IF(W75="",U75*MAX(0,R75-S75),"")</x:f>
+        <x:v>15.694442487681037</x:v>
       </x:c>
       <x:c r="K45" s="75" t="n">
-        <x:f>IF(W75="估算",IF(OR(O75=0,K75=0),0,U75*E24*MIN(1,(K75+P75)/L75)),"")</x:f>
-        <x:v>78.82613819999999</x:v>
+        <x:f>IF(W75="",IF(OR(AK75=0,K75=0),0,U75*E24*MIN(1,(K75+AL75)/L75)),"")</x:f>
+        <x:v>78.88870886666668</x:v>
       </x:c>
       <x:c r="L45" s="34" t="n">
-        <x:f>IF(W75="估算",V75,"")</x:f>
-        <x:v>0.013878220660721112</x:v>
+        <x:f>IF(W75="",V75,"")</x:f>
+        <x:v>0.02578020452459391</x:v>
       </x:c>
       <x:c r="M45" s="34" t="n">
-        <x:f>IF(W75="估算",E45*V75/60,"")</x:f>
-        <x:v>0.006939110330360556</x:v>
+        <x:f>IF(W75="",E45*V75/60,"")</x:f>
+        <x:v>0.012890102262296955</x:v>
       </x:c>
       <x:c r="N45" s="34" t="n">
-        <x:f>IF(W75="估算",V75/60000*1e6,"")</x:f>
-        <x:v>0.23130367767868518</x:v>
+        <x:f>IF(W75="",V75/60000*1e6,"")</x:f>
+        <x:v>0.42967007540989854</x:v>
       </x:c>
       <x:c r="O45" s="30" t="str">
-        <x:f>IF(W75="估算","相位平均估算",W75)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W75="","",W75)</x:f>
       </x:c>
       <x:c r="P45" s="49" t="n">
         <x:f>Q75</x:f>
-        <x:v>23.347392</x:v>
-      </x:c>
-      <x:c r="Q45" s="30"/>
-      <x:c r="R45" s="30"/>
-      <x:c r="S45" s="30"/>
-      <x:c r="T45" s="30"/>
+        <x:v>23.445190747680634</x:v>
+      </x:c>
+      <x:c r="Q45" s="102" t="n">
+        <x:f>AE75</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R45" s="102" t="n">
+        <x:f>AF75</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S45" s="102" t="n">
+        <x:f>IF(W75="",AI75,"")</x:f>
+        <x:v>0.013878220660721112</x:v>
+      </x:c>
+      <x:c r="T45" s="102" t="n">
+        <x:f>IF(W75="",AJ75,"")</x:f>
+        <x:v>0.011901983863872798</x:v>
+      </x:c>
       <x:c r="U45" s="30"/>
       <x:c r="V45" s="30"/>
       <x:c r="W45" s="30"/>
@@ -14172,45 +14504,56 @@
         <x:v>24.3612672</x:v>
       </x:c>
       <x:c r="H46" s="75" t="n">
-        <x:f>IF(W76="估算",U76*R76,"")</x:f>
-        <x:v>17.585103284347703</x:v>
+        <x:f>IF(W76="",U76*R76,"")</x:f>
+        <x:v>17.58591942347998</x:v>
       </x:c>
       <x:c r="I46" s="75" t="n">
-        <x:f>IF(W76="估算",U76*S76,"")</x:f>
-        <x:v>11.64841735565414</x:v>
+        <x:f>IF(W76="",U76*S76,"")</x:f>
+        <x:v>11.647601216521863</x:v>
       </x:c>
       <x:c r="J46" s="75" t="n">
-        <x:f>IF(W76="估算",U76*MAX(0,R76-S76),"")</x:f>
-        <x:v>5.936685928693564</x:v>
+        <x:f>IF(W76="",U76*MAX(0,R76-S76),"")</x:f>
+        <x:v>5.938318206958115</x:v>
       </x:c>
       <x:c r="K46" s="75" t="n">
-        <x:f>IF(W76="估算",IF(OR(O76=0,K76=0),0,U76*E24*MIN(1,(K76+P76)/L76)),"")</x:f>
-        <x:v>1344.8295021600002</x:v>
+        <x:f>IF(W76="",IF(OR(AK76=0,K76=0),0,U76*E24*MIN(1,(K76+AL76)/L76)),"")</x:f>
+        <x:v>1344.90458696</x:v>
       </x:c>
       <x:c r="L46" s="34" t="n">
-        <x:f>IF(W76="估算",V76,"")</x:f>
-        <x:v>0.23698749901699329</x:v>
+        <x:f>IF(W76="",V76,"")</x:f>
+        <x:v>0.4402269658411606</x:v>
       </x:c>
       <x:c r="M46" s="34" t="n">
-        <x:f>IF(W76="估算",E46*V76/60,"")</x:f>
-        <x:v>0.019748958251416107</x:v>
+        <x:f>IF(W76="",E46*V76/60,"")</x:f>
+        <x:v>0.03668558048676339</x:v>
       </x:c>
       <x:c r="N46" s="34" t="n">
-        <x:f>IF(W76="估算",V76/60000*1e6,"")</x:f>
-        <x:v>3.9497916502832213</x:v>
+        <x:f>IF(W76="",V76/60000*1e6,"")</x:f>
+        <x:v>7.337116097352677</x:v>
       </x:c>
       <x:c r="O46" s="30" t="str">
-        <x:f>IF(W76="估算","相位平均估算",W76)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W76="","",W76)</x:f>
       </x:c>
       <x:c r="P46" s="49" t="n">
         <x:f>Q76</x:f>
-        <x:v>140.084352</x:v>
-      </x:c>
-      <x:c r="Q46" s="30"/>
-      <x:c r="R46" s="30"/>
-      <x:c r="S46" s="30"/>
-      <x:c r="T46" s="30"/>
+        <x:v>143.68042396579565</x:v>
+      </x:c>
+      <x:c r="Q46" s="102" t="n">
+        <x:f>AE76</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R46" s="102" t="n">
+        <x:f>AF76</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S46" s="102" t="n">
+        <x:f>IF(W76="",AI76,"")</x:f>
+        <x:v>0.23698749901699329</x:v>
+      </x:c>
+      <x:c r="T46" s="102" t="n">
+        <x:f>IF(W76="",AJ76,"")</x:f>
+        <x:v>0.20323946682416733</x:v>
+      </x:c>
       <x:c r="U46" s="30"/>
       <x:c r="V46" s="30"/>
       <x:c r="W46" s="30"/>
@@ -14246,45 +14589,56 @@
         <x:v>24.3612672</x:v>
       </x:c>
       <x:c r="H47" s="75" t="n">
-        <x:f>IF(W77="估算",U77*R77,"")</x:f>
-        <x:v>10.276247294348506</x:v>
+        <x:f>IF(W77="",U77*R77,"")</x:f>
+        <x:v>10.276655363913312</x:v>
       </x:c>
       <x:c r="I47" s="75" t="n">
-        <x:f>IF(W77="估算",U77*S77,"")</x:f>
-        <x:v>4.340513025652415</x:v>
+        <x:f>IF(W77="",U77*S77,"")</x:f>
+        <x:v>4.340104956087609</x:v>
       </x:c>
       <x:c r="J47" s="75" t="n">
-        <x:f>IF(W77="估算",U77*MAX(0,R77-S77),"")</x:f>
-        <x:v>5.935734268696091</x:v>
+        <x:f>IF(W77="",U77*MAX(0,R77-S77),"")</x:f>
+        <x:v>5.9365504078257025</x:v>
       </x:c>
       <x:c r="K47" s="75" t="n">
-        <x:f>IF(W77="估算",IF(OR(O77=0,K77=0),0,U77*E24*MIN(1,(K77+P77)/L77)),"")</x:f>
-        <x:v>672.4147510800001</x:v>
+        <x:f>IF(W77="",IF(OR(AK77=0,K77=0),0,U77*E24*MIN(1,(K77+AL77)/L77)),"")</x:f>
+        <x:v>672.45229348</x:v>
       </x:c>
       <x:c r="L47" s="34" t="n">
-        <x:f>IF(W77="估算",V77,"")</x:f>
-        <x:v>0.11849374950849664</x:v>
+        <x:f>IF(W77="",V77,"")</x:f>
+        <x:v>0.2201134829205803</x:v>
       </x:c>
       <x:c r="M47" s="34" t="n">
-        <x:f>IF(W77="估算",E47*V77/60,"")</x:f>
-        <x:v>0.019748958251416107</x:v>
+        <x:f>IF(W77="",E47*V77/60,"")</x:f>
+        <x:v>0.03668558048676339</x:v>
       </x:c>
       <x:c r="N47" s="34" t="n">
-        <x:f>IF(W77="估算",V77/60000*1e6,"")</x:f>
-        <x:v>1.9748958251416107</x:v>
+        <x:f>IF(W77="",V77/60000*1e6,"")</x:f>
+        <x:v>3.6685580486763385</x:v>
       </x:c>
       <x:c r="O47" s="30" t="str">
-        <x:f>IF(W77="估算","相位平均估算",W77)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W77="","",W77)</x:f>
       </x:c>
       <x:c r="P47" s="49" t="n">
         <x:f>Q77</x:f>
-        <x:v>70.042176</x:v>
-      </x:c>
-      <x:c r="Q47" s="30"/>
-      <x:c r="R47" s="30"/>
-      <x:c r="S47" s="30"/>
-      <x:c r="T47" s="30"/>
+        <x:v>70.92980098685632</x:v>
+      </x:c>
+      <x:c r="Q47" s="102" t="n">
+        <x:f>AE77</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R47" s="102" t="n">
+        <x:f>AF77</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S47" s="102" t="n">
+        <x:f>IF(W77="",AI77,"")</x:f>
+        <x:v>0.11849374950849664</x:v>
+      </x:c>
+      <x:c r="T47" s="102" t="n">
+        <x:f>IF(W77="",AJ77,"")</x:f>
+        <x:v>0.10161973341208366</x:v>
+      </x:c>
       <x:c r="U47" s="30"/>
       <x:c r="V47" s="30"/>
       <x:c r="W47" s="30"/>
@@ -14320,45 +14674,56 @@
         <x:v>24.3612672</x:v>
       </x:c>
       <x:c r="H48" s="75" t="n">
-        <x:f>IF(W78="估算",U78*R78,"")</x:f>
-        <x:v>6.621819299347909</x:v>
+        <x:f>IF(W78="",U78*R78,"")</x:f>
+        <x:v>6.622023334130311</x:v>
       </x:c>
       <x:c r="I48" s="75" t="n">
-        <x:f>IF(W78="估算",U78*S78,"")</x:f>
-        <x:v>0.686560860652552</x:v>
+        <x:f>IF(W78="",U78*S78,"")</x:f>
+        <x:v>0.6863568258701491</x:v>
       </x:c>
       <x:c r="J48" s="75" t="n">
-        <x:f>IF(W78="估算",U78*MAX(0,R78-S78),"")</x:f>
-        <x:v>5.935258438695357</x:v>
+        <x:f>IF(W78="",U78*MAX(0,R78-S78),"")</x:f>
+        <x:v>5.935666508260162</x:v>
       </x:c>
       <x:c r="K48" s="75" t="n">
-        <x:f>IF(W78="估算",IF(OR(O78=0,K78=0),0,U78*E24*MIN(1,(K78+P78)/L78)),"")</x:f>
-        <x:v>336.20737554000004</x:v>
+        <x:f>IF(W78="",IF(OR(AK78=0,K78=0),0,U78*E24*MIN(1,(K78+AL78)/L78)),"")</x:f>
+        <x:v>336.22614674</x:v>
       </x:c>
       <x:c r="L48" s="34" t="n">
-        <x:f>IF(W78="估算",V78,"")</x:f>
-        <x:v>0.05924687475424832</x:v>
+        <x:f>IF(W78="",V78,"")</x:f>
+        <x:v>0.11005674146029015</x:v>
       </x:c>
       <x:c r="M48" s="34" t="n">
-        <x:f>IF(W78="估算",E48*V78/60,"")</x:f>
-        <x:v>0.019748958251416107</x:v>
+        <x:f>IF(W78="",E48*V78/60,"")</x:f>
+        <x:v>0.03668558048676339</x:v>
       </x:c>
       <x:c r="N48" s="34" t="n">
-        <x:f>IF(W78="估算",V78/60000*1e6,"")</x:f>
-        <x:v>0.9874479125708053</x:v>
+        <x:f>IF(W78="",V78/60000*1e6,"")</x:f>
+        <x:v>1.8342790243381693</x:v>
       </x:c>
       <x:c r="O48" s="30" t="str">
-        <x:f>IF(W78="估算","相位平均估算",W78)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W78="","",W78)</x:f>
       </x:c>
       <x:c r="P48" s="49" t="n">
         <x:f>Q78</x:f>
-        <x:v>35.021088</x:v>
-      </x:c>
-      <x:c r="Q48" s="30"/>
-      <x:c r="R48" s="30"/>
-      <x:c r="S48" s="30"/>
-      <x:c r="T48" s="30"/>
+        <x:v>35.24159702200649</x:v>
+      </x:c>
+      <x:c r="Q48" s="102" t="n">
+        <x:f>AE78</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R48" s="102" t="n">
+        <x:f>AF78</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S48" s="102" t="n">
+        <x:f>IF(W78="",AI78,"")</x:f>
+        <x:v>0.05924687475424832</x:v>
+      </x:c>
+      <x:c r="T48" s="102" t="n">
+        <x:f>IF(W78="",AJ78,"")</x:f>
+        <x:v>0.05080986670604183</x:v>
+      </x:c>
       <x:c r="U48" s="30"/>
       <x:c r="V48" s="30"/>
       <x:c r="W48" s="30"/>
@@ -14394,45 +14759,56 @@
         <x:v>24.3612672</x:v>
       </x:c>
       <x:c r="H49" s="75" t="n">
-        <x:f>IF(W79="估算",U79*R79,"")</x:f>
-        <x:v>5.4036766343481535</x:v>
+        <x:f>IF(W79="",U79*R79,"")</x:f>
+        <x:v>5.403812657536422</x:v>
       </x:c>
       <x:c r="I49" s="75" t="n">
-        <x:f>IF(W79="估算",U79*S79,"")</x:f>
+        <x:f>IF(W79="",U79*S79,"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="J49" s="75" t="n">
-        <x:f>IF(W79="估算",U79*MAX(0,R79-S79),"")</x:f>
-        <x:v>5.4036766343481535</x:v>
+        <x:f>IF(W79="",U79*MAX(0,R79-S79),"")</x:f>
+        <x:v>5.403812657536422</x:v>
       </x:c>
       <x:c r="K49" s="75" t="n">
-        <x:f>IF(W79="估算",IF(OR(O79=0,K79=0),0,U79*E24*MIN(1,(K79+P79)/L79)),"")</x:f>
-        <x:v>224.13825036000003</x:v>
+        <x:f>IF(W79="",IF(OR(AK79=0,K79=0),0,U79*E24*MIN(1,(K79+AL79)/L79)),"")</x:f>
+        <x:v>224.15076449333333</x:v>
       </x:c>
       <x:c r="L49" s="34" t="n">
-        <x:f>IF(W79="估算",V79,"")</x:f>
-        <x:v>0.039497916502832214</x:v>
+        <x:f>IF(W79="",V79,"")</x:f>
+        <x:v>0.07337116097352676</x:v>
       </x:c>
       <x:c r="M49" s="34" t="n">
-        <x:f>IF(W79="估算",E49*V79/60,"")</x:f>
-        <x:v>0.019748958251416107</x:v>
+        <x:f>IF(W79="",E49*V79/60,"")</x:f>
+        <x:v>0.03668558048676338</x:v>
       </x:c>
       <x:c r="N49" s="34" t="n">
-        <x:f>IF(W79="估算",V79/60000*1e6,"")</x:f>
-        <x:v>0.6582986083805369</x:v>
+        <x:f>IF(W79="",V79/60000*1e6,"")</x:f>
+        <x:v>1.2228526828921127</x:v>
       </x:c>
       <x:c r="O49" s="30" t="str">
-        <x:f>IF(W79="估算","相位平均估算",W79)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W79="","",W79)</x:f>
       </x:c>
       <x:c r="P49" s="49" t="n">
         <x:f>Q79</x:f>
-        <x:v>23.347392</x:v>
-      </x:c>
-      <x:c r="Q49" s="30"/>
-      <x:c r="R49" s="30"/>
-      <x:c r="S49" s="30"/>
-      <x:c r="T49" s="30"/>
+        <x:v>23.445190747680634</x:v>
+      </x:c>
+      <x:c r="Q49" s="102" t="n">
+        <x:f>AE79</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R49" s="102" t="n">
+        <x:f>AF79</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S49" s="102" t="n">
+        <x:f>IF(W79="",AI79,"")</x:f>
+        <x:v>0.039497916502832214</x:v>
+      </x:c>
+      <x:c r="T49" s="102" t="n">
+        <x:f>IF(W79="",AJ79,"")</x:f>
+        <x:v>0.03387324447069455</x:v>
+      </x:c>
       <x:c r="U49" s="30"/>
       <x:c r="V49" s="30"/>
       <x:c r="W49" s="30"/>
@@ -14468,45 +14844,56 @@
         <x:v>96.83884032</x:v>
       </x:c>
       <x:c r="H50" s="75" t="n">
-        <x:f>IF(W80="估算",U80*R80,"")</x:f>
-        <x:v>20.357215718782573</x:v>
+        <x:f>IF(W80="",U80*R80,"")</x:f>
+        <x:v>20.35748776516</x:v>
       </x:c>
       <x:c r="I50" s="75" t="n">
-        <x:f>IF(W80="估算",U80*S80,"")</x:f>
-        <x:v>18.378320409218052</x:v>
+        <x:f>IF(W80="",U80*S80,"")</x:f>
+        <x:v>18.378048362840627</x:v>
       </x:c>
       <x:c r="J50" s="75" t="n">
-        <x:f>IF(W80="估算",U80*MAX(0,R80-S80),"")</x:f>
-        <x:v>1.9788953095645212</x:v>
+        <x:f>IF(W80="",U80*MAX(0,R80-S80),"")</x:f>
+        <x:v>1.9794394023193718</x:v>
       </x:c>
       <x:c r="K50" s="75" t="n">
-        <x:f>IF(W80="估算",IF(OR(O80=0,K80=0),0,U80*E24*MIN(1,(K80+P80)/L80)),"")</x:f>
-        <x:v>1781.863846128</x:v>
+        <x:f>IF(W80="",IF(OR(AK80=0,K80=0),0,U80*E24*MIN(1,(K80+AL80)/L80)),"")</x:f>
+        <x:v>1781.8888743946668</x:v>
       </x:c>
       <x:c r="L50" s="34" t="n">
-        <x:f>IF(W80="估算",V80,"")</x:f>
-        <x:v>0.3140183761780676</x:v>
+        <x:f>IF(W80="",V80,"")</x:f>
+        <x:v>0.5833190903861447</x:v>
       </x:c>
       <x:c r="M50" s="34" t="n">
-        <x:f>IF(W80="估算",E50*V80/60,"")</x:f>
-        <x:v>0.02616819801483897</x:v>
+        <x:f>IF(W80="",E50*V80/60,"")</x:f>
+        <x:v>0.04860992419884539</x:v>
       </x:c>
       <x:c r="N50" s="34" t="n">
-        <x:f>IF(W80="估算",V80/60000*1e6,"")</x:f>
-        <x:v>5.233639602967793</x:v>
+        <x:f>IF(W80="",V80/60000*1e6,"")</x:f>
+        <x:v>9.721984839769078</x:v>
       </x:c>
       <x:c r="O50" s="30" t="str">
-        <x:f>IF(W80="估算","相位平均估算",W80)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W80="","",W80)</x:f>
       </x:c>
       <x:c r="P50" s="49" t="n">
         <x:f>Q80</x:f>
-        <x:v>140.084352</x:v>
-      </x:c>
-      <x:c r="Q50" s="30"/>
-      <x:c r="R50" s="30"/>
-      <x:c r="S50" s="30"/>
-      <x:c r="T50" s="30"/>
+        <x:v>143.68042396579565</x:v>
+      </x:c>
+      <x:c r="Q50" s="102" t="n">
+        <x:f>AE80</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R50" s="102" t="n">
+        <x:f>AF80</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S50" s="102" t="n">
+        <x:f>IF(W80="",AI80,"")</x:f>
+        <x:v>0.3140183761780676</x:v>
+      </x:c>
+      <x:c r="T50" s="102" t="n">
+        <x:f>IF(W80="",AJ80,"")</x:f>
+        <x:v>0.26930071420807705</x:v>
+      </x:c>
       <x:c r="U50" s="30"/>
       <x:c r="V50" s="30"/>
       <x:c r="W50" s="30"/>
@@ -14542,45 +14929,56 @@
         <x:v>96.83884032</x:v>
       </x:c>
       <x:c r="H51" s="75" t="n">
-        <x:f>IF(W81="估算",U81*R81,"")</x:f>
-        <x:v>10.673173076782616</x:v>
+        <x:f>IF(W81="",U81*R81,"")</x:f>
+        <x:v>10.673309099971329</x:v>
       </x:c>
       <x:c r="I51" s="75" t="n">
-        <x:f>IF(W81="估算",U81*S81,"")</x:f>
-        <x:v>8.694594987217696</x:v>
+        <x:f>IF(W81="",U81*S81,"")</x:f>
+        <x:v>8.694458964028984</x:v>
       </x:c>
       <x:c r="J51" s="75" t="n">
-        <x:f>IF(W81="估算",U81*MAX(0,R81-S81),"")</x:f>
-        <x:v>1.9785780895649197</x:v>
+        <x:f>IF(W81="",U81*MAX(0,R81-S81),"")</x:f>
+        <x:v>1.978850135942345</x:v>
       </x:c>
       <x:c r="K51" s="75" t="n">
-        <x:f>IF(W81="估算",IF(OR(O81=0,K81=0),0,U81*E24*MIN(1,(K81+P81)/L81)),"")</x:f>
-        <x:v>890.931923064</x:v>
+        <x:f>IF(W81="",IF(OR(AK81=0,K81=0),0,U81*E24*MIN(1,(K81+AL81)/L81)),"")</x:f>
+        <x:v>890.9444371973334</x:v>
       </x:c>
       <x:c r="L51" s="34" t="n">
-        <x:f>IF(W81="估算",V81,"")</x:f>
-        <x:v>0.1570091880890338</x:v>
+        <x:f>IF(W81="",V81,"")</x:f>
+        <x:v>0.29165954519307236</x:v>
       </x:c>
       <x:c r="M51" s="34" t="n">
-        <x:f>IF(W81="估算",E51*V81/60,"")</x:f>
-        <x:v>0.02616819801483897</x:v>
+        <x:f>IF(W81="",E51*V81/60,"")</x:f>
+        <x:v>0.04860992419884539</x:v>
       </x:c>
       <x:c r="N51" s="34" t="n">
-        <x:f>IF(W81="估算",V81/60000*1e6,"")</x:f>
-        <x:v>2.6168198014838966</x:v>
+        <x:f>IF(W81="",V81/60000*1e6,"")</x:f>
+        <x:v>4.860992419884539</x:v>
       </x:c>
       <x:c r="O51" s="30" t="str">
-        <x:f>IF(W81="估算","相位平均估算",W81)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W81="","",W81)</x:f>
       </x:c>
       <x:c r="P51" s="49" t="n">
         <x:f>Q81</x:f>
-        <x:v>70.042176</x:v>
-      </x:c>
-      <x:c r="Q51" s="30"/>
-      <x:c r="R51" s="30"/>
-      <x:c r="S51" s="30"/>
-      <x:c r="T51" s="30"/>
+        <x:v>70.92980098685632</x:v>
+      </x:c>
+      <x:c r="Q51" s="102" t="n">
+        <x:f>AE81</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R51" s="102" t="n">
+        <x:f>AF81</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S51" s="102" t="n">
+        <x:f>IF(W81="",AI81,"")</x:f>
+        <x:v>0.1570091880890338</x:v>
+      </x:c>
+      <x:c r="T51" s="102" t="n">
+        <x:f>IF(W81="",AJ81,"")</x:f>
+        <x:v>0.13465035710403853</x:v>
+      </x:c>
       <x:c r="U51" s="30"/>
       <x:c r="V51" s="30"/>
       <x:c r="W51" s="30"/>
@@ -14616,45 +15014,56 @@
         <x:v>96.83884032</x:v>
       </x:c>
       <x:c r="H52" s="75" t="n">
-        <x:f>IF(W82="估算",U82*R82,"")</x:f>
-        <x:v>5.831151755782638</x:v>
+        <x:f>IF(W82="",U82*R82,"")</x:f>
+        <x:v>5.831219767376661</x:v>
       </x:c>
       <x:c r="I52" s="75" t="n">
-        <x:f>IF(W82="估算",U82*S82,"")</x:f>
-        <x:v>3.8527322762171856</x:v>
+        <x:f>IF(W82="",U82*S82,"")</x:f>
+        <x:v>3.8526642646231624</x:v>
       </x:c>
       <x:c r="J52" s="75" t="n">
-        <x:f>IF(W82="估算",U82*MAX(0,R82-S82),"")</x:f>
-        <x:v>1.978419479565452</x:v>
+        <x:f>IF(W82="",U82*MAX(0,R82-S82),"")</x:f>
+        <x:v>1.9785555027534985</x:v>
       </x:c>
       <x:c r="K52" s="75" t="n">
-        <x:f>IF(W82="估算",IF(OR(O82=0,K82=0),0,U82*E24*MIN(1,(K82+P82)/L82)),"")</x:f>
-        <x:v>445.465961532</x:v>
+        <x:f>IF(W82="",IF(OR(AK82=0,K82=0),0,U82*E24*MIN(1,(K82+AL82)/L82)),"")</x:f>
+        <x:v>445.4722185986667</x:v>
       </x:c>
       <x:c r="L52" s="34" t="n">
-        <x:f>IF(W82="估算",V82,"")</x:f>
-        <x:v>0.0785045940445169</x:v>
+        <x:f>IF(W82="",V82,"")</x:f>
+        <x:v>0.14582977259653618</x:v>
       </x:c>
       <x:c r="M52" s="34" t="n">
-        <x:f>IF(W82="估算",E52*V82/60,"")</x:f>
-        <x:v>0.02616819801483897</x:v>
+        <x:f>IF(W82="",E52*V82/60,"")</x:f>
+        <x:v>0.04860992419884539</x:v>
       </x:c>
       <x:c r="N52" s="34" t="n">
-        <x:f>IF(W82="估算",V82/60000*1e6,"")</x:f>
-        <x:v>1.3084099007419483</x:v>
+        <x:f>IF(W82="",V82/60000*1e6,"")</x:f>
+        <x:v>2.4304962099422696</x:v>
       </x:c>
       <x:c r="O52" s="30" t="str">
-        <x:f>IF(W82="估算","相位平均估算",W82)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W82="","",W82)</x:f>
       </x:c>
       <x:c r="P52" s="49" t="n">
         <x:f>Q82</x:f>
-        <x:v>35.021088</x:v>
-      </x:c>
-      <x:c r="Q52" s="30"/>
-      <x:c r="R52" s="30"/>
-      <x:c r="S52" s="30"/>
-      <x:c r="T52" s="30"/>
+        <x:v>35.24159702200649</x:v>
+      </x:c>
+      <x:c r="Q52" s="102" t="n">
+        <x:f>AE82</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R52" s="102" t="n">
+        <x:f>AF82</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S52" s="102" t="n">
+        <x:f>IF(W82="",AI82,"")</x:f>
+        <x:v>0.0785045940445169</x:v>
+      </x:c>
+      <x:c r="T52" s="102" t="n">
+        <x:f>IF(W82="",AJ82,"")</x:f>
+        <x:v>0.06732517855201926</x:v>
+      </x:c>
       <x:c r="U52" s="30"/>
       <x:c r="V52" s="30"/>
       <x:c r="W52" s="30"/>
@@ -14690,45 +15099,56 @@
         <x:v>96.83884032</x:v>
       </x:c>
       <x:c r="H53" s="75" t="n">
-        <x:f>IF(W83="估算",U83*R83,"")</x:f>
-        <x:v>4.217144648782645</x:v>
+        <x:f>IF(W83="",U83*R83,"")</x:f>
+        <x:v>4.217189989845549</x:v>
       </x:c>
       <x:c r="I53" s="75" t="n">
-        <x:f>IF(W83="估算",U83*S83,"")</x:f>
-        <x:v>2.2387780392174594</x:v>
+        <x:f>IF(W83="",U83*S83,"")</x:f>
+        <x:v>2.2387326981545552</x:v>
       </x:c>
       <x:c r="J53" s="75" t="n">
-        <x:f>IF(W83="估算",U83*MAX(0,R83-S83),"")</x:f>
-        <x:v>1.9783666095651853</x:v>
+        <x:f>IF(W83="",U83*MAX(0,R83-S83),"")</x:f>
+        <x:v>1.9784572916909937</x:v>
       </x:c>
       <x:c r="K53" s="75" t="n">
-        <x:f>IF(W83="估算",IF(OR(O83=0,K83=0),0,U83*E24*MIN(1,(K83+P83)/L83)),"")</x:f>
-        <x:v>296.977307688</x:v>
+        <x:f>IF(W83="",IF(OR(AK83=0,K83=0),0,U83*E24*MIN(1,(K83+AL83)/L83)),"")</x:f>
+        <x:v>296.9814790657778</x:v>
       </x:c>
       <x:c r="L53" s="34" t="n">
-        <x:f>IF(W83="估算",V83,"")</x:f>
-        <x:v>0.052336396029677934</x:v>
+        <x:f>IF(W83="",V83,"")</x:f>
+        <x:v>0.09721984839769078</x:v>
       </x:c>
       <x:c r="M53" s="34" t="n">
-        <x:f>IF(W83="估算",E53*V83/60,"")</x:f>
-        <x:v>0.02616819801483897</x:v>
+        <x:f>IF(W83="",E53*V83/60,"")</x:f>
+        <x:v>0.04860992419884539</x:v>
       </x:c>
       <x:c r="N53" s="34" t="n">
-        <x:f>IF(W83="估算",V83/60000*1e6,"")</x:f>
-        <x:v>0.8722732671612989</x:v>
+        <x:f>IF(W83="",V83/60000*1e6,"")</x:f>
+        <x:v>1.6203308066281796</x:v>
       </x:c>
       <x:c r="O53" s="30" t="str">
-        <x:f>IF(W83="估算","相位平均估算",W83)</x:f>
-        <x:v>相位平均估算</x:v>
+        <x:f>IF(W83="","",W83)</x:f>
       </x:c>
       <x:c r="P53" s="49" t="n">
         <x:f>Q83</x:f>
-        <x:v>23.347392</x:v>
-      </x:c>
-      <x:c r="Q53" s="30"/>
-      <x:c r="R53" s="30"/>
-      <x:c r="S53" s="30"/>
-      <x:c r="T53" s="30"/>
+        <x:v>23.445190747680634</x:v>
+      </x:c>
+      <x:c r="Q53" s="102" t="n">
+        <x:f>AE83</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="R53" s="102" t="n">
+        <x:f>AF83</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="S53" s="102" t="n">
+        <x:f>IF(W83="",AI83,"")</x:f>
+        <x:v>0.052336396029677934</x:v>
+      </x:c>
+      <x:c r="T53" s="102" t="n">
+        <x:f>IF(W83="",AJ83,"")</x:f>
+        <x:v>0.04488345236801285</x:v>
+      </x:c>
       <x:c r="U53" s="30"/>
       <x:c r="V53" s="30"/>
       <x:c r="W53" s="30"/>
@@ -14816,7 +15236,7 @@
     </x:row>
     <x:row r="57" ht="22" customHeight="1">
       <x:c r="A57" s="30" t="str">
-        <x:v>交接请求总数、每 D DP 请求数、KV 占用和完整计算见下表。全 EP / 部分 EP 是基线窗口交集分类。</x:v>
+        <x:v>EP、TP 增时分别计算后相加；重叠 FW 统计合并层段，不能把两种通信的 FW 次数相加。</x:v>
       </x:c>
       <x:c r="B57" s="30"/>
       <x:c r="C57" s="30"/>
@@ -14924,7 +15344,7 @@
         <x:v>FW 重叠概率</x:v>
       </x:c>
       <x:c r="S59" s="73" t="str">
-        <x:v>全 EP 概率</x:v>
+        <x:v>全通信概率</x:v>
       </x:c>
       <x:c r="T59" s="73" t="str">
         <x:v>每层平均增时 ms</x:v>
@@ -14941,10 +15361,52 @@
       <x:c r="X59" s="73" t="str">
         <x:v>等效全通信 FW/min</x:v>
       </x:c>
+      <x:c r="Y59" s="90" t="str">
+        <x:v>Embedding TP GB</x:v>
+      </x:c>
+      <x:c r="Z59" s="90" t="str">
+        <x:v>Attention SP GB</x:v>
+      </x:c>
+      <x:c r="AA59" s="90" t="str">
+        <x:v>Dense TP GB</x:v>
+      </x:c>
+      <x:c r="AB59" s="90" t="str">
+        <x:v>Shared TP GB</x:v>
+      </x:c>
+      <x:c r="AC59" s="90" t="str">
+        <x:v>Final Hidden GB</x:v>
+      </x:c>
+      <x:c r="AD59" s="90" t="str">
+        <x:v>Sampling TP GB</x:v>
+      </x:c>
+      <x:c r="AE59" s="90" t="str">
+        <x:v>TP GB/Rank/步</x:v>
+      </x:c>
+      <x:c r="AF59" s="90" t="str">
+        <x:v>TP 带宽项 ms</x:v>
+      </x:c>
+      <x:c r="AG59" s="90" t="str">
+        <x:v>每层 TP 段 ms</x:v>
+      </x:c>
+      <x:c r="AH59" s="90" t="str">
+        <x:v>TP 每层增时 ms</x:v>
+      </x:c>
+      <x:c r="AI59" s="90" t="str">
+        <x:v>EP 增时 ms/60s</x:v>
+      </x:c>
+      <x:c r="AJ59" s="90" t="str">
+        <x:v>TP 增时 ms/60s</x:v>
+      </x:c>
+      <x:c r="AK59" s="90" t="str">
+        <x:v>EP+TP 带宽 ms</x:v>
+      </x:c>
+      <x:c r="AL59" s="90" t="str">
+        <x:v>每层合并段 ms</x:v>
+      </x:c>
     </x:row>
     <x:row r="60" ht="22" customHeight="1">
       <x:c r="A60" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D30),D30&gt;0),AND(ISNUMBER(E30),E30&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C30),C30&gt;=2,MOD(C30,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D30),D30&gt;0),AND(ISNUMBER(E30),E30&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C30),C30&gt;=2,MOD(C30,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B60" s="76" t="n">
@@ -15008,19 +15470,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q60" s="76" t="n">
-        <x:f>IF(A60,N60*1000/C60,"")</x:f>
-        <x:v>136.165888</x:v>
+        <x:f>IF(A60,IF(C60&gt;AF60,N60*1000/(C60-AF60),""),"")</x:f>
+        <x:v>139.66137001168445</x:v>
       </x:c>
       <x:c r="R60" s="76" t="n">
-        <x:f>IF(W60="估算",IF(OR(K60=0,O60=0),0,1-((E23-1)*MAX(0,(C60-O60)/E23-(K60))+MAX(0,L60-((E23-1)*C60/E23+P60)-(K60)))/L60),"")</x:f>
-        <x:v>0.001664804876811532</x:v>
+        <x:f>IF(W60="",IF(OR(K60=0,AK60=0),0,1-((E23-1)*MAX(0,(C60-AK60)/E23-(K60))+MAX(0,L60-((E23-1)*C60/E23+AL60)-(K60)))/L60),"")</x:f>
+        <x:v>0.0016651449347825364</x:v>
       </x:c>
       <x:c r="S60" s="76" t="n">
-        <x:f>IF(W60="估算",IF(O60=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C60-O60)/E23-(L60-K60))+MAX(0,L60-((E23-1)*C60/E23+P60)-(L60-K60)))/L60))),"")</x:f>
+        <x:f>IF(W60="",IF(AK60=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C60-AK60)/E23-(L60-K60))+MAX(0,L60-((E23-1)*C60/E23+AL60)-(L60-K60)))/L60))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T60" s="76" t="n">
-        <x:f>IF(W60="估算",IF(OR(P60=0,K60=0,$J$7=0),0,IF(P60&lt;=(1-$J$7)*K60,$J$7*P60*K60/(1-$J$7)-$J$7^2*P60^2/(2*(1-$J$7)^2),$J$7*P60*K60+$J$7^2*K60^2/2)/L60),"")</x:f>
+        <x:f>IF(W60="",IF(OR(P60=0,K60=0,$J$7=0),0,IF(P60&lt;=(1-$J$7)*K60,$J$7*P60*K60/(1-$J$7)-$J$7^2*P60^2/(2*(1-$J$7)^2),$J$7*P60*K60+$J$7^2*K60^2/2)/L60),"")</x:f>
         <x:v>7.331541340902606e-8</x:v>
       </x:c>
       <x:c r="U60" s="76" t="n">
@@ -15028,21 +15490,76 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="V60" s="76" t="n">
-        <x:f>IF(W60="估算",U60*E23*T60*M23*N23,"")</x:f>
+        <x:f>IF(W60="",SUM(AI60:AJ60),"")</x:f>
+        <x:v>0.15235211958680156</x:v>
+      </x:c>
+      <x:c r="W60" s="76" t="str">
+        <x:f>IF(NOT(A60),"输入无效",IF(K60&gt;=L60,"KV 超载",IF(AK60&gt;C60+1e-9,"TPOT 不自洽",IF(OR(C60&gt;L60,MAX(P60,AG60)&gt;L60-K60),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X60" s="76" t="n">
+        <x:f>IF(W60="",U60*M60,"")</x:f>
+        <x:v>5.1360768</x:v>
+      </x:c>
+      <x:c r="Y60" s="103" t="n">
+        <x:f>IF(A60,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z60" s="103" t="n">
+        <x:f>IF(A60,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA60" s="103" t="n">
+        <x:f>IF(A60,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB60" s="103" t="n">
+        <x:f>IF(A60,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC60" s="103" t="n">
+        <x:f>IF(A60,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD60" s="103" t="n">
+        <x:f>IF(A60,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE60" s="103" t="n">
+        <x:f>IF(A60,SUM(Y60:AD60),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF60" s="103" t="n">
+        <x:f>IF(A60,AE60*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG60" s="103" t="n">
+        <x:f>IF(A60,AF60/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH60" s="103" t="n">
+        <x:f>IF(W60="",IF(OR(AG60=0,K60=0,$J$7=0),0,IF(AG60&lt;=(1-$J$7)*K60,$J$7*AG60*K60/(1-$J$7)-$J$7^2*AG60^2/(2*(1-$J$7)^2),$J$7*AG60*K60+$J$7^2*K60^2/2)/L60),"")</x:f>
+        <x:v>6.468469491235216e-8</x:v>
+      </x:c>
+      <x:c r="AI60" s="103" t="n">
+        <x:f>IF(W60="",U60*E23*T60*M23*N23,"")</x:f>
         <x:v>0.08094021640356477</x:v>
       </x:c>
-      <x:c r="W60" s="76" t="str">
-        <x:f>IF(NOT(A60),"输入无效",IF(K60&gt;=L60,"KV 超载",IF(O60&gt;C60+1e-9,"TPOT 不自洽",IF(OR(C60&gt;L60,P60&gt;L60-K60),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X60" s="76" t="n">
-        <x:f>IF(W60="估算",U60*M60,"")</x:f>
-        <x:v>5.1360768</x:v>
+      <x:c r="AJ60" s="103" t="n">
+        <x:f>IF(W60="",U60*E23*AH60*Q23*R23,"")</x:f>
+        <x:v>0.07141190318323679</x:v>
+      </x:c>
+      <x:c r="AK60" s="103" t="n">
+        <x:f>IF(A60,O60+AF60,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL60" s="103" t="n">
+        <x:f>IF(A60,AK60/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="22" customHeight="1">
       <x:c r="A61" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D31),D31&gt;0),AND(ISNUMBER(E31),E31&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C31),C31&gt;=2,MOD(C31,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D31),D31&gt;0),AND(ISNUMBER(E31),E31&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C31),C31&gt;=2,MOD(C31,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B61" s="76" t="n">
@@ -15106,19 +15623,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q61" s="76" t="n">
-        <x:f>IF(A61,N61*1000/C61,"")</x:f>
-        <x:v>68.082944</x:v>
+        <x:f>IF(A61,IF(C61&gt;AF61,N61*1000/(C61-AF61),""),"")</x:f>
+        <x:v>68.94574018544603</x:v>
       </x:c>
       <x:c r="R61" s="76" t="n">
-        <x:f>IF(W61="估算",IF(OR(K61=0,O61=0),0,1-((E23-1)*MAX(0,(C61-O61)/E23-(K61))+MAX(0,L61-((E23-1)*C61/E23+P61)-(K61)))/L61),"")</x:f>
-        <x:v>0.002901217920289856</x:v>
+        <x:f>IF(W61="",IF(OR(K61=0,AK61=0),0,1-((E23-1)*MAX(0,(C61-AK61)/E23-(K61))+MAX(0,L61-((E23-1)*C61/E23+AL61)-(K61)))/L61),"")</x:f>
+        <x:v>0.0029015579782608603</x:v>
       </x:c>
       <x:c r="S61" s="76" t="n">
-        <x:f>IF(W61="估算",IF(O61=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C61-O61)/E23-(L61-K61))+MAX(0,L61-((E23-1)*C61/E23+P61)-(L61-K61)))/L61))),"")</x:f>
+        <x:f>IF(W61="",IF(AK61=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C61-AK61)/E23-(L61-K61))+MAX(0,L61-((E23-1)*C61/E23+AL61)-(L61-K61)))/L61))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T61" s="76" t="n">
-        <x:f>IF(W61="估算",IF(OR(P61=0,K61=0,$J$7=0),0,IF(P61&lt;=(1-$J$7)*K61,$J$7*P61*K61/(1-$J$7)-$J$7^2*P61^2/(2*(1-$J$7)^2),$J$7*P61*K61+$J$7^2*K61^2/2)/L61),"")</x:f>
+        <x:f>IF(W61="",IF(OR(P61=0,K61=0,$J$7=0),0,IF(P61&lt;=(1-$J$7)*K61,$J$7*P61*K61/(1-$J$7)-$J$7^2*P61^2/(2*(1-$J$7)^2),$J$7*P61*K61+$J$7^2*K61^2/2)/L61),"")</x:f>
         <x:v>7.331541340902606e-8</x:v>
       </x:c>
       <x:c r="U61" s="76" t="n">
@@ -15126,21 +15643,76 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="V61" s="76" t="n">
-        <x:f>IF(W61="估算",U61*E23*T61*M23*N23,"")</x:f>
+        <x:f>IF(W61="",SUM(AI61:AJ61),"")</x:f>
+        <x:v>0.07617605979340078</x:v>
+      </x:c>
+      <x:c r="W61" s="76" t="str">
+        <x:f>IF(NOT(A61),"输入无效",IF(K61&gt;=L61,"KV 超载",IF(AK61&gt;C61+1e-9,"TPOT 不自洽",IF(OR(C61&gt;L61,MAX(P61,AG61)&gt;L61-K61),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X61" s="76" t="n">
+        <x:f>IF(W61="",U61*M61,"")</x:f>
+        <x:v>2.5680384</x:v>
+      </x:c>
+      <x:c r="Y61" s="103" t="n">
+        <x:f>IF(A61,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z61" s="103" t="n">
+        <x:f>IF(A61,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA61" s="103" t="n">
+        <x:f>IF(A61,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB61" s="103" t="n">
+        <x:f>IF(A61,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC61" s="103" t="n">
+        <x:f>IF(A61,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD61" s="103" t="n">
+        <x:f>IF(A61,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE61" s="103" t="n">
+        <x:f>IF(A61,SUM(Y61:AD61),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF61" s="103" t="n">
+        <x:f>IF(A61,AE61*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG61" s="103" t="n">
+        <x:f>IF(A61,AF61/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH61" s="103" t="n">
+        <x:f>IF(W61="",IF(OR(AG61=0,K61=0,$J$7=0),0,IF(AG61&lt;=(1-$J$7)*K61,$J$7*AG61*K61/(1-$J$7)-$J$7^2*AG61^2/(2*(1-$J$7)^2),$J$7*AG61*K61+$J$7^2*K61^2/2)/L61),"")</x:f>
+        <x:v>6.468469491235216e-8</x:v>
+      </x:c>
+      <x:c r="AI61" s="103" t="n">
+        <x:f>IF(W61="",U61*E23*T61*M23*N23,"")</x:f>
         <x:v>0.04047010820178239</x:v>
       </x:c>
-      <x:c r="W61" s="76" t="str">
-        <x:f>IF(NOT(A61),"输入无效",IF(K61&gt;=L61,"KV 超载",IF(O61&gt;C61+1e-9,"TPOT 不自洽",IF(OR(C61&gt;L61,P61&gt;L61-K61),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X61" s="76" t="n">
-        <x:f>IF(W61="估算",U61*M61,"")</x:f>
-        <x:v>2.5680384</x:v>
+      <x:c r="AJ61" s="103" t="n">
+        <x:f>IF(W61="",U61*E23*AH61*Q23*R23,"")</x:f>
+        <x:v>0.03570595159161839</x:v>
+      </x:c>
+      <x:c r="AK61" s="103" t="n">
+        <x:f>IF(A61,O61+AF61,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL61" s="103" t="n">
+        <x:f>IF(A61,AK61/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="22" customHeight="1">
       <x:c r="A62" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D32),D32&gt;0),AND(ISNUMBER(E32),E32&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C32),C32&gt;=2,MOD(C32,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D32),D32&gt;0),AND(ISNUMBER(E32),E32&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C32),C32&gt;=2,MOD(C32,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B62" s="76" t="n">
@@ -15204,19 +15776,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q62" s="76" t="n">
-        <x:f>IF(A62,N62*1000/C62,"")</x:f>
-        <x:v>34.041472</x:v>
+        <x:f>IF(A62,IF(C62&gt;AF62,N62*1000/(C62-AF62),""),"")</x:f>
+        <x:v>34.25581290506786</x:v>
       </x:c>
       <x:c r="R62" s="76" t="n">
-        <x:f>IF(W62="估算",IF(OR(K62=0,O62=0),0,1-((E23-1)*MAX(0,(C62-O62)/E23-(K62))+MAX(0,L62-((E23-1)*C62/E23+P62)-(K62)))/L62),"")</x:f>
-        <x:v>0.005374044007246281</x:v>
+        <x:f>IF(W62="",IF(OR(K62=0,AK62=0),0,1-((E23-1)*MAX(0,(C62-AK62)/E23-(K62))+MAX(0,L62-((E23-1)*C62/E23+AL62)-(K62)))/L62),"")</x:f>
+        <x:v>0.005374384065217286</x:v>
       </x:c>
       <x:c r="S62" s="76" t="n">
-        <x:f>IF(W62="估算",IF(O62=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C62-O62)/E23-(L62-K62))+MAX(0,L62-((E23-1)*C62/E23+P62)-(L62-K62)))/L62))),"")</x:f>
+        <x:f>IF(W62="",IF(AK62=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C62-AK62)/E23-(L62-K62))+MAX(0,L62-((E23-1)*C62/E23+AL62)-(L62-K62)))/L62))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T62" s="76" t="n">
-        <x:f>IF(W62="估算",IF(OR(P62=0,K62=0,$J$7=0),0,IF(P62&lt;=(1-$J$7)*K62,$J$7*P62*K62/(1-$J$7)-$J$7^2*P62^2/(2*(1-$J$7)^2),$J$7*P62*K62+$J$7^2*K62^2/2)/L62),"")</x:f>
+        <x:f>IF(W62="",IF(OR(P62=0,K62=0,$J$7=0),0,IF(P62&lt;=(1-$J$7)*K62,$J$7*P62*K62/(1-$J$7)-$J$7^2*P62^2/(2*(1-$J$7)^2),$J$7*P62*K62+$J$7^2*K62^2/2)/L62),"")</x:f>
         <x:v>7.331541340902606e-8</x:v>
       </x:c>
       <x:c r="U62" s="76" t="n">
@@ -15224,21 +15796,76 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="V62" s="76" t="n">
-        <x:f>IF(W62="估算",U62*E23*T62*M23*N23,"")</x:f>
+        <x:f>IF(W62="",SUM(AI62:AJ62),"")</x:f>
+        <x:v>0.03808802989670039</x:v>
+      </x:c>
+      <x:c r="W62" s="76" t="str">
+        <x:f>IF(NOT(A62),"输入无效",IF(K62&gt;=L62,"KV 超载",IF(AK62&gt;C62+1e-9,"TPOT 不自洽",IF(OR(C62&gt;L62,MAX(P62,AG62)&gt;L62-K62),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X62" s="76" t="n">
+        <x:f>IF(W62="",U62*M62,"")</x:f>
+        <x:v>1.2840192</x:v>
+      </x:c>
+      <x:c r="Y62" s="103" t="n">
+        <x:f>IF(A62,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z62" s="103" t="n">
+        <x:f>IF(A62,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA62" s="103" t="n">
+        <x:f>IF(A62,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB62" s="103" t="n">
+        <x:f>IF(A62,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC62" s="103" t="n">
+        <x:f>IF(A62,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD62" s="103" t="n">
+        <x:f>IF(A62,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE62" s="103" t="n">
+        <x:f>IF(A62,SUM(Y62:AD62),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF62" s="103" t="n">
+        <x:f>IF(A62,AE62*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG62" s="103" t="n">
+        <x:f>IF(A62,AF62/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH62" s="103" t="n">
+        <x:f>IF(W62="",IF(OR(AG62=0,K62=0,$J$7=0),0,IF(AG62&lt;=(1-$J$7)*K62,$J$7*AG62*K62/(1-$J$7)-$J$7^2*AG62^2/(2*(1-$J$7)^2),$J$7*AG62*K62+$J$7^2*K62^2/2)/L62),"")</x:f>
+        <x:v>6.468469491235216e-8</x:v>
+      </x:c>
+      <x:c r="AI62" s="103" t="n">
+        <x:f>IF(W62="",U62*E23*T62*M23*N23,"")</x:f>
         <x:v>0.020235054100891194</x:v>
       </x:c>
-      <x:c r="W62" s="76" t="str">
-        <x:f>IF(NOT(A62),"输入无效",IF(K62&gt;=L62,"KV 超载",IF(O62&gt;C62+1e-9,"TPOT 不自洽",IF(OR(C62&gt;L62,P62&gt;L62-K62),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X62" s="76" t="n">
-        <x:f>IF(W62="估算",U62*M62,"")</x:f>
-        <x:v>1.2840192</x:v>
+      <x:c r="AJ62" s="103" t="n">
+        <x:f>IF(W62="",U62*E23*AH62*Q23*R23,"")</x:f>
+        <x:v>0.017852975795809196</x:v>
+      </x:c>
+      <x:c r="AK62" s="103" t="n">
+        <x:f>IF(A62,O62+AF62,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL62" s="103" t="n">
+        <x:f>IF(A62,AK62/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="22" customHeight="1">
       <x:c r="A63" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D33),D33&gt;0),AND(ISNUMBER(E33),E33&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C33),C33&gt;=2,MOD(C33,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D33),D33&gt;0),AND(ISNUMBER(E33),E33&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C33),C33&gt;=2,MOD(C33,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B63" s="76" t="n">
@@ -15302,19 +15929,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q63" s="76" t="n">
-        <x:f>IF(A63,N63*1000/C63,"")</x:f>
-        <x:v>22.694314666666667</x:v>
+        <x:f>IF(A63,IF(C63&gt;AF63,N63*1000/(C63-AF63),""),"")</x:f>
+        <x:v>22.789377770668615</x:v>
       </x:c>
       <x:c r="R63" s="76" t="n">
-        <x:f>IF(W63="估算",IF(OR(K63=0,O63=0),0,1-((E23-1)*MAX(0,(C63-O63)/E23-(K63))+MAX(0,L63-((E23-1)*C63/E23+P63)-(K63)))/L63),"")</x:f>
-        <x:v>0.007846870094202818</x:v>
+        <x:f>IF(W63="",IF(OR(K63=0,AK63=0),0,1-((E23-1)*MAX(0,(C63-AK63)/E23-(K63))+MAX(0,L63-((E23-1)*C63/E23+AL63)-(K63)))/L63),"")</x:f>
+        <x:v>0.007847210152173822</x:v>
       </x:c>
       <x:c r="S63" s="76" t="n">
-        <x:f>IF(W63="估算",IF(O63=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C63-O63)/E23-(L63-K63))+MAX(0,L63-((E23-1)*C63/E23+P63)-(L63-K63)))/L63))),"")</x:f>
+        <x:f>IF(W63="",IF(AK63=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C63-AK63)/E23-(L63-K63))+MAX(0,L63-((E23-1)*C63/E23+AL63)-(L63-K63)))/L63))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T63" s="76" t="n">
-        <x:f>IF(W63="估算",IF(OR(P63=0,K63=0,$J$7=0),0,IF(P63&lt;=(1-$J$7)*K63,$J$7*P63*K63/(1-$J$7)-$J$7^2*P63^2/(2*(1-$J$7)^2),$J$7*P63*K63+$J$7^2*K63^2/2)/L63),"")</x:f>
+        <x:f>IF(W63="",IF(OR(P63=0,K63=0,$J$7=0),0,IF(P63&lt;=(1-$J$7)*K63,$J$7*P63*K63/(1-$J$7)-$J$7^2*P63^2/(2*(1-$J$7)^2),$J$7*P63*K63+$J$7^2*K63^2/2)/L63),"")</x:f>
         <x:v>7.331541340902606e-8</x:v>
       </x:c>
       <x:c r="U63" s="76" t="n">
@@ -15322,21 +15949,76 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="V63" s="76" t="n">
-        <x:f>IF(W63="估算",U63*E23*T63*M23*N23,"")</x:f>
+        <x:f>IF(W63="",SUM(AI63:AJ63),"")</x:f>
+        <x:v>0.025392019931133596</x:v>
+      </x:c>
+      <x:c r="W63" s="76" t="str">
+        <x:f>IF(NOT(A63),"输入无效",IF(K63&gt;=L63,"KV 超载",IF(AK63&gt;C63+1e-9,"TPOT 不自洽",IF(OR(C63&gt;L63,MAX(P63,AG63)&gt;L63-K63),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X63" s="76" t="n">
+        <x:f>IF(W63="",U63*M63,"")</x:f>
+        <x:v>0.8560128</x:v>
+      </x:c>
+      <x:c r="Y63" s="103" t="n">
+        <x:f>IF(A63,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z63" s="103" t="n">
+        <x:f>IF(A63,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA63" s="103" t="n">
+        <x:f>IF(A63,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB63" s="103" t="n">
+        <x:f>IF(A63,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC63" s="103" t="n">
+        <x:f>IF(A63,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD63" s="103" t="n">
+        <x:f>IF(A63,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE63" s="103" t="n">
+        <x:f>IF(A63,SUM(Y63:AD63),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF63" s="103" t="n">
+        <x:f>IF(A63,AE63*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG63" s="103" t="n">
+        <x:f>IF(A63,AF63/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH63" s="103" t="n">
+        <x:f>IF(W63="",IF(OR(AG63=0,K63=0,$J$7=0),0,IF(AG63&lt;=(1-$J$7)*K63,$J$7*AG63*K63/(1-$J$7)-$J$7^2*AG63^2/(2*(1-$J$7)^2),$J$7*AG63*K63+$J$7^2*K63^2/2)/L63),"")</x:f>
+        <x:v>6.468469491235216e-8</x:v>
+      </x:c>
+      <x:c r="AI63" s="103" t="n">
+        <x:f>IF(W63="",U63*E23*T63*M23*N23,"")</x:f>
         <x:v>0.013490036067260796</x:v>
       </x:c>
-      <x:c r="W63" s="76" t="str">
-        <x:f>IF(NOT(A63),"输入无效",IF(K63&gt;=L63,"KV 超载",IF(O63&gt;C63+1e-9,"TPOT 不自洽",IF(OR(C63&gt;L63,P63&gt;L63-K63),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X63" s="76" t="n">
-        <x:f>IF(W63="估算",U63*M63,"")</x:f>
-        <x:v>0.8560128</x:v>
+      <x:c r="AJ63" s="103" t="n">
+        <x:f>IF(W63="",U63*E23*AH63*Q23*R23,"")</x:f>
+        <x:v>0.011901983863872798</x:v>
+      </x:c>
+      <x:c r="AK63" s="103" t="n">
+        <x:f>IF(A63,O63+AF63,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL63" s="103" t="n">
+        <x:f>IF(A63,AK63/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="22" customHeight="1">
       <x:c r="A64" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D34),D34&gt;0),AND(ISNUMBER(E34),E34&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C34),C34&gt;=2,MOD(C34,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D34),D34&gt;0),AND(ISNUMBER(E34),E34&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C34),C34&gt;=2,MOD(C34,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B64" s="76" t="n">
@@ -15400,19 +16082,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q64" s="76" t="n">
-        <x:f>IF(A64,N64*1000/C64,"")</x:f>
-        <x:v>136.165888</x:v>
+        <x:f>IF(A64,IF(C64&gt;AF64,N64*1000/(C64-AF64),""),"")</x:f>
+        <x:v>139.66137001168445</x:v>
       </x:c>
       <x:c r="R64" s="76" t="n">
-        <x:f>IF(W64="估算",IF(OR(K64=0,O64=0),0,1-((E23-1)*MAX(0,(C64-O64)/E23-(K64))+MAX(0,L64-((E23-1)*C64/E23+P64)-(K64)))/L64),"")</x:f>
-        <x:v>0.001465423055362458</x:v>
+        <x:f>IF(W64="",IF(OR(K64=0,AK64=0),0,1-((E23-1)*MAX(0,(C64-AK64)/E23-(K64))+MAX(0,L64-((E23-1)*C64/E23+AL64)-(K64)))/L64),"")</x:f>
+        <x:v>0.0014654910669565924</x:v>
       </x:c>
       <x:c r="S64" s="76" t="n">
-        <x:f>IF(W64="估算",IF(O64=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C64-O64)/E23-(L64-K64))+MAX(0,L64-((E23-1)*C64/E23+P64)-(L64-K64)))/L64))),"")</x:f>
-        <x:v>0.0009707036646378064</x:v>
+        <x:f>IF(W64="",IF(AK64=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C64-AK64)/E23-(L64-K64))+MAX(0,L64-((E23-1)*C64/E23+AL64)-(L64-K64)))/L64))),"")</x:f>
+        <x:v>0.0009706356530435611</x:v>
       </x:c>
       <x:c r="T64" s="76" t="n">
-        <x:f>IF(W64="估算",IF(OR(P64=0,K64=0,$J$7=0),0,IF(P64&lt;=(1-$J$7)*K64,$J$7*P64*K64/(1-$J$7)-$J$7^2*P64^2/(2*(1-$J$7)^2),$J$7*P64*K64+$J$7^2*K64^2/2)/L64),"")</x:f>
+        <x:f>IF(W64="",IF(OR(P64=0,K64=0,$J$7=0),0,IF(P64&lt;=(1-$J$7)*K64,$J$7*P64*K64/(1-$J$7)-$J$7^2*P64^2/(2*(1-$J$7)^2),$J$7*P64*K64+$J$7^2*K64^2/2)/L64),"")</x:f>
         <x:v>2.0865803128980522e-7</x:v>
       </x:c>
       <x:c r="U64" s="76" t="n">
@@ -15420,21 +16102,76 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="V64" s="76" t="n">
-        <x:f>IF(W64="估算",U64*E23*T64*M23*N23,"")</x:f>
+        <x:f>IF(W64="",SUM(AI64:AJ64),"")</x:f>
+        <x:v>0.43359793336811225</x:v>
+      </x:c>
+      <x:c r="W64" s="76" t="str">
+        <x:f>IF(NOT(A64),"输入无效",IF(K64&gt;=L64,"KV 超载",IF(AK64&gt;C64+1e-9,"TPOT 不自洽",IF(OR(C64&gt;L64,MAX(P64,AG64)&gt;L64-K64),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X64" s="76" t="n">
+        <x:f>IF(W64="",U64*M64,"")</x:f>
+        <x:v>14.61676032</x:v>
+      </x:c>
+      <x:c r="Y64" s="103" t="n">
+        <x:f>IF(A64,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z64" s="103" t="n">
+        <x:f>IF(A64,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA64" s="103" t="n">
+        <x:f>IF(A64,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB64" s="103" t="n">
+        <x:f>IF(A64,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC64" s="103" t="n">
+        <x:f>IF(A64,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD64" s="103" t="n">
+        <x:f>IF(A64,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE64" s="103" t="n">
+        <x:f>IF(A64,SUM(Y64:AD64),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF64" s="103" t="n">
+        <x:f>IF(A64,AE64*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG64" s="103" t="n">
+        <x:f>IF(A64,AF64/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH64" s="103" t="n">
+        <x:f>IF(W64="",IF(OR(AG64=0,K64=0,$J$7=0),0,IF(AG64&lt;=(1-$J$7)*K64,$J$7*AG64*K64/(1-$J$7)-$J$7^2*AG64^2/(2*(1-$J$7)^2),$J$7*AG64*K64+$J$7^2*K64^2/2)/L64),"")</x:f>
+        <x:v>1.8409371994942692e-7</x:v>
+      </x:c>
+      <x:c r="AI64" s="103" t="n">
+        <x:f>IF(W64="",U64*E23*T64*M23*N23,"")</x:f>
         <x:v>0.23035846654394496</x:v>
       </x:c>
-      <x:c r="W64" s="76" t="str">
-        <x:f>IF(NOT(A64),"输入无效",IF(K64&gt;=L64,"KV 超载",IF(O64&gt;C64+1e-9,"TPOT 不自洽",IF(OR(C64&gt;L64,P64&gt;L64-K64),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X64" s="76" t="n">
-        <x:f>IF(W64="估算",U64*M64,"")</x:f>
-        <x:v>14.61676032</x:v>
+      <x:c r="AJ64" s="103" t="n">
+        <x:f>IF(W64="",U64*E23*AH64*Q23*R23,"")</x:f>
+        <x:v>0.20323946682416733</x:v>
+      </x:c>
+      <x:c r="AK64" s="103" t="n">
+        <x:f>IF(A64,O64+AF64,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL64" s="103" t="n">
+        <x:f>IF(A64,AK64/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="22" customHeight="1">
       <x:c r="A65" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D35),D35&gt;0),AND(ISNUMBER(E35),E35&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C35),C35&gt;=2,MOD(C35,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D35),D35&gt;0),AND(ISNUMBER(E35),E35&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C35),C35&gt;=2,MOD(C35,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B65" s="76" t="n">
@@ -15498,19 +16235,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q65" s="76" t="n">
-        <x:f>IF(A65,N65*1000/C65,"")</x:f>
-        <x:v>68.082944</x:v>
+        <x:f>IF(A65,IF(C65&gt;AF65,N65*1000/(C65-AF65),""),"")</x:f>
+        <x:v>68.94574018544603</x:v>
       </x:c>
       <x:c r="R65" s="76" t="n">
-        <x:f>IF(W65="估算",IF(OR(K65=0,O65=0),0,1-((E23-1)*MAX(0,(C65-O65)/E23-(K65))+MAX(0,L65-((E23-1)*C65/E23+P65)-(K65)))/L65),"")</x:f>
-        <x:v>0.0017127056640580118</x:v>
+        <x:f>IF(W65="",IF(OR(K65=0,AK65=0),0,1-((E23-1)*MAX(0,(C65-AK65)/E23-(K65))+MAX(0,L65-((E23-1)*C65/E23+AL65)-(K65)))/L65),"")</x:f>
+        <x:v>0.0017127736756523682</x:v>
       </x:c>
       <x:c r="S65" s="76" t="n">
-        <x:f>IF(W65="估算",IF(O65=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C65-O65)/E23-(L65-K65))+MAX(0,L65-((E23-1)*C65/E23+P65)-(L65-K65)))/L65))),"")</x:f>
-        <x:v>0.0007234210559421417</x:v>
+        <x:f>IF(W65="",IF(AK65=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C65-AK65)/E23-(L65-K65))+MAX(0,L65-((E23-1)*C65/E23+AL65)-(L65-K65)))/L65))),"")</x:f>
+        <x:v>0.0007233530443477854</x:v>
       </x:c>
       <x:c r="T65" s="76" t="n">
-        <x:f>IF(W65="估算",IF(OR(P65=0,K65=0,$J$7=0),0,IF(P65&lt;=(1-$J$7)*K65,$J$7*P65*K65/(1-$J$7)-$J$7^2*P65^2/(2*(1-$J$7)^2),$J$7*P65*K65+$J$7^2*K65^2/2)/L65),"")</x:f>
+        <x:f>IF(W65="",IF(OR(P65=0,K65=0,$J$7=0),0,IF(P65&lt;=(1-$J$7)*K65,$J$7*P65*K65/(1-$J$7)-$J$7^2*P65^2/(2*(1-$J$7)^2),$J$7*P65*K65+$J$7^2*K65^2/2)/L65),"")</x:f>
         <x:v>2.0865803128980522e-7</x:v>
       </x:c>
       <x:c r="U65" s="76" t="n">
@@ -15518,21 +16255,76 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="V65" s="76" t="n">
-        <x:f>IF(W65="估算",U65*E23*T65*M23*N23,"")</x:f>
+        <x:f>IF(W65="",SUM(AI65:AJ65),"")</x:f>
+        <x:v>0.21679896668405613</x:v>
+      </x:c>
+      <x:c r="W65" s="76" t="str">
+        <x:f>IF(NOT(A65),"输入无效",IF(K65&gt;=L65,"KV 超载",IF(AK65&gt;C65+1e-9,"TPOT 不自洽",IF(OR(C65&gt;L65,MAX(P65,AG65)&gt;L65-K65),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X65" s="76" t="n">
+        <x:f>IF(W65="",U65*M65,"")</x:f>
+        <x:v>7.30838016</x:v>
+      </x:c>
+      <x:c r="Y65" s="103" t="n">
+        <x:f>IF(A65,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z65" s="103" t="n">
+        <x:f>IF(A65,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA65" s="103" t="n">
+        <x:f>IF(A65,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB65" s="103" t="n">
+        <x:f>IF(A65,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC65" s="103" t="n">
+        <x:f>IF(A65,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD65" s="103" t="n">
+        <x:f>IF(A65,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE65" s="103" t="n">
+        <x:f>IF(A65,SUM(Y65:AD65),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF65" s="103" t="n">
+        <x:f>IF(A65,AE65*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG65" s="103" t="n">
+        <x:f>IF(A65,AF65/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH65" s="103" t="n">
+        <x:f>IF(W65="",IF(OR(AG65=0,K65=0,$J$7=0),0,IF(AG65&lt;=(1-$J$7)*K65,$J$7*AG65*K65/(1-$J$7)-$J$7^2*AG65^2/(2*(1-$J$7)^2),$J$7*AG65*K65+$J$7^2*K65^2/2)/L65),"")</x:f>
+        <x:v>1.8409371994942692e-7</x:v>
+      </x:c>
+      <x:c r="AI65" s="103" t="n">
+        <x:f>IF(W65="",U65*E23*T65*M23*N23,"")</x:f>
         <x:v>0.11517923327197248</x:v>
       </x:c>
-      <x:c r="W65" s="76" t="str">
-        <x:f>IF(NOT(A65),"输入无效",IF(K65&gt;=L65,"KV 超载",IF(O65&gt;C65+1e-9,"TPOT 不自洽",IF(OR(C65&gt;L65,P65&gt;L65-K65),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X65" s="76" t="n">
-        <x:f>IF(W65="估算",U65*M65,"")</x:f>
-        <x:v>7.30838016</x:v>
+      <x:c r="AJ65" s="103" t="n">
+        <x:f>IF(W65="",U65*E23*AH65*Q23*R23,"")</x:f>
+        <x:v>0.10161973341208366</x:v>
+      </x:c>
+      <x:c r="AK65" s="103" t="n">
+        <x:f>IF(A65,O65+AF65,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL65" s="103" t="n">
+        <x:f>IF(A65,AK65/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="22" customHeight="1">
       <x:c r="A66" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D36),D36&gt;0),AND(ISNUMBER(E36),E36&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C36),C36&gt;=2,MOD(C36,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D36),D36&gt;0),AND(ISNUMBER(E36),E36&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C36),C36&gt;=2,MOD(C36,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B66" s="76" t="n">
@@ -15596,19 +16388,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q66" s="76" t="n">
-        <x:f>IF(A66,N66*1000/C66,"")</x:f>
-        <x:v>34.041472</x:v>
+        <x:f>IF(A66,IF(C66&gt;AF66,N66*1000/(C66-AF66),""),"")</x:f>
+        <x:v>34.25581290506786</x:v>
       </x:c>
       <x:c r="R66" s="76" t="n">
-        <x:f>IF(W66="估算",IF(OR(K66=0,O66=0),0,1-((E23-1)*MAX(0,(C66-O66)/E23-(K66))+MAX(0,L66-((E23-1)*C66/E23+P66)-(K66)))/L66),"")</x:f>
-        <x:v>0.0022072708814494524</x:v>
+        <x:f>IF(W66="",IF(OR(K66=0,AK66=0),0,1-((E23-1)*MAX(0,(C66-AK66)/E23-(K66))+MAX(0,L66-((E23-1)*C66/E23+AL66)-(K66)))/L66),"")</x:f>
+        <x:v>0.0022073388930435867</x:v>
       </x:c>
       <x:c r="S66" s="76" t="n">
-        <x:f>IF(W66="估算",IF(O66=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C66-O66)/E23-(L66-K66))+MAX(0,L66-((E23-1)*C66/E23+P66)-(L66-K66)))/L66))),"")</x:f>
-        <x:v>0.00022885583855081215</x:v>
+        <x:f>IF(W66="",IF(AK66=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C66-AK66)/E23-(L66-K66))+MAX(0,L66-((E23-1)*C66/E23+AL66)-(L66-K66)))/L66))),"")</x:f>
+        <x:v>0.00022878782695656685</x:v>
       </x:c>
       <x:c r="T66" s="76" t="n">
-        <x:f>IF(W66="估算",IF(OR(P66=0,K66=0,$J$7=0),0,IF(P66&lt;=(1-$J$7)*K66,$J$7*P66*K66/(1-$J$7)-$J$7^2*P66^2/(2*(1-$J$7)^2),$J$7*P66*K66+$J$7^2*K66^2/2)/L66),"")</x:f>
+        <x:f>IF(W66="",IF(OR(P66=0,K66=0,$J$7=0),0,IF(P66&lt;=(1-$J$7)*K66,$J$7*P66*K66/(1-$J$7)-$J$7^2*P66^2/(2*(1-$J$7)^2),$J$7*P66*K66+$J$7^2*K66^2/2)/L66),"")</x:f>
         <x:v>2.0865803128980522e-7</x:v>
       </x:c>
       <x:c r="U66" s="76" t="n">
@@ -15616,21 +16408,76 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="V66" s="76" t="n">
-        <x:f>IF(W66="估算",U66*E23*T66*M23*N23,"")</x:f>
+        <x:f>IF(W66="",SUM(AI66:AJ66),"")</x:f>
+        <x:v>0.10839948334202806</x:v>
+      </x:c>
+      <x:c r="W66" s="76" t="str">
+        <x:f>IF(NOT(A66),"输入无效",IF(K66&gt;=L66,"KV 超载",IF(AK66&gt;C66+1e-9,"TPOT 不自洽",IF(OR(C66&gt;L66,MAX(P66,AG66)&gt;L66-K66),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X66" s="76" t="n">
+        <x:f>IF(W66="",U66*M66,"")</x:f>
+        <x:v>3.65419008</x:v>
+      </x:c>
+      <x:c r="Y66" s="103" t="n">
+        <x:f>IF(A66,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z66" s="103" t="n">
+        <x:f>IF(A66,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA66" s="103" t="n">
+        <x:f>IF(A66,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB66" s="103" t="n">
+        <x:f>IF(A66,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC66" s="103" t="n">
+        <x:f>IF(A66,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD66" s="103" t="n">
+        <x:f>IF(A66,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE66" s="103" t="n">
+        <x:f>IF(A66,SUM(Y66:AD66),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF66" s="103" t="n">
+        <x:f>IF(A66,AE66*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG66" s="103" t="n">
+        <x:f>IF(A66,AF66/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH66" s="103" t="n">
+        <x:f>IF(W66="",IF(OR(AG66=0,K66=0,$J$7=0),0,IF(AG66&lt;=(1-$J$7)*K66,$J$7*AG66*K66/(1-$J$7)-$J$7^2*AG66^2/(2*(1-$J$7)^2),$J$7*AG66*K66+$J$7^2*K66^2/2)/L66),"")</x:f>
+        <x:v>1.8409371994942692e-7</x:v>
+      </x:c>
+      <x:c r="AI66" s="103" t="n">
+        <x:f>IF(W66="",U66*E23*T66*M23*N23,"")</x:f>
         <x:v>0.05758961663598624</x:v>
       </x:c>
-      <x:c r="W66" s="76" t="str">
-        <x:f>IF(NOT(A66),"输入无效",IF(K66&gt;=L66,"KV 超载",IF(O66&gt;C66+1e-9,"TPOT 不自洽",IF(OR(C66&gt;L66,P66&gt;L66-K66),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X66" s="76" t="n">
-        <x:f>IF(W66="估算",U66*M66,"")</x:f>
-        <x:v>3.65419008</x:v>
+      <x:c r="AJ66" s="103" t="n">
+        <x:f>IF(W66="",U66*E23*AH66*Q23*R23,"")</x:f>
+        <x:v>0.05080986670604183</x:v>
+      </x:c>
+      <x:c r="AK66" s="103" t="n">
+        <x:f>IF(A66,O66+AF66,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL66" s="103" t="n">
+        <x:f>IF(A66,AK66/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="22" customHeight="1">
       <x:c r="A67" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D37),D37&gt;0),AND(ISNUMBER(E37),E37&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C37),C37&gt;=2,MOD(C37,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D37),D37&gt;0),AND(ISNUMBER(E37),E37&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C37),C37&gt;=2,MOD(C37,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B67" s="76" t="n">
@@ -15694,19 +16541,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q67" s="76" t="n">
-        <x:f>IF(A67,N67*1000/C67,"")</x:f>
-        <x:v>22.694314666666667</x:v>
+        <x:f>IF(A67,IF(C67&gt;AF67,N67*1000/(C67-AF67),""),"")</x:f>
+        <x:v>22.789377770668615</x:v>
       </x:c>
       <x:c r="R67" s="76" t="n">
-        <x:f>IF(W67="估算",IF(OR(K67=0,O67=0),0,1-((E23-1)*MAX(0,(C67-O67)/E23-(K67))+MAX(0,L67-((E23-1)*C67/E23+P67)-(K67)))/L67),"")</x:f>
-        <x:v>0.00270183609884056</x:v>
+        <x:f>IF(W67="",IF(OR(K67=0,AK67=0),0,1-((E23-1)*MAX(0,(C67-AK67)/E23-(K67))+MAX(0,L67-((E23-1)*C67/E23+AL67)-(K67)))/L67),"")</x:f>
+        <x:v>0.002701904110434916</x:v>
       </x:c>
       <x:c r="S67" s="76" t="n">
-        <x:f>IF(W67="估算",IF(O67=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C67-O67)/E23-(L67-K67))+MAX(0,L67-((E23-1)*C67/E23+P67)-(L67-K67)))/L67))),"")</x:f>
+        <x:f>IF(W67="",IF(AK67=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C67-AK67)/E23-(L67-K67))+MAX(0,L67-((E23-1)*C67/E23+AL67)-(L67-K67)))/L67))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T67" s="76" t="n">
-        <x:f>IF(W67="估算",IF(OR(P67=0,K67=0,$J$7=0),0,IF(P67&lt;=(1-$J$7)*K67,$J$7*P67*K67/(1-$J$7)-$J$7^2*P67^2/(2*(1-$J$7)^2),$J$7*P67*K67+$J$7^2*K67^2/2)/L67),"")</x:f>
+        <x:f>IF(W67="",IF(OR(P67=0,K67=0,$J$7=0),0,IF(P67&lt;=(1-$J$7)*K67,$J$7*P67*K67/(1-$J$7)-$J$7^2*P67^2/(2*(1-$J$7)^2),$J$7*P67*K67+$J$7^2*K67^2/2)/L67),"")</x:f>
         <x:v>2.0865803128980522e-7</x:v>
       </x:c>
       <x:c r="U67" s="76" t="n">
@@ -15714,21 +16561,76 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="V67" s="76" t="n">
-        <x:f>IF(W67="估算",U67*E23*T67*M23*N23,"")</x:f>
+        <x:f>IF(W67="",SUM(AI67:AJ67),"")</x:f>
+        <x:v>0.07226632222801871</x:v>
+      </x:c>
+      <x:c r="W67" s="76" t="str">
+        <x:f>IF(NOT(A67),"输入无效",IF(K67&gt;=L67,"KV 超载",IF(AK67&gt;C67+1e-9,"TPOT 不自洽",IF(OR(C67&gt;L67,MAX(P67,AG67)&gt;L67-K67),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X67" s="76" t="n">
+        <x:f>IF(W67="",U67*M67,"")</x:f>
+        <x:v>2.43612672</x:v>
+      </x:c>
+      <x:c r="Y67" s="103" t="n">
+        <x:f>IF(A67,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z67" s="103" t="n">
+        <x:f>IF(A67,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA67" s="103" t="n">
+        <x:f>IF(A67,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB67" s="103" t="n">
+        <x:f>IF(A67,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC67" s="103" t="n">
+        <x:f>IF(A67,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD67" s="103" t="n">
+        <x:f>IF(A67,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE67" s="103" t="n">
+        <x:f>IF(A67,SUM(Y67:AD67),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF67" s="103" t="n">
+        <x:f>IF(A67,AE67*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG67" s="103" t="n">
+        <x:f>IF(A67,AF67/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH67" s="103" t="n">
+        <x:f>IF(W67="",IF(OR(AG67=0,K67=0,$J$7=0),0,IF(AG67&lt;=(1-$J$7)*K67,$J$7*AG67*K67/(1-$J$7)-$J$7^2*AG67^2/(2*(1-$J$7)^2),$J$7*AG67*K67+$J$7^2*K67^2/2)/L67),"")</x:f>
+        <x:v>1.8409371994942692e-7</x:v>
+      </x:c>
+      <x:c r="AI67" s="103" t="n">
+        <x:f>IF(W67="",U67*E23*T67*M23*N23,"")</x:f>
         <x:v>0.03839307775732416</x:v>
       </x:c>
-      <x:c r="W67" s="76" t="str">
-        <x:f>IF(NOT(A67),"输入无效",IF(K67&gt;=L67,"KV 超载",IF(O67&gt;C67+1e-9,"TPOT 不自洽",IF(OR(C67&gt;L67,P67&gt;L67-K67),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X67" s="76" t="n">
-        <x:f>IF(W67="估算",U67*M67,"")</x:f>
-        <x:v>2.43612672</x:v>
+      <x:c r="AJ67" s="103" t="n">
+        <x:f>IF(W67="",U67*E23*AH67*Q23*R23,"")</x:f>
+        <x:v>0.03387324447069455</x:v>
+      </x:c>
+      <x:c r="AK67" s="103" t="n">
+        <x:f>IF(A67,O67+AF67,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL67" s="103" t="n">
+        <x:f>IF(A67,AK67/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="22" customHeight="1">
       <x:c r="A68" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D38),D38&gt;0),AND(ISNUMBER(E38),E38&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C38),C38&gt;=2,MOD(C38,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D38),D38&gt;0),AND(ISNUMBER(E38),E38&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C38),C38&gt;=2,MOD(C38,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B68" s="76" t="n">
@@ -15792,19 +16694,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q68" s="76" t="n">
-        <x:f>IF(A68,N68*1000/C68,"")</x:f>
-        <x:v>136.165888</x:v>
+        <x:f>IF(A68,IF(C68&gt;AF68,N68*1000/(C68-AF68),""),"")</x:f>
+        <x:v>139.66137001168445</x:v>
       </x:c>
       <x:c r="R68" s="76" t="n">
-        <x:f>IF(W68="估算",IF(OR(K68=0,O68=0),0,1-((E23-1)*MAX(0,(C68-O68)/E23-(K68))+MAX(0,L68-((E23-1)*C68/E23+P68)-(K68)))/L68),"")</x:f>
-        <x:v>0.0016964339037874865</x:v>
+        <x:f>IF(W68="",IF(OR(K68=0,AK68=0),0,1-((E23-1)*MAX(0,(C68-AK68)/E23-(K68))+MAX(0,L68-((E23-1)*C68/E23+AL68)-(K68)))/L68),"")</x:f>
+        <x:v>0.0016964565743189386</x:v>
       </x:c>
       <x:c r="S68" s="76" t="n">
-        <x:f>IF(W68="估算",IF(O68=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C68-O68)/E23-(L68-K68))+MAX(0,L68-((E23-1)*C68/E23+P68)-(L68-K68)))/L68))),"")</x:f>
-        <x:v>0.0015315274402125656</x:v>
+        <x:f>IF(W68="",IF(AK68=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C68-AK68)/E23-(L68-K68))+MAX(0,L68-((E23-1)*C68/E23+AL68)-(L68-K68)))/L68))),"")</x:f>
+        <x:v>0.0015315047696811135</x:v>
       </x:c>
       <x:c r="T68" s="76" t="n">
-        <x:f>IF(W68="估算",IF(OR(P68=0,K68=0,$J$7=0),0,IF(P68&lt;=(1-$J$7)*K68,$J$7*P68*K68/(1-$J$7)-$J$7^2*P68^2/(2*(1-$J$7)^2),$J$7*P68*K68+$J$7^2*K68^2/2)/L68),"")</x:f>
+        <x:f>IF(W68="",IF(OR(P68=0,K68=0,$J$7=0),0,IF(P68&lt;=(1-$J$7)*K68,$J$7*P68*K68/(1-$J$7)-$J$7^2*P68^2/(2*(1-$J$7)^2),$J$7*P68*K68+$J$7^2*K68^2/2)/L68),"")</x:f>
         <x:v>2.764806222784684e-7</x:v>
       </x:c>
       <x:c r="U68" s="76" t="n">
@@ -15812,21 +16714,76 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="V68" s="76" t="n">
-        <x:f>IF(W68="估算",U68*E23*T68*M23*N23,"")</x:f>
+        <x:f>IF(W68="",SUM(AI68:AJ68),"")</x:f>
+        <x:v>0.5745353212035063</x:v>
+      </x:c>
+      <x:c r="W68" s="76" t="str">
+        <x:f>IF(NOT(A68),"输入无效",IF(K68&gt;=L68,"KV 超载",IF(AK68&gt;C68+1e-9,"TPOT 不自洽",IF(OR(C68&gt;L68,MAX(P68,AG68)&gt;L68-K68),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X68" s="76" t="n">
+        <x:f>IF(W68="",U68*M68,"")</x:f>
+        <x:v>19.367768064</x:v>
+      </x:c>
+      <x:c r="Y68" s="103" t="n">
+        <x:f>IF(A68,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z68" s="103" t="n">
+        <x:f>IF(A68,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA68" s="103" t="n">
+        <x:f>IF(A68,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB68" s="103" t="n">
+        <x:f>IF(A68,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC68" s="103" t="n">
+        <x:f>IF(A68,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD68" s="103" t="n">
+        <x:f>IF(A68,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE68" s="103" t="n">
+        <x:f>IF(A68,SUM(Y68:AD68),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF68" s="103" t="n">
+        <x:f>IF(A68,AE68*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG68" s="103" t="n">
+        <x:f>IF(A68,AF68/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH68" s="103" t="n">
+        <x:f>IF(W68="",IF(OR(AG68=0,K68=0,$J$7=0),0,IF(AG68&lt;=(1-$J$7)*K68,$J$7*AG68*K68/(1-$J$7)-$J$7^2*AG68^2/(2*(1-$J$7)^2),$J$7*AG68*K68+$J$7^2*K68^2/2)/L68),"")</x:f>
+        <x:v>2.439318063478959e-7</x:v>
+      </x:c>
+      <x:c r="AI68" s="103" t="n">
+        <x:f>IF(W68="",U68*E23*T68*M23*N23,"")</x:f>
         <x:v>0.30523460699542915</x:v>
       </x:c>
-      <x:c r="W68" s="76" t="str">
-        <x:f>IF(NOT(A68),"输入无效",IF(K68&gt;=L68,"KV 超载",IF(O68&gt;C68+1e-9,"TPOT 不自洽",IF(OR(C68&gt;L68,P68&gt;L68-K68),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X68" s="76" t="n">
-        <x:f>IF(W68="估算",U68*M68,"")</x:f>
-        <x:v>19.367768064</x:v>
+      <x:c r="AJ68" s="103" t="n">
+        <x:f>IF(W68="",U68*E23*AH68*Q23*R23,"")</x:f>
+        <x:v>0.26930071420807705</x:v>
+      </x:c>
+      <x:c r="AK68" s="103" t="n">
+        <x:f>IF(A68,O68+AF68,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL68" s="103" t="n">
+        <x:f>IF(A68,AK68/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="22" customHeight="1">
       <x:c r="A69" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D39),D39&gt;0),AND(ISNUMBER(E39),E39&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C39),C39&gt;=2,MOD(C39,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D39),D39&gt;0),AND(ISNUMBER(E39),E39&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C39),C39&gt;=2,MOD(C39,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B69" s="76" t="n">
@@ -15890,19 +16847,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q69" s="76" t="n">
-        <x:f>IF(A69,N69*1000/C69,"")</x:f>
-        <x:v>68.082944</x:v>
+        <x:f>IF(A69,IF(C69&gt;AF69,N69*1000/(C69-AF69),""),"")</x:f>
+        <x:v>68.94574018544603</x:v>
       </x:c>
       <x:c r="R69" s="76" t="n">
-        <x:f>IF(W69="估算",IF(OR(K69=0,O69=0),0,1-((E23-1)*MAX(0,(C69-O69)/E23-(K69))+MAX(0,L69-((E23-1)*C69/E23+P69)-(K69)))/L69),"")</x:f>
-        <x:v>0.0017788614400192637</x:v>
+        <x:f>IF(W69="",IF(OR(K69=0,AK69=0),0,1-((E23-1)*MAX(0,(C69-AK69)/E23-(K69))+MAX(0,L69-((E23-1)*C69/E23+AL69)-(K69)))/L69),"")</x:f>
+        <x:v>0.0017788841105507158</x:v>
       </x:c>
       <x:c r="S69" s="76" t="n">
-        <x:f>IF(W69="估算",IF(O69=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C69-O69)/E23-(L69-K69))+MAX(0,L69-((E23-1)*C69/E23+P69)-(L69-K69)))/L69))),"")</x:f>
-        <x:v>0.0014490999039806773</x:v>
+        <x:f>IF(W69="",IF(AK69=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C69-AK69)/E23-(L69-K69))+MAX(0,L69-((E23-1)*C69/E23+AL69)-(L69-K69)))/L69))),"")</x:f>
+        <x:v>0.0014490772334492252</x:v>
       </x:c>
       <x:c r="T69" s="76" t="n">
-        <x:f>IF(W69="估算",IF(OR(P69=0,K69=0,$J$7=0),0,IF(P69&lt;=(1-$J$7)*K69,$J$7*P69*K69/(1-$J$7)-$J$7^2*P69^2/(2*(1-$J$7)^2),$J$7*P69*K69+$J$7^2*K69^2/2)/L69),"")</x:f>
+        <x:f>IF(W69="",IF(OR(P69=0,K69=0,$J$7=0),0,IF(P69&lt;=(1-$J$7)*K69,$J$7*P69*K69/(1-$J$7)-$J$7^2*P69^2/(2*(1-$J$7)^2),$J$7*P69*K69+$J$7^2*K69^2/2)/L69),"")</x:f>
         <x:v>2.764806222784684e-7</x:v>
       </x:c>
       <x:c r="U69" s="76" t="n">
@@ -15910,21 +16867,76 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="V69" s="76" t="n">
-        <x:f>IF(W69="估算",U69*E23*T69*M23*N23,"")</x:f>
+        <x:f>IF(W69="",SUM(AI69:AJ69),"")</x:f>
+        <x:v>0.2872676606017531</x:v>
+      </x:c>
+      <x:c r="W69" s="76" t="str">
+        <x:f>IF(NOT(A69),"输入无效",IF(K69&gt;=L69,"KV 超载",IF(AK69&gt;C69+1e-9,"TPOT 不自洽",IF(OR(C69&gt;L69,MAX(P69,AG69)&gt;L69-K69),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X69" s="76" t="n">
+        <x:f>IF(W69="",U69*M69,"")</x:f>
+        <x:v>9.683884032</x:v>
+      </x:c>
+      <x:c r="Y69" s="103" t="n">
+        <x:f>IF(A69,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z69" s="103" t="n">
+        <x:f>IF(A69,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA69" s="103" t="n">
+        <x:f>IF(A69,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB69" s="103" t="n">
+        <x:f>IF(A69,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC69" s="103" t="n">
+        <x:f>IF(A69,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD69" s="103" t="n">
+        <x:f>IF(A69,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE69" s="103" t="n">
+        <x:f>IF(A69,SUM(Y69:AD69),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF69" s="103" t="n">
+        <x:f>IF(A69,AE69*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG69" s="103" t="n">
+        <x:f>IF(A69,AF69/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH69" s="103" t="n">
+        <x:f>IF(W69="",IF(OR(AG69=0,K69=0,$J$7=0),0,IF(AG69&lt;=(1-$J$7)*K69,$J$7*AG69*K69/(1-$J$7)-$J$7^2*AG69^2/(2*(1-$J$7)^2),$J$7*AG69*K69+$J$7^2*K69^2/2)/L69),"")</x:f>
+        <x:v>2.439318063478959e-7</x:v>
+      </x:c>
+      <x:c r="AI69" s="103" t="n">
+        <x:f>IF(W69="",U69*E23*T69*M23*N23,"")</x:f>
         <x:v>0.15261730349771457</x:v>
       </x:c>
-      <x:c r="W69" s="76" t="str">
-        <x:f>IF(NOT(A69),"输入无效",IF(K69&gt;=L69,"KV 超载",IF(O69&gt;C69+1e-9,"TPOT 不自洽",IF(OR(C69&gt;L69,P69&gt;L69-K69),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X69" s="76" t="n">
-        <x:f>IF(W69="估算",U69*M69,"")</x:f>
-        <x:v>9.683884032</x:v>
+      <x:c r="AJ69" s="103" t="n">
+        <x:f>IF(W69="",U69*E23*AH69*Q23*R23,"")</x:f>
+        <x:v>0.13465035710403853</x:v>
+      </x:c>
+      <x:c r="AK69" s="103" t="n">
+        <x:f>IF(A69,O69+AF69,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL69" s="103" t="n">
+        <x:f>IF(A69,AK69/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="22" customHeight="1">
       <x:c r="A70" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D40),D40&gt;0),AND(ISNUMBER(E40),E40&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C40),C40&gt;=2,MOD(C40,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D40),D40&gt;0),AND(ISNUMBER(E40),E40&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C40),C40&gt;=2,MOD(C40,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B70" s="76" t="n">
@@ -15988,19 +17000,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q70" s="76" t="n">
-        <x:f>IF(A70,N70*1000/C70,"")</x:f>
-        <x:v>34.041472</x:v>
+        <x:f>IF(A70,IF(C70&gt;AF70,N70*1000/(C70-AF70),""),"")</x:f>
+        <x:v>34.25581290506786</x:v>
       </x:c>
       <x:c r="R70" s="76" t="n">
-        <x:f>IF(W70="估算",IF(OR(K70=0,O70=0),0,1-((E23-1)*MAX(0,(C70-O70)/E23-(K70))+MAX(0,L70-((E23-1)*C70/E23+P70)-(K70)))/L70),"")</x:f>
-        <x:v>0.0019437165124830402</x:v>
+        <x:f>IF(W70="",IF(OR(K70=0,AK70=0),0,1-((E23-1)*MAX(0,(C70-AK70)/E23-(K70))+MAX(0,L70-((E23-1)*C70/E23+AL70)-(K70)))/L70),"")</x:f>
+        <x:v>0.0019437391830144923</x:v>
       </x:c>
       <x:c r="S70" s="76" t="n">
-        <x:f>IF(W70="估算",IF(O70=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C70-O70)/E23-(L70-K70))+MAX(0,L70-((E23-1)*C70/E23+P70)-(L70-K70)))/L70))),"")</x:f>
-        <x:v>0.0012842448315170119</x:v>
+        <x:f>IF(W70="",IF(AK70=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C70-AK70)/E23-(L70-K70))+MAX(0,L70-((E23-1)*C70/E23+AL70)-(L70-K70)))/L70))),"")</x:f>
+        <x:v>0.0012842221609855597</x:v>
       </x:c>
       <x:c r="T70" s="76" t="n">
-        <x:f>IF(W70="估算",IF(OR(P70=0,K70=0,$J$7=0),0,IF(P70&lt;=(1-$J$7)*K70,$J$7*P70*K70/(1-$J$7)-$J$7^2*P70^2/(2*(1-$J$7)^2),$J$7*P70*K70+$J$7^2*K70^2/2)/L70),"")</x:f>
+        <x:f>IF(W70="",IF(OR(P70=0,K70=0,$J$7=0),0,IF(P70&lt;=(1-$J$7)*K70,$J$7*P70*K70/(1-$J$7)-$J$7^2*P70^2/(2*(1-$J$7)^2),$J$7*P70*K70+$J$7^2*K70^2/2)/L70),"")</x:f>
         <x:v>2.764806222784684e-7</x:v>
       </x:c>
       <x:c r="U70" s="76" t="n">
@@ -16008,21 +17020,76 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="V70" s="76" t="n">
-        <x:f>IF(W70="估算",U70*E23*T70*M23*N23,"")</x:f>
+        <x:f>IF(W70="",SUM(AI70:AJ70),"")</x:f>
+        <x:v>0.14363383030087656</x:v>
+      </x:c>
+      <x:c r="W70" s="76" t="str">
+        <x:f>IF(NOT(A70),"输入无效",IF(K70&gt;=L70,"KV 超载",IF(AK70&gt;C70+1e-9,"TPOT 不自洽",IF(OR(C70&gt;L70,MAX(P70,AG70)&gt;L70-K70),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X70" s="76" t="n">
+        <x:f>IF(W70="",U70*M70,"")</x:f>
+        <x:v>4.841942016</x:v>
+      </x:c>
+      <x:c r="Y70" s="103" t="n">
+        <x:f>IF(A70,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z70" s="103" t="n">
+        <x:f>IF(A70,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA70" s="103" t="n">
+        <x:f>IF(A70,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB70" s="103" t="n">
+        <x:f>IF(A70,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC70" s="103" t="n">
+        <x:f>IF(A70,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD70" s="103" t="n">
+        <x:f>IF(A70,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE70" s="103" t="n">
+        <x:f>IF(A70,SUM(Y70:AD70),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF70" s="103" t="n">
+        <x:f>IF(A70,AE70*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG70" s="103" t="n">
+        <x:f>IF(A70,AF70/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH70" s="103" t="n">
+        <x:f>IF(W70="",IF(OR(AG70=0,K70=0,$J$7=0),0,IF(AG70&lt;=(1-$J$7)*K70,$J$7*AG70*K70/(1-$J$7)-$J$7^2*AG70^2/(2*(1-$J$7)^2),$J$7*AG70*K70+$J$7^2*K70^2/2)/L70),"")</x:f>
+        <x:v>2.439318063478959e-7</x:v>
+      </x:c>
+      <x:c r="AI70" s="103" t="n">
+        <x:f>IF(W70="",U70*E23*T70*M23*N23,"")</x:f>
         <x:v>0.07630865174885729</x:v>
       </x:c>
-      <x:c r="W70" s="76" t="str">
-        <x:f>IF(NOT(A70),"输入无效",IF(K70&gt;=L70,"KV 超载",IF(O70&gt;C70+1e-9,"TPOT 不自洽",IF(OR(C70&gt;L70,P70&gt;L70-K70),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X70" s="76" t="n">
-        <x:f>IF(W70="估算",U70*M70,"")</x:f>
-        <x:v>4.841942016</x:v>
+      <x:c r="AJ70" s="103" t="n">
+        <x:f>IF(W70="",U70*E23*AH70*Q23*R23,"")</x:f>
+        <x:v>0.06732517855201926</x:v>
+      </x:c>
+      <x:c r="AK70" s="103" t="n">
+        <x:f>IF(A70,O70+AF70,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL70" s="103" t="n">
+        <x:f>IF(A70,AK70/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="22" customHeight="1">
       <x:c r="A71" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D41),D41&gt;0),AND(ISNUMBER(E41),E41&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C41),C41&gt;=2,MOD(C41,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I23),I23&gt;0),AND(ISNUMBER(J23),J23&gt;0),AND(ISNUMBER(K23),K23&gt;0),AND(ISNUMBER(L23),L23&gt;0),AND(ISNUMBER(D41),D41&gt;0),AND(ISNUMBER(E41),E41&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K23,1)=0,ISNUMBER(C41),C41&gt;=2,MOD(C41,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M23),M23&gt;=0,M23&lt;=1),AND(ISNUMBER(N23),N23&gt;=0,N23&lt;=1)),ISNUMBER(P23),P23&gt;0,ISNUMBER(Q23),Q23&gt;=0,Q23&lt;=1,ISNUMBER(R23),R23&gt;=0,R23&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B71" s="76" t="n">
@@ -16086,19 +17153,19 @@
         <x:v>0.0015417333333333334</x:v>
       </x:c>
       <x:c r="Q71" s="76" t="n">
-        <x:f>IF(A71,N71*1000/C71,"")</x:f>
-        <x:v>22.694314666666667</x:v>
+        <x:f>IF(A71,IF(C71&gt;AF71,N71*1000/(C71-AF71),""),"")</x:f>
+        <x:v>22.789377770668615</x:v>
       </x:c>
       <x:c r="R71" s="76" t="n">
-        <x:f>IF(W71="估算",IF(OR(K71=0,O71=0),0,1-((E23-1)*MAX(0,(C71-O71)/E23-(K71))+MAX(0,L71-((E23-1)*C71/E23+P71)-(K71)))/L71),"")</x:f>
-        <x:v>0.0021085715849469278</x:v>
+        <x:f>IF(W71="",IF(OR(K71=0,AK71=0),0,1-((E23-1)*MAX(0,(C71-AK71)/E23-(K71))+MAX(0,L71-((E23-1)*C71/E23+AL71)-(K71)))/L71),"")</x:f>
+        <x:v>0.002108594255478269</x:v>
       </x:c>
       <x:c r="S71" s="76" t="n">
-        <x:f>IF(W71="估算",IF(O71=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C71-O71)/E23-(L71-K71))+MAX(0,L71-((E23-1)*C71/E23+P71)-(L71-K71)))/L71))),"")</x:f>
-        <x:v>0.0011193897590531243</x:v>
+        <x:f>IF(W71="",IF(AK71=0,0,MAX(0,1-(1-((E23-1)*MAX(0,(C71-AK71)/E23-(L71-K71))+MAX(0,L71-((E23-1)*C71/E23+AL71)-(L71-K71)))/L71))),"")</x:f>
+        <x:v>0.0011193670885217832</x:v>
       </x:c>
       <x:c r="T71" s="76" t="n">
-        <x:f>IF(W71="估算",IF(OR(P71=0,K71=0,$J$7=0),0,IF(P71&lt;=(1-$J$7)*K71,$J$7*P71*K71/(1-$J$7)-$J$7^2*P71^2/(2*(1-$J$7)^2),$J$7*P71*K71+$J$7^2*K71^2/2)/L71),"")</x:f>
+        <x:f>IF(W71="",IF(OR(P71=0,K71=0,$J$7=0),0,IF(P71&lt;=(1-$J$7)*K71,$J$7*P71*K71/(1-$J$7)-$J$7^2*P71^2/(2*(1-$J$7)^2),$J$7*P71*K71+$J$7^2*K71^2/2)/L71),"")</x:f>
         <x:v>2.764806222784684e-7</x:v>
       </x:c>
       <x:c r="U71" s="76" t="n">
@@ -16106,21 +17173,76 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="V71" s="76" t="n">
-        <x:f>IF(W71="估算",U71*E23*T71*M23*N23,"")</x:f>
+        <x:f>IF(W71="",SUM(AI71:AJ71),"")</x:f>
+        <x:v>0.09575588686725103</x:v>
+      </x:c>
+      <x:c r="W71" s="76" t="str">
+        <x:f>IF(NOT(A71),"输入无效",IF(K71&gt;=L71,"KV 超载",IF(AK71&gt;C71+1e-9,"TPOT 不自洽",IF(OR(C71&gt;L71,MAX(P71,AG71)&gt;L71-K71),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X71" s="76" t="n">
+        <x:f>IF(W71="",U71*M71,"")</x:f>
+        <x:v>3.227961344</x:v>
+      </x:c>
+      <x:c r="Y71" s="103" t="n">
+        <x:f>IF(A71,K23*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z71" s="103" t="n">
+        <x:f>IF(A71,S23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA71" s="103" t="n">
+        <x:f>IF(A71,T23*ROUNDUP(K23/D23,0)*F23*2*2*(D23-1)/D23/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB71" s="103" t="n">
+        <x:f>IF(A71,U23*2*ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC71" s="103" t="n">
+        <x:f>IF(A71,ROUNDUP(K23/D23,0)*F23*2*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD71" s="103" t="n">
+        <x:f>IF(A71,K23*256*(2+4)*(D23-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE71" s="103" t="n">
+        <x:f>IF(A71,SUM(Y71:AD71),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF71" s="103" t="n">
+        <x:f>IF(A71,AE71*1000/P23,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG71" s="103" t="n">
+        <x:f>IF(A71,AF71/E23,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH71" s="103" t="n">
+        <x:f>IF(W71="",IF(OR(AG71=0,K71=0,$J$7=0),0,IF(AG71&lt;=(1-$J$7)*K71,$J$7*AG71*K71/(1-$J$7)-$J$7^2*AG71^2/(2*(1-$J$7)^2),$J$7*AG71*K71+$J$7^2*K71^2/2)/L71),"")</x:f>
+        <x:v>2.439318063478959e-7</x:v>
+      </x:c>
+      <x:c r="AI71" s="103" t="n">
+        <x:f>IF(W71="",U71*E23*T71*M23*N23,"")</x:f>
         <x:v>0.05087243449923819</x:v>
       </x:c>
-      <x:c r="W71" s="76" t="str">
-        <x:f>IF(NOT(A71),"输入无效",IF(K71&gt;=L71,"KV 超载",IF(O71&gt;C71+1e-9,"TPOT 不自洽",IF(OR(C71&gt;L71,P71&gt;L71-K71),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X71" s="76" t="n">
-        <x:f>IF(W71="估算",U71*M71,"")</x:f>
-        <x:v>3.227961344</x:v>
+      <x:c r="AJ71" s="103" t="n">
+        <x:f>IF(W71="",U71*E23*AH71*Q23*R23,"")</x:f>
+        <x:v>0.04488345236801285</x:v>
+      </x:c>
+      <x:c r="AK71" s="103" t="n">
+        <x:f>IF(A71,O71+AF71,"")</x:f>
+        <x:v>0.26698079999999996</x:v>
+      </x:c>
+      <x:c r="AL71" s="103" t="n">
+        <x:f>IF(A71,AK71/E23,"")</x:f>
+        <x:v>0.002901965217391304</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="22" customHeight="1">
       <x:c r="A72" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D42),D42&gt;0),AND(ISNUMBER(E42),E42&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C42),C42&gt;=2,MOD(C42,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D42),D42&gt;0),AND(ISNUMBER(E42),E42&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C42),C42&gt;=2,MOD(C42,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B72" s="76" t="n">
@@ -16184,19 +17306,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q72" s="76" t="n">
-        <x:f>IF(A72,N72*1000/C72,"")</x:f>
-        <x:v>140.084352</x:v>
+        <x:f>IF(A72,IF(C72&gt;AF72,N72*1000/(C72-AF72),""),"")</x:f>
+        <x:v>143.68042396579565</x:v>
       </x:c>
       <x:c r="R72" s="76" t="n">
-        <x:f>IF(W72="估算",IF(OR(K72=0,O72=0),0,1-((E24-1)*MAX(0,(C72-O72)/E24-(K72))+MAX(0,L72-((E24-1)*C72/E24+P72)-(K72)))/L72),"")</x:f>
-        <x:v>0.0016648159684782282</x:v>
+        <x:f>IF(W72="",IF(OR(K72=0,AK72=0),0,1-((E24-1)*MAX(0,(C72-AK72)/E24-(K72))+MAX(0,L72-((E24-1)*C72/E24+AL72)-(K72)))/L72),"")</x:f>
+        <x:v>0.0016651560264492327</x:v>
       </x:c>
       <x:c r="S72" s="76" t="n">
-        <x:f>IF(W72="估算",IF(O72=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C72-O72)/E24-(L72-K72))+MAX(0,L72-((E24-1)*C72/E24+P72)-(L72-K72)))/L72))),"")</x:f>
+        <x:f>IF(W72="",IF(AK72=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C72-AK72)/E24-(L72-K72))+MAX(0,L72-((E24-1)*C72/E24+AL72)-(L72-K72)))/L72))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T72" s="76" t="n">
-        <x:f>IF(W72="估算",IF(OR(P72=0,K72=0,$J$7=0),0,IF(P72&lt;=(1-$J$7)*K72,$J$7*P72*K72/(1-$J$7)-$J$7^2*P72^2/(2*(1-$J$7)^2),$J$7*P72*K72+$J$7^2*K72^2/2)/L72),"")</x:f>
+        <x:f>IF(W72="",IF(OR(P72=0,K72=0,$J$7=0),0,IF(P72&lt;=(1-$J$7)*K72,$J$7*P72*K72/(1-$J$7)-$J$7^2*P72^2/(2*(1-$J$7)^2),$J$7*P72*K72+$J$7^2*K72^2/2)/L72),"")</x:f>
         <x:v>7.542511228652778e-8</x:v>
       </x:c>
       <x:c r="U72" s="76" t="n">
@@ -16204,21 +17326,76 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="V72" s="76" t="n">
-        <x:f>IF(W72="估算",U72*E24*T72*M24*N24,"")</x:f>
+        <x:f>IF(W72="",SUM(AI72:AJ72),"")</x:f>
+        <x:v>0.15468122714756344</x:v>
+      </x:c>
+      <x:c r="W72" s="76" t="str">
+        <x:f>IF(NOT(A72),"输入无效",IF(K72&gt;=L72,"KV 超载",IF(AK72&gt;C72+1e-9,"TPOT 不自洽",IF(OR(C72&gt;L72,MAX(P72,AG72)&gt;L72-K72),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X72" s="76" t="n">
+        <x:f>IF(W72="",U72*M72,"")</x:f>
+        <x:v>5.1360768</x:v>
+      </x:c>
+      <x:c r="Y72" s="103" t="n">
+        <x:f>IF(A72,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z72" s="103" t="n">
+        <x:f>IF(A72,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA72" s="103" t="n">
+        <x:f>IF(A72,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB72" s="103" t="n">
+        <x:f>IF(A72,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC72" s="103" t="n">
+        <x:f>IF(A72,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD72" s="103" t="n">
+        <x:f>IF(A72,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE72" s="103" t="n">
+        <x:f>IF(A72,SUM(Y72:AD72),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF72" s="103" t="n">
+        <x:f>IF(A72,AE72*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG72" s="103" t="n">
+        <x:f>IF(A72,AF72/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH72" s="103" t="n">
+        <x:f>IF(W72="",IF(OR(AG72=0,K72=0,$J$7=0),0,IF(AG72&lt;=(1-$J$7)*K72,$J$7*AG72*K72/(1-$J$7)-$J$7^2*AG72^2/(2*(1-$J$7)^2),$J$7*AG72*K72+$J$7^2*K72^2/2)/L72),"")</x:f>
+        <x:v>6.468469491235216e-8</x:v>
+      </x:c>
+      <x:c r="AI72" s="103" t="n">
+        <x:f>IF(W72="",U72*E24*T72*M24*N24,"")</x:f>
         <x:v>0.08326932396432667</x:v>
       </x:c>
-      <x:c r="W72" s="76" t="str">
-        <x:f>IF(NOT(A72),"输入无效",IF(K72&gt;=L72,"KV 超载",IF(O72&gt;C72+1e-9,"TPOT 不自洽",IF(OR(C72&gt;L72,P72&gt;L72-K72),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X72" s="76" t="n">
-        <x:f>IF(W72="估算",U72*M72,"")</x:f>
-        <x:v>5.1360768</x:v>
+      <x:c r="AJ72" s="103" t="n">
+        <x:f>IF(W72="",U72*E24*AH72*Q24*R24,"")</x:f>
+        <x:v>0.07141190318323679</x:v>
+      </x:c>
+      <x:c r="AK72" s="103" t="n">
+        <x:f>IF(A72,O72+AF72,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL72" s="103" t="n">
+        <x:f>IF(A72,AK72/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="22" customHeight="1">
       <x:c r="A73" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D43),D43&gt;0),AND(ISNUMBER(E43),E43&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C43),C43&gt;=2,MOD(C43,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D43),D43&gt;0),AND(ISNUMBER(E43),E43&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C43),C43&gt;=2,MOD(C43,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B73" s="76" t="n">
@@ -16282,19 +17459,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q73" s="76" t="n">
-        <x:f>IF(A73,N73*1000/C73,"")</x:f>
-        <x:v>70.042176</x:v>
+        <x:f>IF(A73,IF(C73&gt;AF73,N73*1000/(C73-AF73),""),"")</x:f>
+        <x:v>70.92980098685632</x:v>
       </x:c>
       <x:c r="R73" s="76" t="n">
-        <x:f>IF(W73="估算",IF(OR(K73=0,O73=0),0,1-((E24-1)*MAX(0,(C73-O73)/E24-(K73))+MAX(0,L73-((E24-1)*C73/E24+P73)-(K73)))/L73),"")</x:f>
-        <x:v>0.002901229011956552</x:v>
+        <x:f>IF(W73="",IF(OR(K73=0,AK73=0),0,1-((E24-1)*MAX(0,(C73-AK73)/E24-(K73))+MAX(0,L73-((E24-1)*C73/E24+AL73)-(K73)))/L73),"")</x:f>
+        <x:v>0.0029015690699275565</x:v>
       </x:c>
       <x:c r="S73" s="76" t="n">
-        <x:f>IF(W73="估算",IF(O73=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C73-O73)/E24-(L73-K73))+MAX(0,L73-((E24-1)*C73/E24+P73)-(L73-K73)))/L73))),"")</x:f>
+        <x:f>IF(W73="",IF(AK73=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C73-AK73)/E24-(L73-K73))+MAX(0,L73-((E24-1)*C73/E24+AL73)-(L73-K73)))/L73))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T73" s="76" t="n">
-        <x:f>IF(W73="估算",IF(OR(P73=0,K73=0,$J$7=0),0,IF(P73&lt;=(1-$J$7)*K73,$J$7*P73*K73/(1-$J$7)-$J$7^2*P73^2/(2*(1-$J$7)^2),$J$7*P73*K73+$J$7^2*K73^2/2)/L73),"")</x:f>
+        <x:f>IF(W73="",IF(OR(P73=0,K73=0,$J$7=0),0,IF(P73&lt;=(1-$J$7)*K73,$J$7*P73*K73/(1-$J$7)-$J$7^2*P73^2/(2*(1-$J$7)^2),$J$7*P73*K73+$J$7^2*K73^2/2)/L73),"")</x:f>
         <x:v>7.542511228652778e-8</x:v>
       </x:c>
       <x:c r="U73" s="76" t="n">
@@ -16302,21 +17479,76 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="V73" s="76" t="n">
-        <x:f>IF(W73="估算",U73*E24*T73*M24*N24,"")</x:f>
+        <x:f>IF(W73="",SUM(AI73:AJ73),"")</x:f>
+        <x:v>0.07734061357378172</x:v>
+      </x:c>
+      <x:c r="W73" s="76" t="str">
+        <x:f>IF(NOT(A73),"输入无效",IF(K73&gt;=L73,"KV 超载",IF(AK73&gt;C73+1e-9,"TPOT 不自洽",IF(OR(C73&gt;L73,MAX(P73,AG73)&gt;L73-K73),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X73" s="76" t="n">
+        <x:f>IF(W73="",U73*M73,"")</x:f>
+        <x:v>2.5680384</x:v>
+      </x:c>
+      <x:c r="Y73" s="103" t="n">
+        <x:f>IF(A73,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z73" s="103" t="n">
+        <x:f>IF(A73,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA73" s="103" t="n">
+        <x:f>IF(A73,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB73" s="103" t="n">
+        <x:f>IF(A73,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC73" s="103" t="n">
+        <x:f>IF(A73,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD73" s="103" t="n">
+        <x:f>IF(A73,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE73" s="103" t="n">
+        <x:f>IF(A73,SUM(Y73:AD73),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF73" s="103" t="n">
+        <x:f>IF(A73,AE73*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG73" s="103" t="n">
+        <x:f>IF(A73,AF73/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH73" s="103" t="n">
+        <x:f>IF(W73="",IF(OR(AG73=0,K73=0,$J$7=0),0,IF(AG73&lt;=(1-$J$7)*K73,$J$7*AG73*K73/(1-$J$7)-$J$7^2*AG73^2/(2*(1-$J$7)^2),$J$7*AG73*K73+$J$7^2*K73^2/2)/L73),"")</x:f>
+        <x:v>6.468469491235216e-8</x:v>
+      </x:c>
+      <x:c r="AI73" s="103" t="n">
+        <x:f>IF(W73="",U73*E24*T73*M24*N24,"")</x:f>
         <x:v>0.04163466198216333</x:v>
       </x:c>
-      <x:c r="W73" s="76" t="str">
-        <x:f>IF(NOT(A73),"输入无效",IF(K73&gt;=L73,"KV 超载",IF(O73&gt;C73+1e-9,"TPOT 不自洽",IF(OR(C73&gt;L73,P73&gt;L73-K73),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X73" s="76" t="n">
-        <x:f>IF(W73="估算",U73*M73,"")</x:f>
-        <x:v>2.5680384</x:v>
+      <x:c r="AJ73" s="103" t="n">
+        <x:f>IF(W73="",U73*E24*AH73*Q24*R24,"")</x:f>
+        <x:v>0.03570595159161839</x:v>
+      </x:c>
+      <x:c r="AK73" s="103" t="n">
+        <x:f>IF(A73,O73+AF73,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL73" s="103" t="n">
+        <x:f>IF(A73,AK73/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="22" customHeight="1">
       <x:c r="A74" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D44),D44&gt;0),AND(ISNUMBER(E44),E44&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C44),C44&gt;=2,MOD(C44,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D44),D44&gt;0),AND(ISNUMBER(E44),E44&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C44),C44&gt;=2,MOD(C44,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B74" s="76" t="n">
@@ -16380,19 +17612,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q74" s="76" t="n">
-        <x:f>IF(A74,N74*1000/C74,"")</x:f>
-        <x:v>35.021088</x:v>
+        <x:f>IF(A74,IF(C74&gt;AF74,N74*1000/(C74-AF74),""),"")</x:f>
+        <x:v>35.24159702200649</x:v>
       </x:c>
       <x:c r="R74" s="76" t="n">
-        <x:f>IF(W74="估算",IF(OR(K74=0,O74=0),0,1-((E24-1)*MAX(0,(C74-O74)/E24-(K74))+MAX(0,L74-((E24-1)*C74/E24+P74)-(K74)))/L74),"")</x:f>
-        <x:v>0.005374055098912978</x:v>
+        <x:f>IF(W74="",IF(OR(K74=0,AK74=0),0,1-((E24-1)*MAX(0,(C74-AK74)/E24-(K74))+MAX(0,L74-((E24-1)*C74/E24+AL74)-(K74)))/L74),"")</x:f>
+        <x:v>0.005374395156883982</x:v>
       </x:c>
       <x:c r="S74" s="76" t="n">
-        <x:f>IF(W74="估算",IF(O74=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C74-O74)/E24-(L74-K74))+MAX(0,L74-((E24-1)*C74/E24+P74)-(L74-K74)))/L74))),"")</x:f>
+        <x:f>IF(W74="",IF(AK74=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C74-AK74)/E24-(L74-K74))+MAX(0,L74-((E24-1)*C74/E24+AL74)-(L74-K74)))/L74))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T74" s="76" t="n">
-        <x:f>IF(W74="估算",IF(OR(P74=0,K74=0,$J$7=0),0,IF(P74&lt;=(1-$J$7)*K74,$J$7*P74*K74/(1-$J$7)-$J$7^2*P74^2/(2*(1-$J$7)^2),$J$7*P74*K74+$J$7^2*K74^2/2)/L74),"")</x:f>
+        <x:f>IF(W74="",IF(OR(P74=0,K74=0,$J$7=0),0,IF(P74&lt;=(1-$J$7)*K74,$J$7*P74*K74/(1-$J$7)-$J$7^2*P74^2/(2*(1-$J$7)^2),$J$7*P74*K74+$J$7^2*K74^2/2)/L74),"")</x:f>
         <x:v>7.542511228652778e-8</x:v>
       </x:c>
       <x:c r="U74" s="76" t="n">
@@ -16400,21 +17632,76 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="V74" s="76" t="n">
-        <x:f>IF(W74="估算",U74*E24*T74*M24*N24,"")</x:f>
+        <x:f>IF(W74="",SUM(AI74:AJ74),"")</x:f>
+        <x:v>0.03867030678689086</x:v>
+      </x:c>
+      <x:c r="W74" s="76" t="str">
+        <x:f>IF(NOT(A74),"输入无效",IF(K74&gt;=L74,"KV 超载",IF(AK74&gt;C74+1e-9,"TPOT 不自洽",IF(OR(C74&gt;L74,MAX(P74,AG74)&gt;L74-K74),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X74" s="76" t="n">
+        <x:f>IF(W74="",U74*M74,"")</x:f>
+        <x:v>1.2840192</x:v>
+      </x:c>
+      <x:c r="Y74" s="103" t="n">
+        <x:f>IF(A74,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z74" s="103" t="n">
+        <x:f>IF(A74,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA74" s="103" t="n">
+        <x:f>IF(A74,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB74" s="103" t="n">
+        <x:f>IF(A74,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC74" s="103" t="n">
+        <x:f>IF(A74,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD74" s="103" t="n">
+        <x:f>IF(A74,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE74" s="103" t="n">
+        <x:f>IF(A74,SUM(Y74:AD74),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF74" s="103" t="n">
+        <x:f>IF(A74,AE74*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG74" s="103" t="n">
+        <x:f>IF(A74,AF74/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH74" s="103" t="n">
+        <x:f>IF(W74="",IF(OR(AG74=0,K74=0,$J$7=0),0,IF(AG74&lt;=(1-$J$7)*K74,$J$7*AG74*K74/(1-$J$7)-$J$7^2*AG74^2/(2*(1-$J$7)^2),$J$7*AG74*K74+$J$7^2*K74^2/2)/L74),"")</x:f>
+        <x:v>6.468469491235216e-8</x:v>
+      </x:c>
+      <x:c r="AI74" s="103" t="n">
+        <x:f>IF(W74="",U74*E24*T74*M24*N24,"")</x:f>
         <x:v>0.020817330991081667</x:v>
       </x:c>
-      <x:c r="W74" s="76" t="str">
-        <x:f>IF(NOT(A74),"输入无效",IF(K74&gt;=L74,"KV 超载",IF(O74&gt;C74+1e-9,"TPOT 不自洽",IF(OR(C74&gt;L74,P74&gt;L74-K74),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X74" s="76" t="n">
-        <x:f>IF(W74="估算",U74*M74,"")</x:f>
-        <x:v>1.2840192</x:v>
+      <x:c r="AJ74" s="103" t="n">
+        <x:f>IF(W74="",U74*E24*AH74*Q24*R24,"")</x:f>
+        <x:v>0.017852975795809196</x:v>
+      </x:c>
+      <x:c r="AK74" s="103" t="n">
+        <x:f>IF(A74,O74+AF74,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL74" s="103" t="n">
+        <x:f>IF(A74,AK74/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="22" customHeight="1">
       <x:c r="A75" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D45),D45&gt;0),AND(ISNUMBER(E45),E45&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C45),C45&gt;=2,MOD(C45,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D45),D45&gt;0),AND(ISNUMBER(E45),E45&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C45),C45&gt;=2,MOD(C45,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B75" s="76" t="n">
@@ -16478,19 +17765,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q75" s="76" t="n">
-        <x:f>IF(A75,N75*1000/C75,"")</x:f>
-        <x:v>23.347392</x:v>
+        <x:f>IF(A75,IF(C75&gt;AF75,N75*1000/(C75-AF75),""),"")</x:f>
+        <x:v>23.445190747680634</x:v>
       </x:c>
       <x:c r="R75" s="76" t="n">
-        <x:f>IF(W75="估算",IF(OR(K75=0,O75=0),0,1-((E24-1)*MAX(0,(C75-O75)/E24-(K75))+MAX(0,L75-((E24-1)*C75/E24+P75)-(K75)))/L75),"")</x:f>
-        <x:v>0.007846881185869514</x:v>
+        <x:f>IF(W75="",IF(OR(K75=0,AK75=0),0,1-((E24-1)*MAX(0,(C75-AK75)/E24-(K75))+MAX(0,L75-((E24-1)*C75/E24+AL75)-(K75)))/L75),"")</x:f>
+        <x:v>0.007847221243840519</x:v>
       </x:c>
       <x:c r="S75" s="76" t="n">
-        <x:f>IF(W75="估算",IF(O75=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C75-O75)/E24-(L75-K75))+MAX(0,L75-((E24-1)*C75/E24+P75)-(L75-K75)))/L75))),"")</x:f>
+        <x:f>IF(W75="",IF(AK75=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C75-AK75)/E24-(L75-K75))+MAX(0,L75-((E24-1)*C75/E24+AL75)-(L75-K75)))/L75))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T75" s="76" t="n">
-        <x:f>IF(W75="估算",IF(OR(P75=0,K75=0,$J$7=0),0,IF(P75&lt;=(1-$J$7)*K75,$J$7*P75*K75/(1-$J$7)-$J$7^2*P75^2/(2*(1-$J$7)^2),$J$7*P75*K75+$J$7^2*K75^2/2)/L75),"")</x:f>
+        <x:f>IF(W75="",IF(OR(P75=0,K75=0,$J$7=0),0,IF(P75&lt;=(1-$J$7)*K75,$J$7*P75*K75/(1-$J$7)-$J$7^2*P75^2/(2*(1-$J$7)^2),$J$7*P75*K75+$J$7^2*K75^2/2)/L75),"")</x:f>
         <x:v>7.542511228652778e-8</x:v>
       </x:c>
       <x:c r="U75" s="76" t="n">
@@ -16498,21 +17785,76 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="V75" s="76" t="n">
-        <x:f>IF(W75="估算",U75*E24*T75*M24*N24,"")</x:f>
+        <x:f>IF(W75="",SUM(AI75:AJ75),"")</x:f>
+        <x:v>0.02578020452459391</x:v>
+      </x:c>
+      <x:c r="W75" s="76" t="str">
+        <x:f>IF(NOT(A75),"输入无效",IF(K75&gt;=L75,"KV 超载",IF(AK75&gt;C75+1e-9,"TPOT 不自洽",IF(OR(C75&gt;L75,MAX(P75,AG75)&gt;L75-K75),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X75" s="76" t="n">
+        <x:f>IF(W75="",U75*M75,"")</x:f>
+        <x:v>0.8560128</x:v>
+      </x:c>
+      <x:c r="Y75" s="103" t="n">
+        <x:f>IF(A75,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z75" s="103" t="n">
+        <x:f>IF(A75,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA75" s="103" t="n">
+        <x:f>IF(A75,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB75" s="103" t="n">
+        <x:f>IF(A75,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC75" s="103" t="n">
+        <x:f>IF(A75,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD75" s="103" t="n">
+        <x:f>IF(A75,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE75" s="103" t="n">
+        <x:f>IF(A75,SUM(Y75:AD75),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF75" s="103" t="n">
+        <x:f>IF(A75,AE75*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG75" s="103" t="n">
+        <x:f>IF(A75,AF75/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH75" s="103" t="n">
+        <x:f>IF(W75="",IF(OR(AG75=0,K75=0,$J$7=0),0,IF(AG75&lt;=(1-$J$7)*K75,$J$7*AG75*K75/(1-$J$7)-$J$7^2*AG75^2/(2*(1-$J$7)^2),$J$7*AG75*K75+$J$7^2*K75^2/2)/L75),"")</x:f>
+        <x:v>6.468469491235216e-8</x:v>
+      </x:c>
+      <x:c r="AI75" s="103" t="n">
+        <x:f>IF(W75="",U75*E24*T75*M24*N24,"")</x:f>
         <x:v>0.013878220660721112</x:v>
       </x:c>
-      <x:c r="W75" s="76" t="str">
-        <x:f>IF(NOT(A75),"输入无效",IF(K75&gt;=L75,"KV 超载",IF(O75&gt;C75+1e-9,"TPOT 不自洽",IF(OR(C75&gt;L75,P75&gt;L75-K75),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X75" s="76" t="n">
-        <x:f>IF(W75="估算",U75*M75,"")</x:f>
-        <x:v>0.8560128</x:v>
+      <x:c r="AJ75" s="103" t="n">
+        <x:f>IF(W75="",U75*E24*AH75*Q24*R24,"")</x:f>
+        <x:v>0.011901983863872798</x:v>
+      </x:c>
+      <x:c r="AK75" s="103" t="n">
+        <x:f>IF(A75,O75+AF75,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL75" s="103" t="n">
+        <x:f>IF(A75,AK75/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="22" customHeight="1">
       <x:c r="A76" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D46),D46&gt;0),AND(ISNUMBER(E46),E46&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C46),C46&gt;=2,MOD(C46,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D46),D46&gt;0),AND(ISNUMBER(E46),E46&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C46),C46&gt;=2,MOD(C46,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B76" s="76" t="n">
@@ -16576,19 +17918,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q76" s="76" t="n">
-        <x:f>IF(A76,N76*1000/C76,"")</x:f>
-        <x:v>140.084352</x:v>
+        <x:f>IF(A76,IF(C76&gt;AF76,N76*1000/(C76-AF76),""),"")</x:f>
+        <x:v>143.68042396579565</x:v>
       </x:c>
       <x:c r="R76" s="76" t="n">
-        <x:f>IF(W76="估算",IF(OR(K76=0,O76=0),0,1-((E24-1)*MAX(0,(C76-O76)/E24-(K76))+MAX(0,L76-((E24-1)*C76/E24+P76)-(K76)))/L76),"")</x:f>
-        <x:v>0.001465425273695642</x:v>
+        <x:f>IF(W76="",IF(OR(K76=0,AK76=0),0,1-((E24-1)*MAX(0,(C76-AK76)/E24-(K76))+MAX(0,L76-((E24-1)*C76/E24+AL76)-(K76)))/L76),"")</x:f>
+        <x:v>0.0014654932852899982</x:v>
       </x:c>
       <x:c r="S76" s="76" t="n">
-        <x:f>IF(W76="估算",IF(O76=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C76-O76)/E24-(L76-K76))+MAX(0,L76-((E24-1)*C76/E24+P76)-(L76-K76)))/L76))),"")</x:f>
-        <x:v>0.0009707014463045116</x:v>
+        <x:f>IF(W76="",IF(AK76=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C76-AK76)/E24-(L76-K76))+MAX(0,L76-((E24-1)*C76/E24+AL76)-(L76-K76)))/L76))),"")</x:f>
+        <x:v>0.0009706334347101553</x:v>
       </x:c>
       <x:c r="T76" s="76" t="n">
-        <x:f>IF(W76="估算",IF(OR(P76=0,K76=0,$J$7=0),0,IF(P76&lt;=(1-$J$7)*K76,$J$7*P76*K76/(1-$J$7)-$J$7^2*P76^2/(2*(1-$J$7)^2),$J$7*P76*K76+$J$7^2*K76^2/2)/L76),"")</x:f>
+        <x:f>IF(W76="",IF(OR(P76=0,K76=0,$J$7=0),0,IF(P76&lt;=(1-$J$7)*K76,$J$7*P76*K76/(1-$J$7)-$J$7^2*P76^2/(2*(1-$J$7)^2),$J$7*P76*K76+$J$7^2*K76^2/2)/L76),"")</x:f>
         <x:v>2.1466258968930553e-7</x:v>
       </x:c>
       <x:c r="U76" s="76" t="n">
@@ -16596,21 +17938,76 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="V76" s="76" t="n">
-        <x:f>IF(W76="估算",U76*E24*T76*M24*N24,"")</x:f>
+        <x:f>IF(W76="",SUM(AI76:AJ76),"")</x:f>
+        <x:v>0.4402269658411606</x:v>
+      </x:c>
+      <x:c r="W76" s="76" t="str">
+        <x:f>IF(NOT(A76),"输入无效",IF(K76&gt;=L76,"KV 超载",IF(AK76&gt;C76+1e-9,"TPOT 不自洽",IF(OR(C76&gt;L76,MAX(P76,AG76)&gt;L76-K76),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X76" s="76" t="n">
+        <x:f>IF(W76="",U76*M76,"")</x:f>
+        <x:v>14.61676032</x:v>
+      </x:c>
+      <x:c r="Y76" s="103" t="n">
+        <x:f>IF(A76,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z76" s="103" t="n">
+        <x:f>IF(A76,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA76" s="103" t="n">
+        <x:f>IF(A76,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB76" s="103" t="n">
+        <x:f>IF(A76,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC76" s="103" t="n">
+        <x:f>IF(A76,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD76" s="103" t="n">
+        <x:f>IF(A76,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE76" s="103" t="n">
+        <x:f>IF(A76,SUM(Y76:AD76),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF76" s="103" t="n">
+        <x:f>IF(A76,AE76*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG76" s="103" t="n">
+        <x:f>IF(A76,AF76/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH76" s="103" t="n">
+        <x:f>IF(W76="",IF(OR(AG76=0,K76=0,$J$7=0),0,IF(AG76&lt;=(1-$J$7)*K76,$J$7*AG76*K76/(1-$J$7)-$J$7^2*AG76^2/(2*(1-$J$7)^2),$J$7*AG76*K76+$J$7^2*K76^2/2)/L76),"")</x:f>
+        <x:v>1.8409371994942692e-7</x:v>
+      </x:c>
+      <x:c r="AI76" s="103" t="n">
+        <x:f>IF(W76="",U76*E24*T76*M24*N24,"")</x:f>
         <x:v>0.23698749901699329</x:v>
       </x:c>
-      <x:c r="W76" s="76" t="str">
-        <x:f>IF(NOT(A76),"输入无效",IF(K76&gt;=L76,"KV 超载",IF(O76&gt;C76+1e-9,"TPOT 不自洽",IF(OR(C76&gt;L76,P76&gt;L76-K76),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X76" s="76" t="n">
-        <x:f>IF(W76="估算",U76*M76,"")</x:f>
-        <x:v>14.61676032</x:v>
+      <x:c r="AJ76" s="103" t="n">
+        <x:f>IF(W76="",U76*E24*AH76*Q24*R24,"")</x:f>
+        <x:v>0.20323946682416733</x:v>
+      </x:c>
+      <x:c r="AK76" s="103" t="n">
+        <x:f>IF(A76,O76+AF76,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL76" s="103" t="n">
+        <x:f>IF(A76,AK76/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="22" customHeight="1">
       <x:c r="A77" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D47),D47&gt;0),AND(ISNUMBER(E47),E47&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C47),C47&gt;=2,MOD(C47,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D47),D47&gt;0),AND(ISNUMBER(E47),E47&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C47),C47&gt;=2,MOD(C47,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B77" s="76" t="n">
@@ -16674,19 +18071,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q77" s="76" t="n">
-        <x:f>IF(A77,N77*1000/C77,"")</x:f>
-        <x:v>70.042176</x:v>
+        <x:f>IF(A77,IF(C77&gt;AF77,N77*1000/(C77-AF77),""),"")</x:f>
+        <x:v>70.92980098685632</x:v>
       </x:c>
       <x:c r="R77" s="76" t="n">
-        <x:f>IF(W77="估算",IF(OR(K77=0,O77=0),0,1-((E24-1)*MAX(0,(C77-O77)/E24-(K77))+MAX(0,L77-((E24-1)*C77/E24+P77)-(K77)))/L77),"")</x:f>
-        <x:v>0.0017127078823914177</x:v>
+        <x:f>IF(W77="",IF(OR(K77=0,AK77=0),0,1-((E24-1)*MAX(0,(C77-AK77)/E24-(K77))+MAX(0,L77-((E24-1)*C77/E24+AL77)-(K77)))/L77),"")</x:f>
+        <x:v>0.001712775893985552</x:v>
       </x:c>
       <x:c r="S77" s="76" t="n">
-        <x:f>IF(W77="估算",IF(O77=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C77-O77)/E24-(L77-K77))+MAX(0,L77-((E24-1)*C77/E24+P77)-(L77-K77)))/L77))),"")</x:f>
-        <x:v>0.0007234188376087358</x:v>
+        <x:f>IF(W77="",IF(AK77=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C77-AK77)/E24-(L77-K77))+MAX(0,L77-((E24-1)*C77/E24+AL77)-(L77-K77)))/L77))),"")</x:f>
+        <x:v>0.0007233508260146015</x:v>
       </x:c>
       <x:c r="T77" s="76" t="n">
-        <x:f>IF(W77="估算",IF(OR(P77=0,K77=0,$J$7=0),0,IF(P77&lt;=(1-$J$7)*K77,$J$7*P77*K77/(1-$J$7)-$J$7^2*P77^2/(2*(1-$J$7)^2),$J$7*P77*K77+$J$7^2*K77^2/2)/L77),"")</x:f>
+        <x:f>IF(W77="",IF(OR(P77=0,K77=0,$J$7=0),0,IF(P77&lt;=(1-$J$7)*K77,$J$7*P77*K77/(1-$J$7)-$J$7^2*P77^2/(2*(1-$J$7)^2),$J$7*P77*K77+$J$7^2*K77^2/2)/L77),"")</x:f>
         <x:v>2.1466258968930553e-7</x:v>
       </x:c>
       <x:c r="U77" s="76" t="n">
@@ -16694,21 +18091,76 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="V77" s="76" t="n">
-        <x:f>IF(W77="估算",U77*E24*T77*M24*N24,"")</x:f>
+        <x:f>IF(W77="",SUM(AI77:AJ77),"")</x:f>
+        <x:v>0.2201134829205803</x:v>
+      </x:c>
+      <x:c r="W77" s="76" t="str">
+        <x:f>IF(NOT(A77),"输入无效",IF(K77&gt;=L77,"KV 超载",IF(AK77&gt;C77+1e-9,"TPOT 不自洽",IF(OR(C77&gt;L77,MAX(P77,AG77)&gt;L77-K77),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X77" s="76" t="n">
+        <x:f>IF(W77="",U77*M77,"")</x:f>
+        <x:v>7.30838016</x:v>
+      </x:c>
+      <x:c r="Y77" s="103" t="n">
+        <x:f>IF(A77,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z77" s="103" t="n">
+        <x:f>IF(A77,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA77" s="103" t="n">
+        <x:f>IF(A77,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB77" s="103" t="n">
+        <x:f>IF(A77,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC77" s="103" t="n">
+        <x:f>IF(A77,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD77" s="103" t="n">
+        <x:f>IF(A77,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE77" s="103" t="n">
+        <x:f>IF(A77,SUM(Y77:AD77),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF77" s="103" t="n">
+        <x:f>IF(A77,AE77*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG77" s="103" t="n">
+        <x:f>IF(A77,AF77/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH77" s="103" t="n">
+        <x:f>IF(W77="",IF(OR(AG77=0,K77=0,$J$7=0),0,IF(AG77&lt;=(1-$J$7)*K77,$J$7*AG77*K77/(1-$J$7)-$J$7^2*AG77^2/(2*(1-$J$7)^2),$J$7*AG77*K77+$J$7^2*K77^2/2)/L77),"")</x:f>
+        <x:v>1.8409371994942692e-7</x:v>
+      </x:c>
+      <x:c r="AI77" s="103" t="n">
+        <x:f>IF(W77="",U77*E24*T77*M24*N24,"")</x:f>
         <x:v>0.11849374950849664</x:v>
       </x:c>
-      <x:c r="W77" s="76" t="str">
-        <x:f>IF(NOT(A77),"输入无效",IF(K77&gt;=L77,"KV 超载",IF(O77&gt;C77+1e-9,"TPOT 不自洽",IF(OR(C77&gt;L77,P77&gt;L77-K77),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X77" s="76" t="n">
-        <x:f>IF(W77="估算",U77*M77,"")</x:f>
-        <x:v>7.30838016</x:v>
+      <x:c r="AJ77" s="103" t="n">
+        <x:f>IF(W77="",U77*E24*AH77*Q24*R24,"")</x:f>
+        <x:v>0.10161973341208366</x:v>
+      </x:c>
+      <x:c r="AK77" s="103" t="n">
+        <x:f>IF(A77,O77+AF77,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL77" s="103" t="n">
+        <x:f>IF(A77,AK77/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="22" customHeight="1">
       <x:c r="A78" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D48),D48&gt;0),AND(ISNUMBER(E48),E48&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C48),C48&gt;=2,MOD(C48,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D48),D48&gt;0),AND(ISNUMBER(E48),E48&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C48),C48&gt;=2,MOD(C48,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B78" s="76" t="n">
@@ -16772,19 +18224,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q78" s="76" t="n">
-        <x:f>IF(A78,N78*1000/C78,"")</x:f>
-        <x:v>35.021088</x:v>
+        <x:f>IF(A78,IF(C78&gt;AF78,N78*1000/(C78-AF78),""),"")</x:f>
+        <x:v>35.24159702200649</x:v>
       </x:c>
       <x:c r="R78" s="76" t="n">
-        <x:f>IF(W78="估算",IF(OR(K78=0,O78=0),0,1-((E24-1)*MAX(0,(C78-O78)/E24-(K78))+MAX(0,L78-((E24-1)*C78/E24+P78)-(K78)))/L78),"")</x:f>
-        <x:v>0.002207273099782636</x:v>
+        <x:f>IF(W78="",IF(OR(K78=0,AK78=0),0,1-((E24-1)*MAX(0,(C78-AK78)/E24-(K78))+MAX(0,L78-((E24-1)*C78/E24+AL78)-(K78)))/L78),"")</x:f>
+        <x:v>0.0022073411113767705</x:v>
       </x:c>
       <x:c r="S78" s="76" t="n">
-        <x:f>IF(W78="估算",IF(O78=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C78-O78)/E24-(L78-K78))+MAX(0,L78-((E24-1)*C78/E24+P78)-(L78-K78)))/L78))),"")</x:f>
-        <x:v>0.00022885362021751732</x:v>
+        <x:f>IF(W78="",IF(AK78=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C78-AK78)/E24-(L78-K78))+MAX(0,L78-((E24-1)*C78/E24+AL78)-(L78-K78)))/L78))),"")</x:f>
+        <x:v>0.00022878560862338304</x:v>
       </x:c>
       <x:c r="T78" s="76" t="n">
-        <x:f>IF(W78="估算",IF(OR(P78=0,K78=0,$J$7=0),0,IF(P78&lt;=(1-$J$7)*K78,$J$7*P78*K78/(1-$J$7)-$J$7^2*P78^2/(2*(1-$J$7)^2),$J$7*P78*K78+$J$7^2*K78^2/2)/L78),"")</x:f>
+        <x:f>IF(W78="",IF(OR(P78=0,K78=0,$J$7=0),0,IF(P78&lt;=(1-$J$7)*K78,$J$7*P78*K78/(1-$J$7)-$J$7^2*P78^2/(2*(1-$J$7)^2),$J$7*P78*K78+$J$7^2*K78^2/2)/L78),"")</x:f>
         <x:v>2.1466258968930553e-7</x:v>
       </x:c>
       <x:c r="U78" s="76" t="n">
@@ -16792,21 +18244,76 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="V78" s="76" t="n">
-        <x:f>IF(W78="估算",U78*E24*T78*M24*N24,"")</x:f>
+        <x:f>IF(W78="",SUM(AI78:AJ78),"")</x:f>
+        <x:v>0.11005674146029015</x:v>
+      </x:c>
+      <x:c r="W78" s="76" t="str">
+        <x:f>IF(NOT(A78),"输入无效",IF(K78&gt;=L78,"KV 超载",IF(AK78&gt;C78+1e-9,"TPOT 不自洽",IF(OR(C78&gt;L78,MAX(P78,AG78)&gt;L78-K78),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X78" s="76" t="n">
+        <x:f>IF(W78="",U78*M78,"")</x:f>
+        <x:v>3.65419008</x:v>
+      </x:c>
+      <x:c r="Y78" s="103" t="n">
+        <x:f>IF(A78,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z78" s="103" t="n">
+        <x:f>IF(A78,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA78" s="103" t="n">
+        <x:f>IF(A78,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB78" s="103" t="n">
+        <x:f>IF(A78,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC78" s="103" t="n">
+        <x:f>IF(A78,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD78" s="103" t="n">
+        <x:f>IF(A78,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE78" s="103" t="n">
+        <x:f>IF(A78,SUM(Y78:AD78),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF78" s="103" t="n">
+        <x:f>IF(A78,AE78*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG78" s="103" t="n">
+        <x:f>IF(A78,AF78/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH78" s="103" t="n">
+        <x:f>IF(W78="",IF(OR(AG78=0,K78=0,$J$7=0),0,IF(AG78&lt;=(1-$J$7)*K78,$J$7*AG78*K78/(1-$J$7)-$J$7^2*AG78^2/(2*(1-$J$7)^2),$J$7*AG78*K78+$J$7^2*K78^2/2)/L78),"")</x:f>
+        <x:v>1.8409371994942692e-7</x:v>
+      </x:c>
+      <x:c r="AI78" s="103" t="n">
+        <x:f>IF(W78="",U78*E24*T78*M24*N24,"")</x:f>
         <x:v>0.05924687475424832</x:v>
       </x:c>
-      <x:c r="W78" s="76" t="str">
-        <x:f>IF(NOT(A78),"输入无效",IF(K78&gt;=L78,"KV 超载",IF(O78&gt;C78+1e-9,"TPOT 不自洽",IF(OR(C78&gt;L78,P78&gt;L78-K78),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X78" s="76" t="n">
-        <x:f>IF(W78="估算",U78*M78,"")</x:f>
-        <x:v>3.65419008</x:v>
+      <x:c r="AJ78" s="103" t="n">
+        <x:f>IF(W78="",U78*E24*AH78*Q24*R24,"")</x:f>
+        <x:v>0.05080986670604183</x:v>
+      </x:c>
+      <x:c r="AK78" s="103" t="n">
+        <x:f>IF(A78,O78+AF78,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL78" s="103" t="n">
+        <x:f>IF(A78,AK78/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="22" customHeight="1">
       <x:c r="A79" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D49),D49&gt;0),AND(ISNUMBER(E49),E49&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C49),C49&gt;=2,MOD(C49,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D49),D49&gt;0),AND(ISNUMBER(E49),E49&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C49),C49&gt;=2,MOD(C49,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B79" s="76" t="n">
@@ -16870,19 +18377,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q79" s="76" t="n">
-        <x:f>IF(A79,N79*1000/C79,"")</x:f>
-        <x:v>23.347392</x:v>
+        <x:f>IF(A79,IF(C79&gt;AF79,N79*1000/(C79-AF79),""),"")</x:f>
+        <x:v>23.445190747680634</x:v>
       </x:c>
       <x:c r="R79" s="76" t="n">
-        <x:f>IF(W79="估算",IF(OR(K79=0,O79=0),0,1-((E24-1)*MAX(0,(C79-O79)/E24-(K79))+MAX(0,L79-((E24-1)*C79/E24+P79)-(K79)))/L79),"")</x:f>
-        <x:v>0.0027018383171740767</x:v>
+        <x:f>IF(W79="",IF(OR(K79=0,AK79=0),0,1-((E24-1)*MAX(0,(C79-AK79)/E24-(K79))+MAX(0,L79-((E24-1)*C79/E24+AL79)-(K79)))/L79),"")</x:f>
+        <x:v>0.002701906328768211</x:v>
       </x:c>
       <x:c r="S79" s="76" t="n">
-        <x:f>IF(W79="估算",IF(O79=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C79-O79)/E24-(L79-K79))+MAX(0,L79-((E24-1)*C79/E24+P79)-(L79-K79)))/L79))),"")</x:f>
+        <x:f>IF(W79="",IF(AK79=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C79-AK79)/E24-(L79-K79))+MAX(0,L79-((E24-1)*C79/E24+AL79)-(L79-K79)))/L79))),"")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="T79" s="76" t="n">
-        <x:f>IF(W79="估算",IF(OR(P79=0,K79=0,$J$7=0),0,IF(P79&lt;=(1-$J$7)*K79,$J$7*P79*K79/(1-$J$7)-$J$7^2*P79^2/(2*(1-$J$7)^2),$J$7*P79*K79+$J$7^2*K79^2/2)/L79),"")</x:f>
+        <x:f>IF(W79="",IF(OR(P79=0,K79=0,$J$7=0),0,IF(P79&lt;=(1-$J$7)*K79,$J$7*P79*K79/(1-$J$7)-$J$7^2*P79^2/(2*(1-$J$7)^2),$J$7*P79*K79+$J$7^2*K79^2/2)/L79),"")</x:f>
         <x:v>2.1466258968930553e-7</x:v>
       </x:c>
       <x:c r="U79" s="76" t="n">
@@ -16890,21 +18397,76 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="V79" s="76" t="n">
-        <x:f>IF(W79="估算",U79*E24*T79*M24*N24,"")</x:f>
+        <x:f>IF(W79="",SUM(AI79:AJ79),"")</x:f>
+        <x:v>0.07337116097352676</x:v>
+      </x:c>
+      <x:c r="W79" s="76" t="str">
+        <x:f>IF(NOT(A79),"输入无效",IF(K79&gt;=L79,"KV 超载",IF(AK79&gt;C79+1e-9,"TPOT 不自洽",IF(OR(C79&gt;L79,MAX(P79,AG79)&gt;L79-K79),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X79" s="76" t="n">
+        <x:f>IF(W79="",U79*M79,"")</x:f>
+        <x:v>2.43612672</x:v>
+      </x:c>
+      <x:c r="Y79" s="103" t="n">
+        <x:f>IF(A79,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z79" s="103" t="n">
+        <x:f>IF(A79,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA79" s="103" t="n">
+        <x:f>IF(A79,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB79" s="103" t="n">
+        <x:f>IF(A79,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC79" s="103" t="n">
+        <x:f>IF(A79,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD79" s="103" t="n">
+        <x:f>IF(A79,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE79" s="103" t="n">
+        <x:f>IF(A79,SUM(Y79:AD79),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF79" s="103" t="n">
+        <x:f>IF(A79,AE79*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG79" s="103" t="n">
+        <x:f>IF(A79,AF79/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH79" s="103" t="n">
+        <x:f>IF(W79="",IF(OR(AG79=0,K79=0,$J$7=0),0,IF(AG79&lt;=(1-$J$7)*K79,$J$7*AG79*K79/(1-$J$7)-$J$7^2*AG79^2/(2*(1-$J$7)^2),$J$7*AG79*K79+$J$7^2*K79^2/2)/L79),"")</x:f>
+        <x:v>1.8409371994942692e-7</x:v>
+      </x:c>
+      <x:c r="AI79" s="103" t="n">
+        <x:f>IF(W79="",U79*E24*T79*M24*N24,"")</x:f>
         <x:v>0.039497916502832214</x:v>
       </x:c>
-      <x:c r="W79" s="76" t="str">
-        <x:f>IF(NOT(A79),"输入无效",IF(K79&gt;=L79,"KV 超载",IF(O79&gt;C79+1e-9,"TPOT 不自洽",IF(OR(C79&gt;L79,P79&gt;L79-K79),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X79" s="76" t="n">
-        <x:f>IF(W79="估算",U79*M79,"")</x:f>
-        <x:v>2.43612672</x:v>
+      <x:c r="AJ79" s="103" t="n">
+        <x:f>IF(W79="",U79*E24*AH79*Q24*R24,"")</x:f>
+        <x:v>0.03387324447069455</x:v>
+      </x:c>
+      <x:c r="AK79" s="103" t="n">
+        <x:f>IF(A79,O79+AF79,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL79" s="103" t="n">
+        <x:f>IF(A79,AK79/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="22" customHeight="1">
       <x:c r="A80" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D50),D50&gt;0),AND(ISNUMBER(E50),E50&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C50),C50&gt;=2,MOD(C50,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D50),D50&gt;0),AND(ISNUMBER(E50),E50&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C50),C50&gt;=2,MOD(C50,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B80" s="76" t="n">
@@ -16968,19 +18530,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q80" s="76" t="n">
-        <x:f>IF(A80,N80*1000/C80,"")</x:f>
-        <x:v>140.084352</x:v>
+        <x:f>IF(A80,IF(C80&gt;AF80,N80*1000/(C80-AF80),""),"")</x:f>
+        <x:v>143.68042396579565</x:v>
       </x:c>
       <x:c r="R80" s="76" t="n">
-        <x:f>IF(W80="估算",IF(OR(K80=0,O80=0),0,1-((E24-1)*MAX(0,(C80-O80)/E24-(K80))+MAX(0,L80-((E24-1)*C80/E24+P80)-(K80)))/L80),"")</x:f>
-        <x:v>0.001696434643231881</x:v>
+        <x:f>IF(W80="",IF(OR(K80=0,AK80=0),0,1-((E24-1)*MAX(0,(C80-AK80)/E24-(K80))+MAX(0,L80-((E24-1)*C80/E24+AL80)-(K80)))/L80),"")</x:f>
+        <x:v>0.0016964573137633332</x:v>
       </x:c>
       <x:c r="S80" s="76" t="n">
-        <x:f>IF(W80="估算",IF(O80=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C80-O80)/E24-(L80-K80))+MAX(0,L80-((E24-1)*C80/E24+P80)-(L80-K80)))/L80))),"")</x:f>
-        <x:v>0.001531526700768171</x:v>
+        <x:f>IF(W80="",IF(AK80=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C80-AK80)/E24-(L80-K80))+MAX(0,L80-((E24-1)*C80/E24+AL80)-(L80-K80)))/L80))),"")</x:f>
+        <x:v>0.0015315040302367189</x:v>
       </x:c>
       <x:c r="T80" s="76" t="n">
-        <x:f>IF(W80="估算",IF(OR(P80=0,K80=0,$J$7=0),0,IF(P80&lt;=(1-$J$7)*K80,$J$7*P80*K80/(1-$J$7)-$J$7^2*P80^2/(2*(1-$J$7)^2),$J$7*P80*K80+$J$7^2*K80^2/2)/L80),"")</x:f>
+        <x:f>IF(W80="",IF(OR(P80=0,K80=0,$J$7=0),0,IF(P80&lt;=(1-$J$7)*K80,$J$7*P80*K80/(1-$J$7)-$J$7^2*P80^2/(2*(1-$J$7)^2),$J$7*P80*K80+$J$7^2*K80^2/2)/L80),"")</x:f>
         <x:v>2.844369349439018e-7</x:v>
       </x:c>
       <x:c r="U80" s="76" t="n">
@@ -16988,21 +18550,76 @@
         <x:v>12000</x:v>
       </x:c>
       <x:c r="V80" s="76" t="n">
-        <x:f>IF(W80="估算",U80*E24*T80*M24*N24,"")</x:f>
+        <x:f>IF(W80="",SUM(AI80:AJ80),"")</x:f>
+        <x:v>0.5833190903861447</x:v>
+      </x:c>
+      <x:c r="W80" s="76" t="str">
+        <x:f>IF(NOT(A80),"输入无效",IF(K80&gt;=L80,"KV 超载",IF(AK80&gt;C80+1e-9,"TPOT 不自洽",IF(OR(C80&gt;L80,MAX(P80,AG80)&gt;L80-K80),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X80" s="76" t="n">
+        <x:f>IF(W80="",U80*M80,"")</x:f>
+        <x:v>19.367768064</x:v>
+      </x:c>
+      <x:c r="Y80" s="103" t="n">
+        <x:f>IF(A80,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z80" s="103" t="n">
+        <x:f>IF(A80,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA80" s="103" t="n">
+        <x:f>IF(A80,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB80" s="103" t="n">
+        <x:f>IF(A80,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC80" s="103" t="n">
+        <x:f>IF(A80,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD80" s="103" t="n">
+        <x:f>IF(A80,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE80" s="103" t="n">
+        <x:f>IF(A80,SUM(Y80:AD80),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF80" s="103" t="n">
+        <x:f>IF(A80,AE80*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG80" s="103" t="n">
+        <x:f>IF(A80,AF80/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH80" s="103" t="n">
+        <x:f>IF(W80="",IF(OR(AG80=0,K80=0,$J$7=0),0,IF(AG80&lt;=(1-$J$7)*K80,$J$7*AG80*K80/(1-$J$7)-$J$7^2*AG80^2/(2*(1-$J$7)^2),$J$7*AG80*K80+$J$7^2*K80^2/2)/L80),"")</x:f>
+        <x:v>2.439318063478959e-7</x:v>
+      </x:c>
+      <x:c r="AI80" s="103" t="n">
+        <x:f>IF(W80="",U80*E24*T80*M24*N24,"")</x:f>
         <x:v>0.3140183761780676</x:v>
       </x:c>
-      <x:c r="W80" s="76" t="str">
-        <x:f>IF(NOT(A80),"输入无效",IF(K80&gt;=L80,"KV 超载",IF(O80&gt;C80+1e-9,"TPOT 不自洽",IF(OR(C80&gt;L80,P80&gt;L80-K80),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X80" s="76" t="n">
-        <x:f>IF(W80="估算",U80*M80,"")</x:f>
-        <x:v>19.367768064</x:v>
+      <x:c r="AJ80" s="103" t="n">
+        <x:f>IF(W80="",U80*E24*AH80*Q24*R24,"")</x:f>
+        <x:v>0.26930071420807705</x:v>
+      </x:c>
+      <x:c r="AK80" s="103" t="n">
+        <x:f>IF(A80,O80+AF80,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL80" s="103" t="n">
+        <x:f>IF(A80,AK80/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="22" customHeight="1">
       <x:c r="A81" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D51),D51&gt;0),AND(ISNUMBER(E51),E51&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C51),C51&gt;=2,MOD(C51,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D51),D51&gt;0),AND(ISNUMBER(E51),E51&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C51),C51&gt;=2,MOD(C51,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B81" s="76" t="n">
@@ -17066,19 +18683,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q81" s="76" t="n">
-        <x:f>IF(A81,N81*1000/C81,"")</x:f>
-        <x:v>70.042176</x:v>
+        <x:f>IF(A81,IF(C81&gt;AF81,N81*1000/(C81-AF81),""),"")</x:f>
+        <x:v>70.92980098685632</x:v>
       </x:c>
       <x:c r="R81" s="76" t="n">
-        <x:f>IF(W81="估算",IF(OR(K81=0,O81=0),0,1-((E24-1)*MAX(0,(C81-O81)/E24-(K81))+MAX(0,L81-((E24-1)*C81/E24+P81)-(K81)))/L81),"")</x:f>
-        <x:v>0.0017788621794637693</x:v>
+        <x:f>IF(W81="",IF(OR(K81=0,AK81=0),0,1-((E24-1)*MAX(0,(C81-AK81)/E24-(K81))+MAX(0,L81-((E24-1)*C81/E24+AL81)-(K81)))/L81),"")</x:f>
+        <x:v>0.0017788848499952215</x:v>
       </x:c>
       <x:c r="S81" s="76" t="n">
-        <x:f>IF(W81="估算",IF(O81=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C81-O81)/E24-(L81-K81))+MAX(0,L81-((E24-1)*C81/E24+P81)-(L81-K81)))/L81))),"")</x:f>
-        <x:v>0.0014490991645362827</x:v>
+        <x:f>IF(W81="",IF(AK81=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C81-AK81)/E24-(L81-K81))+MAX(0,L81-((E24-1)*C81/E24+AL81)-(L81-K81)))/L81))),"")</x:f>
+        <x:v>0.0014490764940048306</x:v>
       </x:c>
       <x:c r="T81" s="76" t="n">
-        <x:f>IF(W81="估算",IF(OR(P81=0,K81=0,$J$7=0),0,IF(P81&lt;=(1-$J$7)*K81,$J$7*P81*K81/(1-$J$7)-$J$7^2*P81^2/(2*(1-$J$7)^2),$J$7*P81*K81+$J$7^2*K81^2/2)/L81),"")</x:f>
+        <x:f>IF(W81="",IF(OR(P81=0,K81=0,$J$7=0),0,IF(P81&lt;=(1-$J$7)*K81,$J$7*P81*K81/(1-$J$7)-$J$7^2*P81^2/(2*(1-$J$7)^2),$J$7*P81*K81+$J$7^2*K81^2/2)/L81),"")</x:f>
         <x:v>2.844369349439018e-7</x:v>
       </x:c>
       <x:c r="U81" s="76" t="n">
@@ -17086,21 +18703,76 @@
         <x:v>6000</x:v>
       </x:c>
       <x:c r="V81" s="76" t="n">
-        <x:f>IF(W81="估算",U81*E24*T81*M24*N24,"")</x:f>
+        <x:f>IF(W81="",SUM(AI81:AJ81),"")</x:f>
+        <x:v>0.29165954519307236</x:v>
+      </x:c>
+      <x:c r="W81" s="76" t="str">
+        <x:f>IF(NOT(A81),"输入无效",IF(K81&gt;=L81,"KV 超载",IF(AK81&gt;C81+1e-9,"TPOT 不自洽",IF(OR(C81&gt;L81,MAX(P81,AG81)&gt;L81-K81),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X81" s="76" t="n">
+        <x:f>IF(W81="",U81*M81,"")</x:f>
+        <x:v>9.683884032</x:v>
+      </x:c>
+      <x:c r="Y81" s="103" t="n">
+        <x:f>IF(A81,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z81" s="103" t="n">
+        <x:f>IF(A81,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA81" s="103" t="n">
+        <x:f>IF(A81,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB81" s="103" t="n">
+        <x:f>IF(A81,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC81" s="103" t="n">
+        <x:f>IF(A81,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD81" s="103" t="n">
+        <x:f>IF(A81,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE81" s="103" t="n">
+        <x:f>IF(A81,SUM(Y81:AD81),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF81" s="103" t="n">
+        <x:f>IF(A81,AE81*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG81" s="103" t="n">
+        <x:f>IF(A81,AF81/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH81" s="103" t="n">
+        <x:f>IF(W81="",IF(OR(AG81=0,K81=0,$J$7=0),0,IF(AG81&lt;=(1-$J$7)*K81,$J$7*AG81*K81/(1-$J$7)-$J$7^2*AG81^2/(2*(1-$J$7)^2),$J$7*AG81*K81+$J$7^2*K81^2/2)/L81),"")</x:f>
+        <x:v>2.439318063478959e-7</x:v>
+      </x:c>
+      <x:c r="AI81" s="103" t="n">
+        <x:f>IF(W81="",U81*E24*T81*M24*N24,"")</x:f>
         <x:v>0.1570091880890338</x:v>
       </x:c>
-      <x:c r="W81" s="76" t="str">
-        <x:f>IF(NOT(A81),"输入无效",IF(K81&gt;=L81,"KV 超载",IF(O81&gt;C81+1e-9,"TPOT 不自洽",IF(OR(C81&gt;L81,P81&gt;L81-K81),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X81" s="76" t="n">
-        <x:f>IF(W81="估算",U81*M81,"")</x:f>
-        <x:v>9.683884032</x:v>
+      <x:c r="AJ81" s="103" t="n">
+        <x:f>IF(W81="",U81*E24*AH81*Q24*R24,"")</x:f>
+        <x:v>0.13465035710403853</x:v>
+      </x:c>
+      <x:c r="AK81" s="103" t="n">
+        <x:f>IF(A81,O81+AF81,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL81" s="103" t="n">
+        <x:f>IF(A81,AK81/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="22" customHeight="1">
       <x:c r="A82" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D52),D52&gt;0),AND(ISNUMBER(E52),E52&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C52),C52&gt;=2,MOD(C52,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D52),D52&gt;0),AND(ISNUMBER(E52),E52&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C52),C52&gt;=2,MOD(C52,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B82" s="76" t="n">
@@ -17164,19 +18836,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q82" s="76" t="n">
-        <x:f>IF(A82,N82*1000/C82,"")</x:f>
-        <x:v>35.021088</x:v>
+        <x:f>IF(A82,IF(C82&gt;AF82,N82*1000/(C82-AF82),""),"")</x:f>
+        <x:v>35.24159702200649</x:v>
       </x:c>
       <x:c r="R82" s="76" t="n">
-        <x:f>IF(W82="估算",IF(OR(K82=0,O82=0),0,1-((E24-1)*MAX(0,(C82-O82)/E24-(K82))+MAX(0,L82-((E24-1)*C82/E24+P82)-(K82)))/L82),"")</x:f>
-        <x:v>0.0019437172519275459</x:v>
+        <x:f>IF(W82="",IF(OR(K82=0,AK82=0),0,1-((E24-1)*MAX(0,(C82-AK82)/E24-(K82))+MAX(0,L82-((E24-1)*C82/E24+AL82)-(K82)))/L82),"")</x:f>
+        <x:v>0.001943739922458887</x:v>
       </x:c>
       <x:c r="S82" s="76" t="n">
-        <x:f>IF(W82="估算",IF(O82=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C82-O82)/E24-(L82-K82))+MAX(0,L82-((E24-1)*C82/E24+P82)-(L82-K82)))/L82))),"")</x:f>
-        <x:v>0.0012842440920723952</x:v>
+        <x:f>IF(W82="",IF(AK82=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C82-AK82)/E24-(L82-K82))+MAX(0,L82-((E24-1)*C82/E24+AL82)-(L82-K82)))/L82))),"")</x:f>
+        <x:v>0.0012842214215410541</x:v>
       </x:c>
       <x:c r="T82" s="76" t="n">
-        <x:f>IF(W82="估算",IF(OR(P82=0,K82=0,$J$7=0),0,IF(P82&lt;=(1-$J$7)*K82,$J$7*P82*K82/(1-$J$7)-$J$7^2*P82^2/(2*(1-$J$7)^2),$J$7*P82*K82+$J$7^2*K82^2/2)/L82),"")</x:f>
+        <x:f>IF(W82="",IF(OR(P82=0,K82=0,$J$7=0),0,IF(P82&lt;=(1-$J$7)*K82,$J$7*P82*K82/(1-$J$7)-$J$7^2*P82^2/(2*(1-$J$7)^2),$J$7*P82*K82+$J$7^2*K82^2/2)/L82),"")</x:f>
         <x:v>2.844369349439018e-7</x:v>
       </x:c>
       <x:c r="U82" s="76" t="n">
@@ -17184,21 +18856,76 @@
         <x:v>3000</x:v>
       </x:c>
       <x:c r="V82" s="76" t="n">
-        <x:f>IF(W82="估算",U82*E24*T82*M24*N24,"")</x:f>
+        <x:f>IF(W82="",SUM(AI82:AJ82),"")</x:f>
+        <x:v>0.14582977259653618</x:v>
+      </x:c>
+      <x:c r="W82" s="76" t="str">
+        <x:f>IF(NOT(A82),"输入无效",IF(K82&gt;=L82,"KV 超载",IF(AK82&gt;C82+1e-9,"TPOT 不自洽",IF(OR(C82&gt;L82,MAX(P82,AG82)&gt;L82-K82),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X82" s="76" t="n">
+        <x:f>IF(W82="",U82*M82,"")</x:f>
+        <x:v>4.841942016</x:v>
+      </x:c>
+      <x:c r="Y82" s="103" t="n">
+        <x:f>IF(A82,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z82" s="103" t="n">
+        <x:f>IF(A82,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA82" s="103" t="n">
+        <x:f>IF(A82,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB82" s="103" t="n">
+        <x:f>IF(A82,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC82" s="103" t="n">
+        <x:f>IF(A82,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD82" s="103" t="n">
+        <x:f>IF(A82,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE82" s="103" t="n">
+        <x:f>IF(A82,SUM(Y82:AD82),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF82" s="103" t="n">
+        <x:f>IF(A82,AE82*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG82" s="103" t="n">
+        <x:f>IF(A82,AF82/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH82" s="103" t="n">
+        <x:f>IF(W82="",IF(OR(AG82=0,K82=0,$J$7=0),0,IF(AG82&lt;=(1-$J$7)*K82,$J$7*AG82*K82/(1-$J$7)-$J$7^2*AG82^2/(2*(1-$J$7)^2),$J$7*AG82*K82+$J$7^2*K82^2/2)/L82),"")</x:f>
+        <x:v>2.439318063478959e-7</x:v>
+      </x:c>
+      <x:c r="AI82" s="103" t="n">
+        <x:f>IF(W82="",U82*E24*T82*M24*N24,"")</x:f>
         <x:v>0.0785045940445169</x:v>
       </x:c>
-      <x:c r="W82" s="76" t="str">
-        <x:f>IF(NOT(A82),"输入无效",IF(K82&gt;=L82,"KV 超载",IF(O82&gt;C82+1e-9,"TPOT 不自洽",IF(OR(C82&gt;L82,P82&gt;L82-K82),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X82" s="76" t="n">
-        <x:f>IF(W82="估算",U82*M82,"")</x:f>
-        <x:v>4.841942016</x:v>
+      <x:c r="AJ82" s="103" t="n">
+        <x:f>IF(W82="",U82*E24*AH82*Q24*R24,"")</x:f>
+        <x:v>0.06732517855201926</x:v>
+      </x:c>
+      <x:c r="AK82" s="103" t="n">
+        <x:f>IF(A82,O82+AF82,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL82" s="103" t="n">
+        <x:f>IF(A82,AK82/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="22" customHeight="1">
       <x:c r="A83" s="30" t="b">
-        <x:f>AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D53),D53&gt;0),AND(ISNUMBER(E53),E53&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C53),C53&gt;=2,MOD(C53,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1))</x:f>
+        <x:f>AND(AND(AND(ISNUMBER($B$5),$B$5&gt;0),AND(ISNUMBER($F$5),$F$5&gt;0),AND(ISNUMBER($J$5),$J$5&gt;0),AND(ISNUMBER($B$9),$B$9&gt;0),AND(ISNUMBER(I24),I24&gt;0),AND(ISNUMBER(J24),J24&gt;0),AND(ISNUMBER(K24),K24&gt;0),AND(ISNUMBER(L24),L24&gt;0),AND(ISNUMBER(D53),D53&gt;0),AND(ISNUMBER(E53),E53&gt;0),MOD($B$5,1)=0,MOD($F$5,1)=0,MOD($J$5,1)=0,MOD($B$9,1)=0,MOD(K24,1)=0,ISNUMBER(C53),C53&gt;=2,MOD(C53,1)=0,OR($N$9=32,$N$9=64,$N$9=128),ISNUMBER($B$11),$B$11&gt;=0,MOD($B$11,1)=0,ISNUMBER($J$7),$J$7&gt;=0,$J$7&lt;1,AND(ISNUMBER(M24),M24&gt;=0,M24&lt;=1),AND(ISNUMBER(N24),N24&gt;=0,N24&lt;=1)),ISNUMBER(P24),P24&gt;0,ISNUMBER(Q24),Q24&gt;=0,Q24&lt;=1,ISNUMBER(R24),R24&gt;=0,R24&lt;=1)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="B83" s="76" t="n">
@@ -17262,19 +18989,19 @@
         <x:v>0.0015861</x:v>
       </x:c>
       <x:c r="Q83" s="76" t="n">
-        <x:f>IF(A83,N83*1000/C83,"")</x:f>
-        <x:v>23.347392</x:v>
+        <x:f>IF(A83,IF(C83&gt;AF83,N83*1000/(C83-AF83),""),"")</x:f>
+        <x:v>23.445190747680634</x:v>
       </x:c>
       <x:c r="R83" s="76" t="n">
-        <x:f>IF(W83="估算",IF(OR(K83=0,O83=0),0,1-((E24-1)*MAX(0,(C83-O83)/E24-(K83))+MAX(0,L83-((E24-1)*C83/E24+P83)-(K83)))/L83),"")</x:f>
-        <x:v>0.0021085723243913224</x:v>
+        <x:f>IF(W83="",IF(OR(K83=0,AK83=0),0,1-((E24-1)*MAX(0,(C83-AK83)/E24-(K83))+MAX(0,L83-((E24-1)*C83/E24+AL83)-(K83)))/L83),"")</x:f>
+        <x:v>0.0021085949949227745</x:v>
       </x:c>
       <x:c r="S83" s="76" t="n">
-        <x:f>IF(W83="估算",IF(O83=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C83-O83)/E24-(L83-K83))+MAX(0,L83-((E24-1)*C83/E24+P83)-(L83-K83)))/L83))),"")</x:f>
-        <x:v>0.0011193890196087297</x:v>
+        <x:f>IF(W83="",IF(AK83=0,0,MAX(0,1-(1-((E24-1)*MAX(0,(C83-AK83)/E24-(L83-K83))+MAX(0,L83-((E24-1)*C83/E24+AL83)-(L83-K83)))/L83))),"")</x:f>
+        <x:v>0.0011193663490772776</x:v>
       </x:c>
       <x:c r="T83" s="76" t="n">
-        <x:f>IF(W83="估算",IF(OR(P83=0,K83=0,$J$7=0),0,IF(P83&lt;=(1-$J$7)*K83,$J$7*P83*K83/(1-$J$7)-$J$7^2*P83^2/(2*(1-$J$7)^2),$J$7*P83*K83+$J$7^2*K83^2/2)/L83),"")</x:f>
+        <x:f>IF(W83="",IF(OR(P83=0,K83=0,$J$7=0),0,IF(P83&lt;=(1-$J$7)*K83,$J$7*P83*K83/(1-$J$7)-$J$7^2*P83^2/(2*(1-$J$7)^2),$J$7*P83*K83+$J$7^2*K83^2/2)/L83),"")</x:f>
         <x:v>2.844369349439018e-7</x:v>
       </x:c>
       <x:c r="U83" s="76" t="n">
@@ -17282,16 +19009,71 @@
         <x:v>2000</x:v>
       </x:c>
       <x:c r="V83" s="76" t="n">
-        <x:f>IF(W83="估算",U83*E24*T83*M24*N24,"")</x:f>
+        <x:f>IF(W83="",SUM(AI83:AJ83),"")</x:f>
+        <x:v>0.09721984839769078</x:v>
+      </x:c>
+      <x:c r="W83" s="76" t="str">
+        <x:f>IF(NOT(A83),"输入无效",IF(K83&gt;=L83,"KV 超载",IF(AK83&gt;C83+1e-9,"TPOT 不自洽",IF(OR(C83&gt;L83,MAX(P83,AG83)&gt;L83-K83),"需时序仿真",""))))</x:f>
+      </x:c>
+      <x:c r="X83" s="76" t="n">
+        <x:f>IF(W83="",U83*M83,"")</x:f>
+        <x:v>3.227961344</x:v>
+      </x:c>
+      <x:c r="Y83" s="103" t="n">
+        <x:f>IF(A83,K24*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.003211264</x:v>
+      </x:c>
+      <x:c r="Z83" s="103" t="n">
+        <x:f>IF(A83,S24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.298647552</x:v>
+      </x:c>
+      <x:c r="AA83" s="103" t="n">
+        <x:f>IF(A83,T24*ROUNDUP(K24/D24,0)*F24*2*2*(D24-1)/D24/1e9,"")</x:f>
+        <x:v>0.000401408</x:v>
+      </x:c>
+      <x:c r="AB83" s="103" t="n">
+        <x:f>IF(A83,U24*2*ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.295436288</x:v>
+      </x:c>
+      <x:c r="AC83" s="103" t="n">
+        <x:f>IF(A83,ROUNDUP(K24/D24,0)*F24*2*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001605632</x:v>
+      </x:c>
+      <x:c r="AD83" s="103" t="n">
+        <x:f>IF(A83,K24*256*(2+4)*(D24-1)/1e9,"")</x:f>
+        <x:v>0.001376256</x:v>
+      </x:c>
+      <x:c r="AE83" s="103" t="n">
+        <x:f>IF(A83,SUM(Y83:AD83),"")</x:f>
+        <x:v>0.6006784</x:v>
+      </x:c>
+      <x:c r="AF83" s="103" t="n">
+        <x:f>IF(A83,AE83*1000/P24,"")</x:f>
+        <x:v>0.1251413333333333</x:v>
+      </x:c>
+      <x:c r="AG83" s="103" t="n">
+        <x:f>IF(A83,AF83/E24,"")</x:f>
+        <x:v>0.0013602318840579706</x:v>
+      </x:c>
+      <x:c r="AH83" s="103" t="n">
+        <x:f>IF(W83="",IF(OR(AG83=0,K83=0,$J$7=0),0,IF(AG83&lt;=(1-$J$7)*K83,$J$7*AG83*K83/(1-$J$7)-$J$7^2*AG83^2/(2*(1-$J$7)^2),$J$7*AG83*K83+$J$7^2*K83^2/2)/L83),"")</x:f>
+        <x:v>2.439318063478959e-7</x:v>
+      </x:c>
+      <x:c r="AI83" s="103" t="n">
+        <x:f>IF(W83="",U83*E24*T83*M24*N24,"")</x:f>
         <x:v>0.052336396029677934</x:v>
       </x:c>
-      <x:c r="W83" s="76" t="str">
-        <x:f>IF(NOT(A83),"输入无效",IF(K83&gt;=L83,"KV 超载",IF(O83&gt;C83+1e-9,"TPOT 不自洽",IF(OR(C83&gt;L83,P83&gt;L83-K83),"需时序仿真","估算"))))</x:f>
-        <x:v>估算</x:v>
-      </x:c>
-      <x:c r="X83" s="76" t="n">
-        <x:f>IF(W83="估算",U83*M83,"")</x:f>
-        <x:v>3.227961344</x:v>
+      <x:c r="AJ83" s="103" t="n">
+        <x:f>IF(W83="",U83*E24*AH83*Q24*R24,"")</x:f>
+        <x:v>0.04488345236801285</x:v>
+      </x:c>
+      <x:c r="AK83" s="103" t="n">
+        <x:f>IF(A83,O83+AF83,"")</x:f>
+        <x:v>0.2710625333333333</x:v>
+      </x:c>
+      <x:c r="AL83" s="103" t="n">
+        <x:f>IF(A83,AK83/E24,"")</x:f>
+        <x:v>0.0029463318840579704</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="22" customHeight="1">
@@ -18243,7 +20025,7 @@
     </x:row>
     <x:row r="106" ht="22" customHeight="1">
       <x:c r="A106" s="30" t="str">
-        <x:v>MC2：A3 FullMesh BF16；均衡路由。未计 TP / Attention / Engram、通信启动和真实排队，未复现 NPU 实测。</x:v>
+        <x:v>MC2：A3 FullMesh BF16；TP/SP：HCCL Ring，K3 共享专家 TP、Qwen 共享专家 DP。通信启动、Engram 与排队另计。</x:v>
       </x:c>
       <x:c r="B106" s="30"/>
       <x:c r="C106" s="30"/>

--- a/models/kimi-k3/kimi-k3-analysis.xlsx
+++ b/models/kimi-k3/kimi-k3-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rf5363412741648ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R3801da1042f745aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="Rea38094374774576"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rf46c58a971934790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rc0fd1ca1a3514e6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R567046d9bf0a4ab5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -166,7 +166,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="104">
+  <x:cellXfs count="105">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -415,6 +415,9 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="203" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -12160,7 +12163,7 @@
       <x:c r="W4" s="30"/>
       <x:c r="X4" s="30"/>
     </x:row>
-    <x:row r="5" ht="22" customHeight="1">
+    <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="30" t="str">
         <x:v>每 P DP 请求数</x:v>
       </x:c>
@@ -12169,16 +12172,18 @@
       </x:c>
       <x:c r="C5" s="30"/>
       <x:c r="D5" s="30"/>
-      <x:c r="E5" s="30" t="str">
-        <x:v>P EP 组数</x:v>
+      <x:c r="E5" s="79" t="str">
+        <x:v>P deployment
+count</x:v>
       </x:c>
       <x:c r="F5" s="66" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="30"/>
       <x:c r="H5" s="30"/>
-      <x:c r="I5" s="30" t="str">
-        <x:v>D EP 组数</x:v>
+      <x:c r="I5" s="79" t="str">
+        <x:v>D deployment
+count</x:v>
       </x:c>
       <x:c r="J5" s="66" t="n">
         <x:v>1</x:v>
@@ -12296,25 +12301,28 @@
       <x:c r="W8" s="30"/>
       <x:c r="X8" s="30"/>
     </x:row>
-    <x:row r="9" ht="22" customHeight="1">
-      <x:c r="A9" s="30" t="str">
-        <x:v>每周期错峰批数</x:v>
+    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="A9" s="79" t="str">
+        <x:v>KV bursts
+per interval</x:v>
       </x:c>
       <x:c r="B9" s="66" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="30"/>
       <x:c r="D9" s="30"/>
-      <x:c r="E9" s="30" t="str">
-        <x:v>EP 共享比例</x:v>
+      <x:c r="E9" s="79" t="str">
+        <x:v>EP shared
+resource fraction</x:v>
       </x:c>
       <x:c r="F9" s="68" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G9" s="30"/>
       <x:c r="H9" s="30"/>
-      <x:c r="I9" s="30" t="str">
-        <x:v>EP 暴露率</x:v>
+      <x:c r="I9" s="79" t="str">
+        <x:v>EP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="J9" s="68" t="n">
         <x:v>1</x:v>
@@ -12364,7 +12372,7 @@
       <x:c r="W10" s="30"/>
       <x:c r="X10" s="30"/>
     </x:row>
-    <x:row r="11" ht="22" customHeight="1">
+    <x:row r="11" ht="34" customHeight="1">
       <x:c r="A11" s="30" t="str">
         <x:v>Conv 额外 slots</x:v>
       </x:c>
@@ -12381,16 +12389,18 @@
       </x:c>
       <x:c r="G11" s="30"/>
       <x:c r="H11" s="30"/>
-      <x:c r="I11" s="30" t="str">
-        <x:v>TP 共享比例</x:v>
+      <x:c r="I11" s="79" t="str">
+        <x:v>TP shared
+resource fraction</x:v>
       </x:c>
       <x:c r="J11" s="85" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K11" s="30"/>
       <x:c r="L11" s="30"/>
-      <x:c r="M11" s="30" t="str">
-        <x:v>TP 暴露率</x:v>
+      <x:c r="M11" s="79" t="str">
+        <x:v>TP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="N11" s="85" t="n">
         <x:v>1</x:v>
@@ -12408,7 +12418,7 @@
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="30" t="str">
-        <x:v>TTFT 作为批次周期；EP 与 TP 带宽分别填写。TP 不与 KV 共用链路时，将 TP 共享比例设为 0。</x:v>
+        <x:v>P = Prefill，D = Decode。通常只需修改带宽、请求数和 TTFT/TPOT；附加假设可保持默认。</x:v>
       </x:c>
       <x:c r="B12" s="30"/>
       <x:c r="C12" s="30"/>
@@ -12435,7 +12445,9 @@
       <x:c r="X12" s="30"/>
     </x:row>
     <x:row r="13" ht="22" customHeight="1">
-      <x:c r="A13" s="30"/>
+      <x:c r="A13" s="30" t="str">
+        <x:v>Total overhead 表示基线 60 秒工作量的额外耗时；TTFT 在这里作为 KV 批次到达间隔。</x:v>
+      </x:c>
       <x:c r="B13" s="30"/>
       <x:c r="C13" s="30"/>
       <x:c r="D13" s="30"/>
@@ -12514,22 +12526,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G15" s="30"/>
-      <x:c r="H15" s="30" t="str">
-        <x:v>黄色为输入；模型 / EP 带宽可在下表逐项覆盖。</x:v>
-      </x:c>
-      <x:c r="I15" s="30"/>
-      <x:c r="J15" s="30"/>
-      <x:c r="K15" s="30"/>
-      <x:c r="L15" s="30"/>
-      <x:c r="M15" s="30"/>
-      <x:c r="N15" s="30"/>
-      <x:c r="O15" s="30"/>
-      <x:c r="P15" s="30"/>
-      <x:c r="Q15" s="30"/>
-      <x:c r="R15" s="30"/>
-      <x:c r="S15" s="30"/>
-      <x:c r="T15" s="30"/>
-      <x:c r="U15" s="30"/>
+      <x:c r="H15" s="104" t="str">
+        <x:v>Default: P = D = 1; KV bursts = 1; shared / exposed fractions = 100%.</x:v>
+      </x:c>
+      <x:c r="I15" s="104"/>
+      <x:c r="J15" s="104"/>
+      <x:c r="K15" s="104"/>
+      <x:c r="L15" s="104"/>
+      <x:c r="M15" s="104"/>
+      <x:c r="N15" s="104"/>
+      <x:c r="O15" s="104"/>
+      <x:c r="P15" s="104"/>
+      <x:c r="Q15" s="104"/>
+      <x:c r="R15" s="104"/>
+      <x:c r="S15" s="104"/>
+      <x:c r="T15" s="104"/>
+      <x:c r="U15" s="104"/>
       <x:c r="V15" s="30"/>
       <x:c r="W15" s="30"/>
       <x:c r="X15" s="30"/>
@@ -12552,22 +12564,22 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="G16" s="30"/>
-      <x:c r="H16" s="30" t="str">
-        <x:v>时间增量针对基线 60 秒工作量；不表示实测吞吐或 P99。</x:v>
-      </x:c>
-      <x:c r="I16" s="30"/>
-      <x:c r="J16" s="30"/>
-      <x:c r="K16" s="30"/>
-      <x:c r="L16" s="30"/>
-      <x:c r="M16" s="30"/>
-      <x:c r="N16" s="30"/>
-      <x:c r="O16" s="30"/>
-      <x:c r="P16" s="30"/>
-      <x:c r="Q16" s="30"/>
-      <x:c r="R16" s="30"/>
-      <x:c r="S16" s="30"/>
-      <x:c r="T16" s="30"/>
-      <x:c r="U16" s="30"/>
+      <x:c r="H16" s="104" t="str">
+        <x:v>Deployment count：完整 EP 部署的套数；EP32 每套 32 卡，EP256 每套 256 卡。</x:v>
+      </x:c>
+      <x:c r="I16" s="104"/>
+      <x:c r="J16" s="104"/>
+      <x:c r="K16" s="104"/>
+      <x:c r="L16" s="104"/>
+      <x:c r="M16" s="104"/>
+      <x:c r="N16" s="104"/>
+      <x:c r="O16" s="104"/>
+      <x:c r="P16" s="104"/>
+      <x:c r="Q16" s="104"/>
+      <x:c r="R16" s="104"/>
+      <x:c r="S16" s="104"/>
+      <x:c r="T16" s="104"/>
+      <x:c r="U16" s="104"/>
       <x:c r="V16" s="30"/>
       <x:c r="W16" s="30"/>
       <x:c r="X16" s="30"/>
@@ -12590,22 +12602,22 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="G17" s="30"/>
-      <x:c r="H17" s="30" t="str">
-        <x:v>TTFT 只用于到达节奏，本页估算 D 侧 TPOT；P 耗时仍见原表。</x:v>
-      </x:c>
-      <x:c r="I17" s="30"/>
-      <x:c r="J17" s="30"/>
-      <x:c r="K17" s="30"/>
-      <x:c r="L17" s="30"/>
-      <x:c r="M17" s="30"/>
-      <x:c r="N17" s="30"/>
-      <x:c r="O17" s="30"/>
-      <x:c r="P17" s="30"/>
-      <x:c r="Q17" s="30"/>
-      <x:c r="R17" s="30"/>
-      <x:c r="S17" s="30"/>
-      <x:c r="T17" s="30"/>
-      <x:c r="U17" s="30"/>
+      <x:c r="H17" s="104" t="str">
+        <x:v>Shared resource fraction：通信中与 KV 竞争同一资源的比例。100% = 全部；0% = 资源独立。</x:v>
+      </x:c>
+      <x:c r="I17" s="104"/>
+      <x:c r="J17" s="104"/>
+      <x:c r="K17" s="104"/>
+      <x:c r="L17" s="104"/>
+      <x:c r="M17" s="104"/>
+      <x:c r="N17" s="104"/>
+      <x:c r="O17" s="104"/>
+      <x:c r="P17" s="104"/>
+      <x:c r="Q17" s="104"/>
+      <x:c r="R17" s="104"/>
+      <x:c r="S17" s="104"/>
+      <x:c r="T17" s="104"/>
+      <x:c r="U17" s="104"/>
       <x:c r="V17" s="30"/>
       <x:c r="W17" s="30"/>
       <x:c r="X17" s="30"/>
@@ -12622,22 +12634,22 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="G18" s="30"/>
-      <x:c r="H18" s="30" t="str">
-        <x:v>全通信＝该步所有等效 EP＋TP 段都在 KV 窗口内；TP 首尾通信均摊到层段。</x:v>
-      </x:c>
-      <x:c r="I18" s="30"/>
-      <x:c r="J18" s="30"/>
-      <x:c r="K18" s="30"/>
-      <x:c r="L18" s="30"/>
-      <x:c r="M18" s="30"/>
-      <x:c r="N18" s="30"/>
-      <x:c r="O18" s="30"/>
-      <x:c r="P18" s="30"/>
-      <x:c r="Q18" s="30"/>
-      <x:c r="R18" s="30"/>
-      <x:c r="S18" s="30"/>
-      <x:c r="T18" s="30"/>
-      <x:c r="U18" s="30"/>
+      <x:c r="H18" s="104" t="str">
+        <x:v>Exposed communication fraction：通信增时最终计入 forward 的比例；被计算遮住的部分不计入。</x:v>
+      </x:c>
+      <x:c r="I18" s="104"/>
+      <x:c r="J18" s="104"/>
+      <x:c r="K18" s="104"/>
+      <x:c r="L18" s="104"/>
+      <x:c r="M18" s="104"/>
+      <x:c r="N18" s="104"/>
+      <x:c r="O18" s="104"/>
+      <x:c r="P18" s="104"/>
+      <x:c r="Q18" s="104"/>
+      <x:c r="R18" s="104"/>
+      <x:c r="S18" s="104"/>
+      <x:c r="T18" s="104"/>
+      <x:c r="U18" s="104"/>
       <x:c r="V18" s="30"/>
       <x:c r="W18" s="30"/>
       <x:c r="X18" s="30"/>
@@ -12650,20 +12662,22 @@
       <x:c r="E19" s="30"/>
       <x:c r="F19" s="30"/>
       <x:c r="G19" s="30"/>
-      <x:c r="H19" s="30"/>
-      <x:c r="I19" s="30"/>
-      <x:c r="J19" s="30"/>
-      <x:c r="K19" s="30"/>
-      <x:c r="L19" s="30"/>
-      <x:c r="M19" s="30"/>
-      <x:c r="N19" s="30"/>
-      <x:c r="O19" s="30"/>
-      <x:c r="P19" s="30"/>
-      <x:c r="Q19" s="30"/>
-      <x:c r="R19" s="30"/>
-      <x:c r="S19" s="30"/>
-      <x:c r="T19" s="30"/>
-      <x:c r="U19" s="30"/>
+      <x:c r="H19" s="104" t="str">
+        <x:v>KV bursts per interval：一批 KV 均分成 m 次、等间隔发送；m = 2 时每次一半，总量不变。</x:v>
+      </x:c>
+      <x:c r="I19" s="104"/>
+      <x:c r="J19" s="104"/>
+      <x:c r="K19" s="104"/>
+      <x:c r="L19" s="104"/>
+      <x:c r="M19" s="104"/>
+      <x:c r="N19" s="104"/>
+      <x:c r="O19" s="104"/>
+      <x:c r="P19" s="104"/>
+      <x:c r="Q19" s="104"/>
+      <x:c r="R19" s="104"/>
+      <x:c r="S19" s="104"/>
+      <x:c r="T19" s="104"/>
+      <x:c r="U19" s="104"/>
       <x:c r="V19" s="30"/>
       <x:c r="W19" s="30"/>
       <x:c r="X19" s="30"/>
@@ -12676,20 +12690,22 @@
       <x:c r="E20" s="30"/>
       <x:c r="F20" s="30"/>
       <x:c r="G20" s="30"/>
-      <x:c r="H20" s="30"/>
-      <x:c r="I20" s="30"/>
-      <x:c r="J20" s="30"/>
-      <x:c r="K20" s="30"/>
-      <x:c r="L20" s="30"/>
-      <x:c r="M20" s="30"/>
-      <x:c r="N20" s="30"/>
-      <x:c r="O20" s="30"/>
-      <x:c r="P20" s="30"/>
-      <x:c r="Q20" s="30"/>
-      <x:c r="R20" s="30"/>
-      <x:c r="S20" s="30"/>
-      <x:c r="T20" s="30"/>
-      <x:c r="U20" s="30"/>
+      <x:c r="H20" s="104" t="str">
+        <x:v>Temporal overlap 由 KV 窗口自动计算；没有 profiling 时，不必另猜 shared / exposed 两个比例。</x:v>
+      </x:c>
+      <x:c r="I20" s="104"/>
+      <x:c r="J20" s="104"/>
+      <x:c r="K20" s="104"/>
+      <x:c r="L20" s="104"/>
+      <x:c r="M20" s="104"/>
+      <x:c r="N20" s="104"/>
+      <x:c r="O20" s="104"/>
+      <x:c r="P20" s="104"/>
+      <x:c r="Q20" s="104"/>
+      <x:c r="R20" s="104"/>
+      <x:c r="S20" s="104"/>
+      <x:c r="T20" s="104"/>
+      <x:c r="U20" s="104"/>
       <x:c r="V20" s="30"/>
       <x:c r="W20" s="30"/>
       <x:c r="X20" s="30"/>
@@ -12757,11 +12773,13 @@
       <x:c r="L22" s="73" t="str">
         <x:v>产出 tokens/步</x:v>
       </x:c>
-      <x:c r="M22" s="73" t="str">
-        <x:v>共享比例</x:v>
-      </x:c>
-      <x:c r="N22" s="73" t="str">
-        <x:v>暴露率</x:v>
+      <x:c r="M22" s="18" t="str">
+        <x:v>EP shared
+resource fraction</x:v>
+      </x:c>
+      <x:c r="N22" s="18" t="str">
+        <x:v>EP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="O22" s="73" t="str">
         <x:v>配置条件</x:v>
@@ -12770,10 +12788,12 @@
         <x:v>TP GB/s 输入</x:v>
       </x:c>
       <x:c r="Q22" s="90" t="str">
-        <x:v>TP 共享比例</x:v>
+        <x:v>TP shared
+resource fraction</x:v>
       </x:c>
       <x:c r="R22" s="90" t="str">
-        <x:v>TP 暴露率</x:v>
+        <x:v>TP exposed
+comm fraction</x:v>
       </x:c>
       <x:c r="S22" s="90" t="str">
         <x:v>Attention 层数</x:v>
@@ -13082,8 +13102,9 @@
       <x:c r="K29" s="73" t="str">
         <x:v>重叠层段 次/min</x:v>
       </x:c>
-      <x:c r="L29" s="73" t="str">
-        <x:v>60s 工作增时 ms</x:v>
+      <x:c r="L29" s="18" t="str">
+        <x:v>Total overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="M29" s="73" t="str">
         <x:v>平均 TPOT 增量 μs</x:v>
@@ -13104,10 +13125,12 @@
         <x:v>TP 带宽项 ms</x:v>
       </x:c>
       <x:c r="S29" s="90" t="str">
-        <x:v>EP 增时 ms/60s</x:v>
+        <x:v>EP overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="T29" s="90" t="str">
-        <x:v>TP 增时 ms/60s</x:v>
+        <x:v>TP overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="U29" s="30"/>
       <x:c r="V29" s="30"/>
@@ -15352,8 +15375,9 @@
       <x:c r="U59" s="73" t="str">
         <x:v>基线 FW/min</x:v>
       </x:c>
-      <x:c r="V59" s="73" t="str">
-        <x:v>60s 工作增时 ms</x:v>
+      <x:c r="V59" s="18" t="str">
+        <x:v>Total overhead
+ms/60s</x:v>
       </x:c>
       <x:c r="W59" s="73" t="str">
         <x:v>输入 / 调度状态</x:v>

--- a/models/kimi-k3/kimi-k3-analysis.xlsx
+++ b/models/kimi-k3/kimi-k3-analysis.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="Rf46c58a971934790"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="Rc0fd1ca1a3514e6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R567046d9bf0a4ab5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prefill" sheetId="1" r:id="R664a75646e524fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decode" sheetId="2" r:id="R514238e05ae44d85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分钟场景" sheetId="3" r:id="R2f27702405a94009"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="13">
+  <x:numFmts count="15">
     <x:numFmt numFmtId="200" formatCode="0.##"/>
     <x:numFmt numFmtId="201" formatCode="0.0000"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.####"/>
@@ -29,6 +29,8 @@
     <x:numFmt numFmtId="210" formatCode="#,##0.000"/>
     <x:numFmt numFmtId="211" formatCode="#,##0.000000"/>
     <x:numFmt numFmtId="212" formatCode="0.000000%"/>
+    <x:numFmt numFmtId="213" formatCode="0.00000000%"/>
+    <x:numFmt numFmtId="214" formatCode="[=0]0.000000%;[&lt;0.00000001]&quot;&lt;0.000001%&quot;;0.000000%"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -69,7 +71,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="13">
+  <x:fills count="15">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -131,6 +133,16 @@
         <x:fgColor rgb="FFD9E1F2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="3">
     <x:border/>
@@ -166,7 +178,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="105">
+  <x:cellXfs count="113">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -417,6 +429,30 @@
     <x:xf numFmtId="203" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="213" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="214" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -12035,7 +12071,7 @@
     <x:col min="18" max="18" width="19" hidden="0" customWidth="1"/>
     <x:col min="19" max="19" width="19" hidden="0" customWidth="1"/>
     <x:col min="20" max="20" width="19" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="19" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="21" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="19" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="19" hidden="0" customWidth="1"/>
     <x:col min="24" max="24" width="19" hidden="0" customWidth="1"/>
@@ -13132,7 +13168,10 @@
         <x:v>TP overhead
 ms/60s</x:v>
       </x:c>
-      <x:c r="U29" s="30"/>
+      <x:c r="U29" s="111" t="str">
+        <x:v>Decode throughput
+loss (%)</x:v>
+      </x:c>
       <x:c r="V29" s="30"/>
       <x:c r="W29" s="30"/>
       <x:c r="X29" s="30"/>
@@ -13217,7 +13256,10 @@
         <x:f>IF(W60="",AJ60,"")</x:f>
         <x:v>0.07141190318323679</x:v>
       </x:c>
-      <x:c r="U30" s="30"/>
+      <x:c r="U30" s="112" t="n">
+        <x:f>IF(ISNUMBER(L30),L30/(60000+L30),IF(L30="","",L30))</x:f>
+        <x:v>0.000002539195545582969</x:v>
+      </x:c>
       <x:c r="V30" s="30"/>
       <x:c r="W30" s="30"/>
       <x:c r="X30" s="30"/>
@@ -13302,7 +13344,10 @@
         <x:f>IF(W61="",AJ61,"")</x:f>
         <x:v>0.03570595159161839</x:v>
       </x:c>
-      <x:c r="U31" s="30"/>
+      <x:c r="U31" s="112" t="n">
+        <x:f>IF(ISNUMBER(L31),L31/(60000+L31),IF(L31="","",L31))</x:f>
+        <x:v>0.0000012695993846720357</x:v>
+      </x:c>
       <x:c r="V31" s="30"/>
       <x:c r="W31" s="30"/>
       <x:c r="X31" s="30"/>
@@ -13387,7 +13432,10 @@
         <x:f>IF(W62="",AJ62,"")</x:f>
         <x:v>0.017852975795809196</x:v>
       </x:c>
-      <x:c r="U32" s="30"/>
+      <x:c r="U32" s="112" t="n">
+        <x:f>IF(ISNUMBER(L32),L32/(60000+L32),IF(L32="","",L32))</x:f>
+        <x:v>6.34800095306923e-7</x:v>
+      </x:c>
       <x:c r="V32" s="30"/>
       <x:c r="W32" s="30"/>
       <x:c r="X32" s="30"/>
@@ -13472,7 +13520,10 @@
         <x:f>IF(W63="",AJ63,"")</x:f>
         <x:v>0.011901983863872798</x:v>
       </x:c>
-      <x:c r="U33" s="30"/>
+      <x:c r="U33" s="112" t="n">
+        <x:f>IF(ISNUMBER(L33),L33/(60000+L33),IF(L33="","",L33))</x:f>
+        <x:v>4.2320015308711454e-7</x:v>
+      </x:c>
       <x:c r="V33" s="30"/>
       <x:c r="W33" s="30"/>
       <x:c r="X33" s="30"/>
@@ -13557,7 +13608,10 @@
         <x:f>IF(W64="",AJ64,"")</x:f>
         <x:v>0.20323946682416733</x:v>
       </x:c>
-      <x:c r="U34" s="30"/>
+      <x:c r="U34" s="112" t="n">
+        <x:f>IF(ISNUMBER(L34),L34/(60000+L34),IF(L34="","",L34))</x:f>
+        <x:v>0.0000072265799989659895</x:v>
+      </x:c>
       <x:c r="V34" s="30"/>
       <x:c r="W34" s="30"/>
       <x:c r="X34" s="30"/>
@@ -13642,7 +13696,10 @@
         <x:f>IF(W65="",AJ65,"")</x:f>
         <x:v>0.10161973341208366</x:v>
       </x:c>
-      <x:c r="U35" s="30"/>
+      <x:c r="U35" s="112" t="n">
+        <x:f>IF(ISNUMBER(L35),L35/(60000+L35),IF(L35="","",L35))</x:f>
+        <x:v>0.00000361330305539479</x:v>
+      </x:c>
       <x:c r="V35" s="30"/>
       <x:c r="W35" s="30"/>
       <x:c r="X35" s="30"/>
@@ -13727,7 +13784,10 @@
         <x:f>IF(W66="",AJ66,"")</x:f>
         <x:v>0.05080986670604183</x:v>
       </x:c>
-      <x:c r="U36" s="30"/>
+      <x:c r="U36" s="112" t="n">
+        <x:f>IF(ISNUMBER(L36),L36/(60000+L36),IF(L36="","",L36))</x:f>
+        <x:v>0.0000018066547916930345</x:v>
+      </x:c>
       <x:c r="V36" s="30"/>
       <x:c r="W36" s="30"/>
       <x:c r="X36" s="30"/>
@@ -13812,7 +13872,10 @@
         <x:f>IF(W67="",AJ67,"")</x:f>
         <x:v>0.03387324447069455</x:v>
       </x:c>
-      <x:c r="U37" s="30"/>
+      <x:c r="U37" s="112" t="n">
+        <x:f>IF(ISNUMBER(L37),L37/(60000+L37),IF(L37="","",L37))</x:f>
+        <x:v>0.000001204437253129468</x:v>
+      </x:c>
       <x:c r="V37" s="30"/>
       <x:c r="W37" s="30"/>
       <x:c r="X37" s="30"/>
@@ -13897,7 +13960,10 @@
         <x:f>IF(W68="",AJ68,"")</x:f>
         <x:v>0.26930071420807705</x:v>
       </x:c>
-      <x:c r="U38" s="30"/>
+      <x:c r="U38" s="112" t="n">
+        <x:f>IF(ISNUMBER(L38),L38/(60000+L38),IF(L38="","",L38))</x:f>
+        <x:v>0.000009575496995704403</x:v>
+      </x:c>
       <x:c r="V38" s="30"/>
       <x:c r="W38" s="30"/>
       <x:c r="X38" s="30"/>
@@ -13982,7 +14048,10 @@
         <x:f>IF(W69="",AJ69,"")</x:f>
         <x:v>0.13465035710403853</x:v>
       </x:c>
-      <x:c r="U39" s="30"/>
+      <x:c r="U39" s="112" t="n">
+        <x:f>IF(ISNUMBER(L39),L39/(60000+L39),IF(L39="","",L39))</x:f>
+        <x:v>0.000004787771420497628</x:v>
+      </x:c>
       <x:c r="V39" s="30"/>
       <x:c r="W39" s="30"/>
       <x:c r="X39" s="30"/>
@@ -14067,7 +14136,10 @@
         <x:f>IF(W70="",AJ70,"")</x:f>
         <x:v>0.06732517855201926</x:v>
       </x:c>
-      <x:c r="U40" s="30"/>
+      <x:c r="U40" s="112" t="n">
+        <x:f>IF(ISNUMBER(L40),L40/(60000+L40),IF(L40="","",L40))</x:f>
+        <x:v>0.0000023938914409513264</x:v>
+      </x:c>
       <x:c r="V40" s="30"/>
       <x:c r="W40" s="30"/>
       <x:c r="X40" s="30"/>
@@ -14152,7 +14224,10 @@
         <x:f>IF(W71="",AJ71,"")</x:f>
         <x:v>0.04488345236801285</x:v>
       </x:c>
-      <x:c r="U41" s="30"/>
+      <x:c r="U41" s="112" t="n">
+        <x:f>IF(ISNUMBER(L41),L41/(60000+L41),IF(L41="","",L41))</x:f>
+        <x:v>0.000001595928900794396</x:v>
+      </x:c>
       <x:c r="V41" s="30"/>
       <x:c r="W41" s="30"/>
       <x:c r="X41" s="30"/>
@@ -14237,7 +14312,10 @@
         <x:f>IF(W72="",AJ72,"")</x:f>
         <x:v>0.07141190318323679</x:v>
       </x:c>
-      <x:c r="U42" s="30"/>
+      <x:c r="U42" s="112" t="n">
+        <x:f>IF(ISNUMBER(L42),L42/(60000+L42),IF(L42="","",L42))</x:f>
+        <x:v>0.0000025780138062870714</x:v>
+      </x:c>
       <x:c r="V42" s="30"/>
       <x:c r="W42" s="30"/>
       <x:c r="X42" s="30"/>
@@ -14322,7 +14400,10 @@
         <x:f>IF(W73="",AJ73,"")</x:f>
         <x:v>0.03570595159161839</x:v>
       </x:c>
-      <x:c r="U43" s="30"/>
+      <x:c r="U43" s="112" t="n">
+        <x:f>IF(ISNUMBER(L43),L43/(60000+L43),IF(L43="","",L43))</x:f>
+        <x:v>0.0000012890085646844738</x:v>
+      </x:c>
       <x:c r="V43" s="30"/>
       <x:c r="W43" s="30"/>
       <x:c r="X43" s="30"/>
@@ -14407,7 +14488,10 @@
         <x:f>IF(W74="",AJ74,"")</x:f>
         <x:v>0.017852975795809196</x:v>
       </x:c>
-      <x:c r="U44" s="30"/>
+      <x:c r="U44" s="112" t="n">
+        <x:f>IF(ISNUMBER(L44),L44/(60000+L44),IF(L44="","",L44))</x:f>
+        <x:v>6.445046977282746e-7</x:v>
+      </x:c>
       <x:c r="V44" s="30"/>
       <x:c r="W44" s="30"/>
       <x:c r="X44" s="30"/>
@@ -14492,7 +14576,10 @@
         <x:f>IF(W75="",AJ75,"")</x:f>
         <x:v>0.011901983863872798</x:v>
       </x:c>
-      <x:c r="U45" s="30"/>
+      <x:c r="U45" s="112" t="n">
+        <x:f>IF(ISNUMBER(L45),L45/(60000+L45),IF(L45="","",L45))</x:f>
+        <x:v>4.2966989079360415e-7</x:v>
+      </x:c>
       <x:c r="V45" s="30"/>
       <x:c r="W45" s="30"/>
       <x:c r="X45" s="30"/>
@@ -14577,7 +14664,10 @@
         <x:f>IF(W76="",AJ76,"")</x:f>
         <x:v>0.20323946682416733</x:v>
       </x:c>
-      <x:c r="U46" s="30"/>
+      <x:c r="U46" s="112" t="n">
+        <x:f>IF(ISNUMBER(L46),L46/(60000+L46),IF(L46="","",L46))</x:f>
+        <x:v>0.0000073370622644750296</x:v>
+      </x:c>
       <x:c r="V46" s="30"/>
       <x:c r="W46" s="30"/>
       <x:c r="X46" s="30"/>
@@ -14662,7 +14752,10 @@
         <x:f>IF(W77="",AJ77,"")</x:f>
         <x:v>0.10161973341208366</x:v>
       </x:c>
-      <x:c r="U47" s="30"/>
+      <x:c r="U47" s="112" t="n">
+        <x:f>IF(ISNUMBER(L47),L47/(60000+L47),IF(L47="","",L47))</x:f>
+        <x:v>0.0000036685445904075544</x:v>
+      </x:c>
       <x:c r="V47" s="30"/>
       <x:c r="W47" s="30"/>
       <x:c r="X47" s="30"/>
@@ -14747,7 +14840,10 @@
         <x:f>IF(W78="",AJ78,"")</x:f>
         <x:v>0.05080986670604183</x:v>
       </x:c>
-      <x:c r="U48" s="30"/>
+      <x:c r="U48" s="112" t="n">
+        <x:f>IF(ISNUMBER(L48),L48/(60000+L48),IF(L48="","",L48))</x:f>
+        <x:v>0.0000018342756597648016</x:v>
+      </x:c>
       <x:c r="V48" s="30"/>
       <x:c r="W48" s="30"/>
       <x:c r="X48" s="30"/>
@@ -14832,7 +14928,10 @@
         <x:f>IF(W79="",AJ79,"")</x:f>
         <x:v>0.03387324447069455</x:v>
       </x:c>
-      <x:c r="U49" s="30"/>
+      <x:c r="U49" s="112" t="n">
+        <x:f>IF(ISNUMBER(L49),L49/(60000+L49),IF(L49="","",L49))</x:f>
+        <x:v>0.0000012228511875252572</x:v>
+      </x:c>
       <x:c r="V49" s="30"/>
       <x:c r="W49" s="30"/>
       <x:c r="X49" s="30"/>
@@ -14917,7 +15016,10 @@
         <x:f>IF(W80="",AJ80,"")</x:f>
         <x:v>0.26930071420807705</x:v>
       </x:c>
-      <x:c r="U50" s="30"/>
+      <x:c r="U50" s="112" t="n">
+        <x:f>IF(ISNUMBER(L50),L50/(60000+L50),IF(L50="","",L50))</x:f>
+        <x:v>0.000009721890323698737</x:v>
+      </x:c>
       <x:c r="V50" s="30"/>
       <x:c r="W50" s="30"/>
       <x:c r="X50" s="30"/>
@@ -15002,7 +15104,10 @@
         <x:f>IF(W81="",AJ81,"")</x:f>
         <x:v>0.13465035710403853</x:v>
       </x:c>
-      <x:c r="U51" s="30"/>
+      <x:c r="U51" s="112" t="n">
+        <x:f>IF(ISNUMBER(L51),L51/(60000+L51),IF(L51="","",L51))</x:f>
+        <x:v>0.000004860968790752094</x:v>
+      </x:c>
       <x:c r="V51" s="30"/>
       <x:c r="W51" s="30"/>
       <x:c r="X51" s="30"/>
@@ -15087,7 +15192,10 @@
         <x:f>IF(W82="",AJ82,"")</x:f>
         <x:v>0.06732517855201926</x:v>
       </x:c>
-      <x:c r="U52" s="30"/>
+      <x:c r="U52" s="112" t="n">
+        <x:f>IF(ISNUMBER(L52),L52/(60000+L52),IF(L52="","",L52))</x:f>
+        <x:v>0.0000024304903026448005</x:v>
+      </x:c>
       <x:c r="V52" s="30"/>
       <x:c r="W52" s="30"/>
       <x:c r="X52" s="30"/>
@@ -15172,13 +15280,18 @@
         <x:f>IF(W83="",AJ83,"")</x:f>
         <x:v>0.04488345236801285</x:v>
       </x:c>
-      <x:c r="U53" s="30"/>
+      <x:c r="U53" s="112" t="n">
+        <x:f>IF(ISNUMBER(L53),L53/(60000+L53),IF(L53="","",L53))</x:f>
+        <x:v>0.000001620328181160511</x:v>
+      </x:c>
       <x:c r="V53" s="30"/>
       <x:c r="W53" s="30"/>
       <x:c r="X53" s="30"/>
     </x:row>
     <x:row r="54" ht="22" customHeight="1">
-      <x:c r="A54" s="30"/>
+      <x:c r="A54" s="30" t="str">
+        <x:v>Decode throughput loss = Total overhead / (60000 + Total overhead). Fixed batch size and tokens/step; Decode stays busy.</x:v>
+      </x:c>
       <x:c r="B54" s="30"/>
       <x:c r="C54" s="30"/>
       <x:c r="D54" s="30"/>
